--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -567,7 +567,7 @@
         <v>45603</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>45812.47355324074</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>45827.64737268518</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>44377</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45313</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>45548</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>45082</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>45728</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45715.38824074074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>45812.55136574074</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44971</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>45202</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>44623</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>44222</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45086</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44575</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45803.55260416667</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>45803.55737268519</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45196</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>45758</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>44356</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>44180</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45442</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45092</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>44497</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>45812</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>45013</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>45799.60315972222</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>44792</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>45803.61035879629</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44351</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44574</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>45316</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>45107</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45736.53695601852</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45097</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44719</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44056</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44664</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>45371</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44974</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>45841.64539351852</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>45442</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>44740</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>44659</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>45026</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>44791</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>45090</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>45803.55535879629</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>44684</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>45831.55982638889</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44495</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>45222</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45474</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>44967</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>45694.55559027778</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>45035.44672453704</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>45841.80690972223</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>45762.62260416667</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>45666</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45715.38105324074</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>45168.50667824074</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>45293</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>44489</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>45189</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>44614</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44379</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>44651</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>44467</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>44532</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>45757.49934027778</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>44917</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>44855</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>45107</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>45762.57244212963</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>44963</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45464</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>45385</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>44081</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44909</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44487</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>45273</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>45694.49650462963</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>45783</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>44673.47858796296</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>45687</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>45107</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>45167</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44897</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44645</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>45803.61554398148</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45805.41232638889</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>44958</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45358</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>45098</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>45763.52524305556</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>45811.38710648148</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>45679</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>45818.60254629629</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>45817.34614583333</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>45336</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>45817</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45736.49902777778</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>45820.84516203704</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>45874.69282407407</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45874</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>44917.59298611111</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>45314.55579861111</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44849</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44144</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>44063</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>44119</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>44583.61803240741</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44602</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>44602</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>44517</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>44567.81241898148</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>44407</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44544</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44526</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44489</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>44609.61430555556</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44083</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44583.62121527778</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44323.58961805556</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44299</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>44714</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44491.50769675926</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>44252</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>44569.5340625</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44486</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>44662.56783564815</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44659.70381944445</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44572.39640046296</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>44230</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>44494</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>44839</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>44603</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>44700</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44784</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>44369.65428240741</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>44612</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>44720</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>44886</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44598</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44883.56321759259</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>44314</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>44610</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>44865.43494212963</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>44167</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>44357</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>44742</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>44704</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>44533.4678587963</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>44764</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>44453</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>44297</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
         <v>44153</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>44351</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>44349.49666666667</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>44584.63190972222</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>44609</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44490.64313657407</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>44091</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>44055</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>44281.4499537037</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44610</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>44335.52201388889</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>44512</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>44740.68142361111</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>44816</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>44297</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>44705.78475694444</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>44705.83326388889</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>44722.30703703704</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>44583.61555555555</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>44575</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>44649</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>44692.87630787037</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>44698.67151620371</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44575.4366087963</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>44847</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>44277.65263888889</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>44328.57100694445</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>44599.43265046296</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>44369</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>44750.678125</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44685.6212037037</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>44543</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>44461</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>44865</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44383</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44461.73350694445</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44378.69857638889</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>44702.70721064815</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>44593</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>44504.59193287037</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>44442.35195601852</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>44442</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>44733.43420138889</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>44643.51446759259</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44711</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>44750.45800925926</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>44076</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>44743</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44095</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44846</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44551.59704861111</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44134</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>44446.47693287037</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>44623.4572337963</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>44571.44563657408</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>44103</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>44479</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>44838.40635416667</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>44491.54116898148</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>44676</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>44459</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>44489</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>44543.34697916666</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>44729</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>44476.61263888889</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44495</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44847.35622685185</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>44705.84535879629</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>44160</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>44144</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>44517</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>44266.57917824074</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>44634</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>44294.37555555555</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44522.55518518519</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44659.57912037037</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>44886.58890046296</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>44791.38336805555</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>44623</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>44762</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>44798</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>44144</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>45266</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>44872</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>45048.55349537037</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45050.49392361111</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>44799.36359953704</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>44848</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45259</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>45513.51815972223</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45617.59006944444</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45187.61136574074</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>45049</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>44560</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>45336.53908564815</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>45614.67020833334</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>45223</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>45371.50738425926</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>44420</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44993</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45714.55368055555</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>45723</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45208.46130787037</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>45723.63290509259</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>45763.52995370371</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>45770.61341435185</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44859.36896990741</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>44328</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>44832</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45677.39440972222</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>44531</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>44883</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>45169</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>44866</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45244.52202546296</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45435.34778935185</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45763</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>44532</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45548.42854166667</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>45741.45114583334</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45763.52744212963</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>44532</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>44847</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45190</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45757.67611111111</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45078</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>44378.56137731481</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45259.52809027778</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>44446</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         <v>45096</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>44977</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45336.54270833333</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>44123</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>44831</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>45758</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44139</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44809.92752314815</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44810</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44371.49178240741</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>45202</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>45638</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45110</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         <v>44900.54711805555</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45580</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>45194</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44395</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>44944</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45555.5727662037</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>45295</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>45474</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>44168.55746527778</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>44095</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>44551.76711805556</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>45611</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45327</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45554</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>45757</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>45300.55680555556</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>45589</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45589</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44609.60171296296</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>44816</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45231.54601851852</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45763.6503125</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>45316</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45317</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44503</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44624.35083333333</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>45456.58491898148</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>44897</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45259</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45259</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>45310.53418981482</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45729</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>45729</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>45327</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>45014</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45222</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>44593</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>45685.5778125</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45695.59805555556</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45460</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>45345.56</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>44883</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24496,7 +24496,7 @@
         <v>44849</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45307</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>45104.6828125</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>44914.67600694444</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>45061</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>44210</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45642</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45583.47836805556</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>44912</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45119</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>44967.78984953704</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>44966</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>44894.57065972222</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>45075.51982638889</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>45349</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44501.71344907407</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>45756.44024305556</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>45756.50738425926</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>45720.60410879629</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>45341</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>45699</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>45733.63099537037</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>45426.61569444444</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45478.60802083334</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45719.40723379629</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>45644</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>45154.34931712963</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26075,7 +26075,7 @@
         <v>44548</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26132,7 +26132,7 @@
         <v>45341.63811342593</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>44550.37994212963</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45699.71063657408</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45729</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44935</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45743.50744212963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44980</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45614.65928240741</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45337.58318287037</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>45175.57060185185</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45695.59197916667</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>45644.47723379629</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45679</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>44504</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>45006</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27002,7 +27002,7 @@
         <v>44435.38657407407</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27059,7 +27059,7 @@
         <v>44602</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>45254.49552083333</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45611</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45344.64759259259</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45307</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>45107</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>45107</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>45107</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>45614</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>45344.69567129629</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>44816</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45327</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>44977</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>45133</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>45096</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>45098.62966435185</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45300</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>45152</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45670</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>44544</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>44519</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28281,7 +28281,7 @@
         <v>45335</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>45293</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>45776.48275462963</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>45776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>44131</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>45163.59913194444</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45096</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45776.45263888889</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45107.55574074074</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44624.64538194444</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>45776.6415162037</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>45618.71140046296</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>44637.56178240741</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>45294.5666550926</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>45777.37119212963</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>45777.34894675926</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45777.32731481481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>45777.52655092593</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45777</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>45520</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45453</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>45574</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>45779.6665162037</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>45779.65787037037</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44140</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>45524</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44109</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>45779.49085648148</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>44967</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30009,7 +30009,7 @@
         <v>44909</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         <v>44599.42277777778</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>44553</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>44593</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>44593.61355324074</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>45783.61053240741</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>45344</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>44946</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>45425.94947916667</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>45664</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45784.57266203704</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>45194.63479166666</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>44569.49344907407</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>44426</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45407.49721064815</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>44106</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>44608</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>45614</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31070,7 +31070,7 @@
         <v>45784.80497685185</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>44603</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>45202.4997337963</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>45161</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45329</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45177.79766203704</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45558.42498842593</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>45562</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45524</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>44629.57741898148</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45468</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>45037</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45368.64787037037</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>45552</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>45134.57021990741</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>44569.69358796296</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>44960</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>44960.66233796296</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44533.46665509259</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>45726</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>45021.29524305555</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>45684</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>45511</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45583</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>45583</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32555,7 +32555,7 @@
         <v>44535</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>45426</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>44637.35744212963</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>45254</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>45036</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>45624</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>44553</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>44126</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45162</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45159.44694444445</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45231</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>44575</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45145</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>45097</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>45201.62318287037</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33415,7 +33415,7 @@
         <v>45358</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45726</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>44522</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>44200</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45371.67368055556</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>44616</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45790.51040509259</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>45181.33571759259</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>44893</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33933,7 +33933,7 @@
         <v>44516</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33990,7 +33990,7 @@
         <v>45369</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44155</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>44904</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>45091</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>45790.44972222222</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>45583.48449074074</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>44659</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34409,7 +34409,7 @@
         <v>45707</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>45584.60038194444</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45177.56940972222</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>45625.58501157408</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>45790.51186342593</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>45736.60863425926</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>45358</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>45379</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>44912.29869212963</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>44614.69730324074</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45691</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>45443</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>44967.55960648148</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>45523</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>45763</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>45721.60894675926</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>45254</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35413,7 +35413,7 @@
         <v>45644</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>45159.45748842593</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>45643</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>44678.3315625</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>44610</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45615</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>45638</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>45202</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>45644</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45188</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>45525</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>44832.49594907407</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         <v>45335.66331018518</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>45366.42888888889</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>45195.64807870371</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>45338.49412037037</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>45835.62752314815</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>45838.42870370371</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45838.43577546296</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>45636</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>44277.65650462963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         <v>45838.43185185185</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>45721.35173611111</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>45148</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>45148</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>45148</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>44512</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>44588</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37044,7 +37044,7 @@
         <v>44159</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>45490</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>45323.55914351852</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45390</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>44617.48311342593</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>45194</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>44245</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>44977</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45601</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>45446.78256944445</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>45439</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37706,7 +37706,7 @@
         <v>44594</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>45638</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45429</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>45769.6009375</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>45698.65606481482</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>45693</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>45371</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45677</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45190</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>45426</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44629.42423611111</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>44993</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45797.45900462963</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>45351.54596064815</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>44733</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>45684</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>45054.9271875</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>44994</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>45798.42252314815</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38804,7 +38804,7 @@
         <v>45646.50211805556</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38861,7 +38861,7 @@
         <v>44665</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38923,7 +38923,7 @@
         <v>45173</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>45798.41734953703</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         <v>45068.58563657408</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>45840.68518518518</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45426.34148148148</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>44594</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>45797.42777777778</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39322,7 +39322,7 @@
         <v>45194.60876157408</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>44819.62</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39441,7 +39441,7 @@
         <v>45799.53348379629</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>45693</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39560,7 +39560,7 @@
         <v>45842.74049768518</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>45839</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>45055</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39731,7 +39731,7 @@
         <v>45182</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>45182</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>45363.54878472222</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39907,7 +39907,7 @@
         <v>45742.49414351852</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>45841.5847337963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>45093.46706018518</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40083,7 +40083,7 @@
         <v>44967.80034722222</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40140,7 +40140,7 @@
         <v>44967</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>44130</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40254,7 +40254,7 @@
         <v>45799.53803240741</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>45799.5421875</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40378,7 +40378,7 @@
         <v>45799.57714120371</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>45799.64877314815</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>45799.67806712963</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>45407.69575231482</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>45188.42052083334</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>44929</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>45733.62903935185</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         <v>45231.62840277778</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45799.68190972223</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>45799.675</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45799.53947916667</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -41030,7 +41030,7 @@
         <v>45799.54104166666</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>45730.43966435185</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>45839</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45677</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41268,7 +41268,7 @@
         <v>45841.81555555556</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>45614</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>45840</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>45737.40503472222</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>45799.65021990741</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>45799.6527199074</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>45695.8391550926</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>45695.84078703704</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>45799.43496527777</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41816,7 +41816,7 @@
         <v>45086.7037037037</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41878,7 +41878,7 @@
         <v>45583</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>44209</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>45744</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>45341</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45608</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>45042</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>44608</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42282,7 +42282,7 @@
         <v>44909.51885416666</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>45803.36384259259</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42406,7 +42406,7 @@
         <v>45600</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>45107.53688657407</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>45456.59535879629</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42582,7 +42582,7 @@
         <v>45705.2953125</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>45845.53202546296</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>45775.46377314815</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45803.63395833333</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>45216</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>45216</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>45173</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45624</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>45762.49243055555</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45694</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>45805.4094675926</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>45805.41010416667</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>44588</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>45729</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>45729</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>45208.4350462963</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>45705</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43576,7 +43576,7 @@
         <v>45805.41813657407</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>45089</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>45180.40255787037</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>44614.59027777778</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43814,7 +43814,7 @@
         <v>45520</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43871,7 +43871,7 @@
         <v>44679.68706018518</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43933,7 +43933,7 @@
         <v>45149.56928240741</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45805.43402777778</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -44057,7 +44057,7 @@
         <v>45805.4255787037</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45181.36815972222</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45511</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45849.49259259259</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>44679.66694444444</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>44223</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45474.41729166666</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>45182</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44528,7 +44528,7 @@
         <v>45182</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>45851.62179398148</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>45810.44339120371</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>45809</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45852.39642361111</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>45175</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>45851.62018518519</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45644.62677083333</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>45215.44233796297</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>45851.60097222222</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>45852.36871527778</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>45642</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>45699</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>45152</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45366,7 +45366,7 @@
         <v>45694.49037037037</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45423,7 +45423,7 @@
         <v>45695.83655092592</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>45707</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45645</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>44699</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45671,7 +45671,7 @@
         <v>45113</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>45113.80170138889</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         <v>45809</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         <v>45839</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45924,7 +45924,7 @@
         <v>45809</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>45757.6997337963</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>45757</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>45631.44464120371</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46157,7 +46157,7 @@
         <v>45453.69339120371</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46219,7 +46219,7 @@
         <v>45852.68978009259</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45810.44299768518</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46343,7 +46343,7 @@
         <v>44222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46400,7 +46400,7 @@
         <v>45852.72965277778</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46462,7 +46462,7 @@
         <v>45809</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46519,7 +46519,7 @@
         <v>45225.46480324074</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>45131</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46633,7 +46633,7 @@
         <v>45852</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46695,7 +46695,7 @@
         <v>45853.76976851852</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46752,7 +46752,7 @@
         <v>45854.44017361111</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45812.48032407407</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45259</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46933,7 +46933,7 @@
         <v>45693</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46990,7 +46990,7 @@
         <v>45810.45960648148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>45719.4094212963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47114,7 +47114,7 @@
         <v>45236.47697916667</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>45719.43872685185</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47233,7 +47233,7 @@
         <v>44644.37548611111</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47295,7 +47295,7 @@
         <v>45299</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47352,7 +47352,7 @@
         <v>45267</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>45856.34959490741</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>45236</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47533,7 +47533,7 @@
         <v>45721.34715277778</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47590,7 +47590,7 @@
         <v>45814</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47647,7 +47647,7 @@
         <v>45813</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
         <v>44400.6750925926</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45813.46034722222</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47823,7 +47823,7 @@
         <v>44403.3119212963</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47885,7 +47885,7 @@
         <v>45856.34034722222</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47947,7 +47947,7 @@
         <v>45856.34231481481</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45856.36153935185</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>45719.42197916667</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45719.43646990741</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>45818.57910879629</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>44799.36695601852</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45254</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45321</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>44980</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>45817</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>45317</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45361.57299768519</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>45820</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>45820</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48775,7 +48775,7 @@
         <v>44508.44033564815</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48837,7 +48837,7 @@
         <v>45817</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>44519.64902777778</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48956,7 +48956,7 @@
         <v>45164.82913194445</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>45442</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49075,7 +49075,7 @@
         <v>45351.48662037037</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>44930</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49189,7 +49189,7 @@
         <v>45820</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49246,7 +49246,7 @@
         <v>45656</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>45310</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>45863.44648148148</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49422,7 +49422,7 @@
         <v>44438</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>45098.63572916666</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>45821.45905092593</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>45824.43798611111</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>45821.44101851852</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45863.45355324074</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>45694</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>44820.47935185185</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45091.69766203704</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>45751.32001157408</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50007,7 +50007,7 @@
         <v>45065.43013888889</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>45637</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>44532</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45691</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50240,7 +50240,7 @@
         <v>45825.44482638889</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45867.58056712963</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>45825.49060185185</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50421,7 +50421,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50478,7 +50478,7 @@
         <v>45827.62096064815</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>45852.67366898148</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>45827.64092592592</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45821.31292824074</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>45691</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50768,7 +50768,7 @@
         <v>45719.43755787037</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45054.95675925926</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>45772.77188657408</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>45827.46288194445</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45874.705</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45831.42365740741</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>45831.42616898148</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45831.73</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45047.31793981481</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>44888</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>45736.45847222222</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>45693</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>44207</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51539,7 +51539,7 @@
         <v>45127</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51596,7 +51596,7 @@
         <v>44379.5745949074</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>45831.46731481481</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51710,7 +51710,7 @@
         <v>44788</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>45761.47540509259</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>45761.47748842592</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45832.35590277778</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51943,7 +51943,7 @@
         <v>45831.40671296296</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         <v>45665</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52057,7 +52057,7 @@
         <v>45832.35545138889</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>45693</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>45831.72686342592</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52238,7 +52238,7 @@
         <v>44817</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>45216.39040509259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52352,7 +52352,7 @@
         <v>45874</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>45876</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45876</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52523,7 +52523,7 @@
         <v>45478</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45599</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52642,7 +52642,7 @@
         <v>45642.63524305556</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52699,7 +52699,7 @@
         <v>45646.61892361111</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52756,7 +52756,7 @@
         <v>44984.69216435185</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52818,7 +52818,7 @@
         <v>44379.56163194445</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>45391.37361111111</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52932,7 +52932,7 @@
         <v>45679</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52994,7 +52994,7 @@
         <v>44063</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>45520</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53108,7 +53108,7 @@
         <v>44581.60254629629</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53170,7 +53170,7 @@
         <v>44568.67040509259</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53232,7 +53232,7 @@
         <v>44123</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53289,7 +53289,7 @@
         <v>44908.425625</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>44358.63490740741</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53403,7 +53403,7 @@
         <v>44949.4708912037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53460,7 +53460,7 @@
         <v>44403.29719907408</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>44946.43564814814</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>45033</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>44531</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>44105</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>44209</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>44273</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>44960.65061342593</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>44960</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53983,7 +53983,7 @@
         <v>44593.64863425926</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54045,7 +54045,7 @@
         <v>44928</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54107,7 +54107,7 @@
         <v>45552</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54164,7 +54164,7 @@
         <v>45121</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54226,7 +54226,7 @@
         <v>44819.50233796296</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>44616</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54345,7 +54345,7 @@
         <v>44886</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54402,7 +54402,7 @@
         <v>44560</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54459,7 +54459,7 @@
         <v>44600</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54521,7 +54521,7 @@
         <v>44623.41775462963</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54583,7 +54583,7 @@
         <v>44623.5571875</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>45167.3721412037</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54702,7 +54702,7 @@
         <v>44965</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>44965</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>45308.63298611111</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54873,7 +54873,7 @@
         <v>45212.34997685185</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54930,7 +54930,7 @@
         <v>44886.5928125</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -54987,7 +54987,7 @@
         <v>45293</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55044,7 +55044,7 @@
         <v>45181.58055555556</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>45670</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>44742</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55230,7 +55230,7 @@
         <v>45231</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>45341</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45594</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>45300.55028935185</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55468,7 +55468,7 @@
         <v>45097</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55525,7 +55525,7 @@
         <v>44969</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>44944</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>45601</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45154.35092592592</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55753,7 +55753,7 @@
         <v>44652</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55810,7 +55810,7 @@
         <v>45678</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55867,7 +55867,7 @@
         <v>44679</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55924,7 +55924,7 @@
         <v>45656</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55986,7 +55986,7 @@
         <v>45694</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56043,7 +56043,7 @@
         <v>44806</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>45049.66025462963</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>45679</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>44574</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>44645.39157407408</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>44497.4666087963</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         <v>45152</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>44964.65261574074</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>44599.44832175926</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45481.83684027778</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         <v>45638</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         <v>45000.44666666666</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>45762.61341435185</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>45713.44519675926</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         <v>45327.61831018519</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>45352</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56960,7 +56960,7 @@
         <v>44944</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -567,7 +567,7 @@
         <v>45603</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>45812.47355324074</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>45827.64737268518</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>44377</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45313</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>45548</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>45082</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>45728</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45715.38824074074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>45812.55136574074</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44971</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>45202</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>44623</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>44222</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45086</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44575</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45803.55260416667</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>45803.55737268519</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45196</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>45758</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>44356</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>44180</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45442</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45092</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>44497</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>45812</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>45013</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>45799.60315972222</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>44792</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>45803.61035879629</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>44500</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44351</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44574</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>45316</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>45107</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45736.53695601852</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45097</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44719</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44056</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44664</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>45371</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44974</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>45841.64539351852</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>45442</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>44740</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>44659</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>45026</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>44791</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>45090</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>45803.55535879629</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>44684</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>45831.55982638889</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44495</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>45222</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45474</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>44967</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>45694.55559027778</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>45035.44672453704</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>45841.80690972223</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>45762.62260416667</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>45666</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45715.38105324074</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>45168.50667824074</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>45293</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>44489</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>45189</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>44614</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44379</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>44651</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>44467</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>44532</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>45757.49934027778</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>44917</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>44855</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>45107</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>45762.57244212963</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>44963</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45464</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>45385</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>44081</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44909</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44487</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>45273</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>45694.49650462963</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>45783</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>44673.47858796296</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>45687</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>45107</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>45167</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44897</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44645</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>45803.61554398148</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45805.41232638889</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>44958</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45358</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>45098</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>45763.52524305556</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>45811.38710648148</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>45679</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>45818.60254629629</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>45817.34614583333</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>45336</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>45817</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45736.49902777778</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>45820.84516203704</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>45874.69282407407</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45874</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>44917.59298611111</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>45314.55579861111</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44849</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44144</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>44063</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>44119</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>44583.61803240741</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44602</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>44602</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>44517</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>44567.81241898148</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>44407</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44544</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44526</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44489</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>44609.61430555556</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44083</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44583.62121527778</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44323.58961805556</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44299</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>44714</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44491.50769675926</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>44252</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>44569.5340625</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44486</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>44662.56783564815</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44659.70381944445</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44572.39640046296</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>44230</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>44494</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>44839</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>44603</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>44700</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44784</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>44369.65428240741</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>44612</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>44720</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>44886</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44598</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44883.56321759259</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>44314</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>44610</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>44865.43494212963</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>44167</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>44357</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>44742</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>44704</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>44533.4678587963</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>44764</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>44453</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>44297</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
         <v>44153</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>44351</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>44349.49666666667</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>44584.63190972222</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>44609</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44490.64313657407</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>44091</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>44055</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>44281.4499537037</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44610</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>44335.52201388889</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>44512</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>44740.68142361111</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>44816</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>44297</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>44705.78475694444</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>44705.83326388889</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>44722.30703703704</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>44583.61555555555</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>44575</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>44649</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>44692.87630787037</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>44698.67151620371</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44575.4366087963</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>44847</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>44277.65263888889</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>44328.57100694445</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>44599.43265046296</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>44369</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>44750.678125</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44685.6212037037</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>44543</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>44461</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>44865</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44383</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44461.73350694445</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44378.69857638889</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>44702.70721064815</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>44593</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>44504.59193287037</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>44442.35195601852</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>44442</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>44733.43420138889</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>44643.51446759259</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44711</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>44750.45800925926</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>44076</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>44743</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44095</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44846</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44551.59704861111</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44134</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>44446.47693287037</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>44623.4572337963</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>44571.44563657408</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>44103</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>44479</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>44838.40635416667</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>44491.54116898148</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>44676</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>44459</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>44489</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>44543.34697916666</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>44729</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>44476.61263888889</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44495</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44847.35622685185</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>44705.84535879629</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>44160</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>44144</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>44517</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>44266.57917824074</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>44634</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>44294.37555555555</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44522.55518518519</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44659.57912037037</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>44886.58890046296</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>44791.38336805555</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>44623</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>44762</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>44798</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>44144</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>45266</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>44872</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>45048.55349537037</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45050.49392361111</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>44799.36359953704</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>44848</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45259</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>45513.51815972223</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45617.59006944444</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45187.61136574074</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>45049</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>44560</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>45336.53908564815</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>45614.67020833334</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>45223</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>45371.50738425926</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>44420</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44993</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45714.55368055555</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>45723</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45208.46130787037</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>45723.63290509259</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>45763.52995370371</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>45770.61341435185</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44859.36896990741</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>44328</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>44832</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45677.39440972222</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>44531</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>44883</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>45169</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>44866</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45244.52202546296</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45435.34778935185</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45763</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>44532</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45548.42854166667</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>45741.45114583334</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45763.52744212963</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>44532</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>44847</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45190</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45757.67611111111</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45078</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>44378.56137731481</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45259.52809027778</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>44446</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         <v>45096</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>44977</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45336.54270833333</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>44123</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>44831</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>45758</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44139</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44809.92752314815</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44810</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44371.49178240741</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>45202</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>45638</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45110</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         <v>44900.54711805555</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45580</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>45194</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44395</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>44944</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45555.5727662037</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>45295</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>45474</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>44168.55746527778</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>44095</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>44551.76711805556</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>45611</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45327</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45554</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>45757</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>45300.55680555556</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>45589</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45589</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44609.60171296296</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>44816</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45231.54601851852</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45763.6503125</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>45316</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45317</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44503</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44624.35083333333</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>45456.58491898148</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>44897</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45259</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45259</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>45310.53418981482</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45729</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>45729</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>45327</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>45014</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45222</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>44593</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>45685.5778125</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45695.59805555556</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45460</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>45345.56</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>44883</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24496,7 +24496,7 @@
         <v>44849</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45307</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>45104.6828125</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>44914.67600694444</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>45061</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>44210</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45642</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45583.47836805556</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>44912</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45119</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>44967.78984953704</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>44966</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>44894.57065972222</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>45075.51982638889</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>45349</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44501.71344907407</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>45756.44024305556</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>45756.50738425926</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>45720.60410879629</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>45341</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>45699</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>45733.63099537037</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>45426.61569444444</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45478.60802083334</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45719.40723379629</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>45644</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>45154.34931712963</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26075,7 +26075,7 @@
         <v>44548</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26132,7 +26132,7 @@
         <v>45341.63811342593</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>44550.37994212963</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45699.71063657408</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45729</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44935</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45743.50744212963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44980</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45614.65928240741</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45337.58318287037</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>45175.57060185185</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45695.59197916667</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>45644.47723379629</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45679</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>44504</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>45006</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27002,7 +27002,7 @@
         <v>44435.38657407407</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27059,7 +27059,7 @@
         <v>44602</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>45254.49552083333</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45611</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45344.64759259259</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45307</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>45107</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>45107</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>45107</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>45614</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>45344.69567129629</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>44816</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45327</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>44977</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>45133</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>45096</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>45098.62966435185</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45300</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>45152</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45670</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>44544</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>44519</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28281,7 +28281,7 @@
         <v>45335</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>45293</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>45776.48275462963</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>45776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>44131</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>45163.59913194444</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45096</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45776.45263888889</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45107.55574074074</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44624.64538194444</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>45776.6415162037</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>45618.71140046296</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>44637.56178240741</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>45294.5666550926</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>45777.37119212963</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>45777.34894675926</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45777.32731481481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>45777.52655092593</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45777</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>45520</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45453</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>45574</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>45779.6665162037</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>45779.65787037037</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44140</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>45524</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44109</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>45779.49085648148</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>44967</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30009,7 +30009,7 @@
         <v>44909</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         <v>44599.42277777778</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>44553</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>44593</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>44593.61355324074</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>45783.61053240741</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>45344</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>44946</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>45425.94947916667</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>45664</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45784.57266203704</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>45194.63479166666</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>44569.49344907407</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>44426</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45407.49721064815</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>44106</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>44608</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>45614</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31070,7 +31070,7 @@
         <v>45784.80497685185</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>44603</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>45202.4997337963</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>45161</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45329</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45177.79766203704</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45558.42498842593</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>45562</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45524</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>44629.57741898148</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45468</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>45037</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45368.64787037037</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>45552</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>45134.57021990741</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>44569.69358796296</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>44960</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>44960.66233796296</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44533.46665509259</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>45726</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>45021.29524305555</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>45684</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>45511</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45583</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>45583</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32555,7 +32555,7 @@
         <v>44535</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>45426</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>44637.35744212963</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>45254</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>45036</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>45624</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>44553</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>44126</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45162</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45159.44694444445</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45231</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>44575</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45145</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>45097</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>45201.62318287037</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33415,7 +33415,7 @@
         <v>45358</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45726</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>44522</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>44200</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45371.67368055556</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>44616</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45790.51040509259</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>45181.33571759259</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>44893</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33933,7 +33933,7 @@
         <v>44516</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33990,7 +33990,7 @@
         <v>45369</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44155</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>44904</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>45091</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>45790.44972222222</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>45583.48449074074</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>44659</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34409,7 +34409,7 @@
         <v>45707</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>45584.60038194444</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45177.56940972222</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>45625.58501157408</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>45790.51186342593</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>45736.60863425926</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>45358</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>45379</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>44912.29869212963</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>44614.69730324074</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45691</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>45443</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>44967.55960648148</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>45523</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>45763</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>45721.60894675926</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>45254</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35413,7 +35413,7 @@
         <v>45644</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>45159.45748842593</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>45643</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>44678.3315625</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>44610</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45615</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>45638</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>45202</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>45644</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45188</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>45525</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>44832.49594907407</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         <v>45335.66331018518</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>45366.42888888889</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>45195.64807870371</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>45338.49412037037</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>45835.62752314815</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>45838.42870370371</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45838.43577546296</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>45636</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>44277.65650462963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         <v>45838.43185185185</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>45721.35173611111</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>45148</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>45148</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>45148</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>44512</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>44588</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37044,7 +37044,7 @@
         <v>44159</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>45490</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>45323.55914351852</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45390</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>44617.48311342593</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>45194</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>44245</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>44977</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45601</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>45446.78256944445</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>45439</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37706,7 +37706,7 @@
         <v>44594</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>45638</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45429</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>45769.6009375</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>45698.65606481482</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>45693</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>45371</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45677</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45190</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>45426</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44629.42423611111</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>44993</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45797.45900462963</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>45351.54596064815</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>44733</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>45684</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>45054.9271875</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>44994</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>45798.42252314815</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38804,7 +38804,7 @@
         <v>45646.50211805556</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38861,7 +38861,7 @@
         <v>44665</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38923,7 +38923,7 @@
         <v>45173</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>45798.41734953703</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         <v>45068.58563657408</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>45840.68518518518</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45426.34148148148</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>44594</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>45797.42777777778</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39322,7 +39322,7 @@
         <v>45194.60876157408</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>44819.62</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39441,7 +39441,7 @@
         <v>45799.53348379629</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>45693</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39560,7 +39560,7 @@
         <v>45842.74049768518</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>45839</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>45055</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39731,7 +39731,7 @@
         <v>45182</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>45182</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>45363.54878472222</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39907,7 +39907,7 @@
         <v>45742.49414351852</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>45841.5847337963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>45093.46706018518</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40083,7 +40083,7 @@
         <v>44967.80034722222</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40140,7 +40140,7 @@
         <v>44967</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>44130</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40254,7 +40254,7 @@
         <v>45799.53803240741</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>45799.5421875</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40378,7 +40378,7 @@
         <v>45799.57714120371</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>45799.64877314815</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>45799.67806712963</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>45407.69575231482</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>45188.42052083334</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>44929</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>45733.62903935185</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         <v>45231.62840277778</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45799.68190972223</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>45799.675</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45799.53947916667</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -41030,7 +41030,7 @@
         <v>45799.54104166666</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>45730.43966435185</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>45839</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45677</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41268,7 +41268,7 @@
         <v>45841.81555555556</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>45614</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>45840</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>45737.40503472222</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>45799.65021990741</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>45799.6527199074</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>45695.8391550926</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>45695.84078703704</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>45799.43496527777</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41816,7 +41816,7 @@
         <v>45086.7037037037</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41878,7 +41878,7 @@
         <v>45583</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>44209</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>45744</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>45341</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45608</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>45042</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>44608</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42282,7 +42282,7 @@
         <v>44909.51885416666</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>45803.36384259259</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42406,7 +42406,7 @@
         <v>45600</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>45107.53688657407</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>45456.59535879629</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42582,7 +42582,7 @@
         <v>45705.2953125</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>45845.53202546296</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>45775.46377314815</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45803.63395833333</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>45216</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>45216</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>45173</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45624</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>45762.49243055555</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45694</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>45805.4094675926</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>45805.41010416667</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>44588</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>45729</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>45729</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>45208.4350462963</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>45705</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43576,7 +43576,7 @@
         <v>45805.41813657407</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>45089</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>45180.40255787037</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>44614.59027777778</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43814,7 +43814,7 @@
         <v>45520</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43871,7 +43871,7 @@
         <v>44679.68706018518</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43933,7 +43933,7 @@
         <v>45149.56928240741</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45805.43402777778</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -44057,7 +44057,7 @@
         <v>45805.4255787037</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45181.36815972222</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45511</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45849.49259259259</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>44679.66694444444</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>44223</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45474.41729166666</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>45182</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44528,7 +44528,7 @@
         <v>45182</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>45851.62179398148</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>45810.44339120371</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>45809</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45852.39642361111</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>45175</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>45851.62018518519</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45644.62677083333</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>45215.44233796297</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>45851.60097222222</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>45852.36871527778</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>45642</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>45699</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>45152</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45366,7 +45366,7 @@
         <v>45694.49037037037</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45423,7 +45423,7 @@
         <v>45695.83655092592</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>45707</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45645</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>44699</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45671,7 +45671,7 @@
         <v>45113</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>45113.80170138889</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         <v>45809</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         <v>45839</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45924,7 +45924,7 @@
         <v>45809</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>45757.6997337963</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>45757</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>45631.44464120371</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46157,7 +46157,7 @@
         <v>45453.69339120371</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46219,7 +46219,7 @@
         <v>45852.68978009259</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45810.44299768518</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46343,7 +46343,7 @@
         <v>44222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46400,7 +46400,7 @@
         <v>45852.72965277778</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46462,7 +46462,7 @@
         <v>45809</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46519,7 +46519,7 @@
         <v>45225.46480324074</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>45131</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46633,7 +46633,7 @@
         <v>45852</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46695,7 +46695,7 @@
         <v>45853.76976851852</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46752,7 +46752,7 @@
         <v>45854.44017361111</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45812.48032407407</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45259</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46933,7 +46933,7 @@
         <v>45693</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46990,7 +46990,7 @@
         <v>45810.45960648148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>45719.4094212963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47114,7 +47114,7 @@
         <v>45236.47697916667</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>45719.43872685185</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47233,7 +47233,7 @@
         <v>44644.37548611111</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47295,7 +47295,7 @@
         <v>45299</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47352,7 +47352,7 @@
         <v>45267</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>45856.34959490741</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>45236</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47533,7 +47533,7 @@
         <v>45721.34715277778</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47590,7 +47590,7 @@
         <v>45814</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47647,7 +47647,7 @@
         <v>45813</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
         <v>44400.6750925926</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45813.46034722222</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47823,7 +47823,7 @@
         <v>44403.3119212963</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47885,7 +47885,7 @@
         <v>45856.34034722222</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47947,7 +47947,7 @@
         <v>45856.34231481481</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45856.36153935185</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>45719.42197916667</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45719.43646990741</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>45818.57910879629</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>44799.36695601852</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45254</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45321</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>44980</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>45817</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>45317</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45361.57299768519</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>45820</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>45820</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48775,7 +48775,7 @@
         <v>44508.44033564815</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48837,7 +48837,7 @@
         <v>45817</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>44519.64902777778</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48956,7 +48956,7 @@
         <v>45164.82913194445</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>45442</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49075,7 +49075,7 @@
         <v>45351.48662037037</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>44930</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49189,7 +49189,7 @@
         <v>45820</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49246,7 +49246,7 @@
         <v>45656</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>45310</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>45863.44648148148</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49422,7 +49422,7 @@
         <v>44438</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>45098.63572916666</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>45821.45905092593</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>45824.43798611111</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>45821.44101851852</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45863.45355324074</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>45694</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>44820.47935185185</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45091.69766203704</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>45751.32001157408</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50007,7 +50007,7 @@
         <v>45065.43013888889</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>45637</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>44532</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45691</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50240,7 +50240,7 @@
         <v>45825.44482638889</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45867.58056712963</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>45825.49060185185</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50421,7 +50421,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50478,7 +50478,7 @@
         <v>45827.62096064815</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>45852.67366898148</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>45827.64092592592</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45821.31292824074</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>45691</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50768,7 +50768,7 @@
         <v>45719.43755787037</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45054.95675925926</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>45772.77188657408</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>45827.46288194445</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45874.705</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45831.42365740741</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>45831.42616898148</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45831.73</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45047.31793981481</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>44888</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>45736.45847222222</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>45693</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>44207</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51539,7 +51539,7 @@
         <v>45127</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51596,7 +51596,7 @@
         <v>44379.5745949074</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>45831.46731481481</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51710,7 +51710,7 @@
         <v>44788</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>45761.47540509259</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>45761.47748842592</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45832.35590277778</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51943,7 +51943,7 @@
         <v>45831.40671296296</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         <v>45665</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52057,7 +52057,7 @@
         <v>45832.35545138889</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>45693</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>45831.72686342592</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52238,7 +52238,7 @@
         <v>44817</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>45216.39040509259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52352,7 +52352,7 @@
         <v>45874</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>45876</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45876</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52523,7 +52523,7 @@
         <v>45478</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45599</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52642,7 +52642,7 @@
         <v>45642.63524305556</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52699,7 +52699,7 @@
         <v>45646.61892361111</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52756,7 +52756,7 @@
         <v>44984.69216435185</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52818,7 +52818,7 @@
         <v>44379.56163194445</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>45391.37361111111</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52932,7 +52932,7 @@
         <v>45679</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52994,7 +52994,7 @@
         <v>44063</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>45520</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53108,7 +53108,7 @@
         <v>44581.60254629629</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53170,7 +53170,7 @@
         <v>44568.67040509259</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53232,7 +53232,7 @@
         <v>44123</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53289,7 +53289,7 @@
         <v>44908.425625</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>44358.63490740741</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53403,7 +53403,7 @@
         <v>44949.4708912037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53460,7 +53460,7 @@
         <v>44403.29719907408</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>44946.43564814814</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>45033</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>44531</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>44105</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>44209</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>44273</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>44960.65061342593</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>44960</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53983,7 +53983,7 @@
         <v>44593.64863425926</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54045,7 +54045,7 @@
         <v>44928</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54107,7 +54107,7 @@
         <v>45552</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54164,7 +54164,7 @@
         <v>45121</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54226,7 +54226,7 @@
         <v>44819.50233796296</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>44616</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54345,7 +54345,7 @@
         <v>44886</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54402,7 +54402,7 @@
         <v>44560</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54459,7 +54459,7 @@
         <v>44600</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54521,7 +54521,7 @@
         <v>44623.41775462963</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54583,7 +54583,7 @@
         <v>44623.5571875</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>45167.3721412037</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54702,7 +54702,7 @@
         <v>44965</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>44965</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>45308.63298611111</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54873,7 +54873,7 @@
         <v>45212.34997685185</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54930,7 +54930,7 @@
         <v>44886.5928125</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -54987,7 +54987,7 @@
         <v>45293</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55044,7 +55044,7 @@
         <v>45181.58055555556</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>45670</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>44742</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55230,7 +55230,7 @@
         <v>45231</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>45341</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45594</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>45300.55028935185</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55468,7 +55468,7 @@
         <v>45097</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55525,7 +55525,7 @@
         <v>44969</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>44944</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>45601</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45154.35092592592</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55753,7 +55753,7 @@
         <v>44652</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55810,7 +55810,7 @@
         <v>45678</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55867,7 +55867,7 @@
         <v>44679</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55924,7 +55924,7 @@
         <v>45656</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55986,7 +55986,7 @@
         <v>45694</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56043,7 +56043,7 @@
         <v>44806</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>45049.66025462963</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>45679</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>44574</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>44645.39157407408</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>44497.4666087963</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         <v>45152</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>44964.65261574074</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>44599.44832175926</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45481.83684027778</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         <v>45638</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         <v>45000.44666666666</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>45762.61341435185</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>45713.44519675926</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         <v>45327.61831018519</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>45352</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56960,7 +56960,7 @@
         <v>44944</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -567,7 +567,7 @@
         <v>45603</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>45812.47355324074</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>45827.64737268518</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,64 +915,174 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
+          <t>A 38958-2024</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>45548</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>45886</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>UPPSALA</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>10</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>22</v>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Rosa jodskinn
+Laxporing
+Rostskinn
+Rynkskinn
+Dvärgbägarlav
+Järpe
+Rosenticka
+Tallticka
+Ullticka
+Vedtrappmossa
+Blodticka
+Brandticka
+Bronshjon
+Flagellkvastmossa
+Grön sköldmossa
+Grönpyrola
+Kattfotslav
+Stuplav
+Vårärt
+Fläcknycklar
+Nattviol
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="S5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0380/artfynd/A 38958-2024 artfynd.xlsx", "A 38958-2024")</f>
+        <v/>
+      </c>
+      <c r="T5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0380/kartor/A 38958-2024 karta.png", "A 38958-2024")</f>
+        <v/>
+      </c>
+      <c r="V5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomål/A 38958-2024 FSC-klagomål.docx", "A 38958-2024")</f>
+        <v/>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomålsmail/A 38958-2024 FSC-klagomål mail.docx", "A 38958-2024")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsyn/A 38958-2024 tillsynsbegäran.docx", "A 38958-2024")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsynsmail/A 38958-2024 tillsynsbegäran mail.docx", "A 38958-2024")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0380/fåglar/A 38958-2024 prioriterade fågelarter.docx", "A 38958-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>A 33279-2021</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B6" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>45885</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>UPPSALA</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="C6" s="1" t="n">
+        <v>45886</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>UPPSALA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Holmen skog AB</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="G6" t="n">
         <v>18.8</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H6" t="n">
         <v>4</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I6" t="n">
         <v>14</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>5</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q6" t="n">
         <v>21</v>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>Liten hornflikmossa
 Rynkskinn
@@ -997,87 +1107,87 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="S5">
+      <c r="S6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/artfynd/A 33279-2021 artfynd.xlsx", "A 33279-2021")</f>
         <v/>
       </c>
-      <c r="T5">
+      <c r="T6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/kartor/A 33279-2021 karta.png", "A 33279-2021")</f>
         <v/>
       </c>
-      <c r="V5">
+      <c r="V6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomål/A 33279-2021 FSC-klagomål.docx", "A 33279-2021")</f>
         <v/>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomålsmail/A 33279-2021 FSC-klagomål mail.docx", "A 33279-2021")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsyn/A 33279-2021 tillsynsbegäran.docx", "A 33279-2021")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsynsmail/A 33279-2021 tillsynsbegäran mail.docx", "A 33279-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 2523-2024</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B7" s="1" t="n">
         <v>45313</v>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>45885</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>UPPSALA</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="C7" s="1" t="n">
+        <v>45886</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>UPPSALA</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>18.8</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" t="n">
         <v>7</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>6</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>10</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>11</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P7" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q7" t="n">
         <v>20</v>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Granticka
@@ -1101,144 +1211,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="S6">
+      <c r="S7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/artfynd/A 2523-2024 artfynd.xlsx", "A 2523-2024")</f>
         <v/>
       </c>
-      <c r="T6">
+      <c r="T7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/kartor/A 2523-2024 karta.png", "A 2523-2024")</f>
         <v/>
       </c>
-      <c r="U6">
+      <c r="U7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/knärot/A 2523-2024 karta knärot.png", "A 2523-2024")</f>
         <v/>
       </c>
-      <c r="V6">
+      <c r="V7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomål/A 2523-2024 FSC-klagomål.docx", "A 2523-2024")</f>
         <v/>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomålsmail/A 2523-2024 FSC-klagomål mail.docx", "A 2523-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsyn/A 2523-2024 tillsynsbegäran.docx", "A 2523-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsynsmail/A 2523-2024 tillsynsbegäran mail.docx", "A 2523-2024")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/fåglar/A 2523-2024 prioriterade fågelarter.docx", "A 2523-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 38958-2024</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>45548</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>45885</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>UPPSALA</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>9</v>
-      </c>
-      <c r="P7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>20</v>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>Rosa jodskinn
-Laxporing
-Rostskinn
-Rynkskinn
-Järpe
-Rosenticka
-Tallticka
-Ullticka
-Vedtrappmossa
-Blodticka
-Brandticka
-Bronshjon
-Flagellkvastmossa
-Grön sköldmossa
-Grönpyrola
-Kattfotslav
-Vårärt
-Fläcknycklar
-Nattviol
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="S7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0380/artfynd/A 38958-2024 artfynd.xlsx", "A 38958-2024")</f>
-        <v/>
-      </c>
-      <c r="T7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0380/kartor/A 38958-2024 karta.png", "A 38958-2024")</f>
-        <v/>
-      </c>
-      <c r="V7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomål/A 38958-2024 FSC-klagomål.docx", "A 38958-2024")</f>
-        <v/>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomålsmail/A 38958-2024 FSC-klagomål mail.docx", "A 38958-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsyn/A 38958-2024 tillsynsbegäran.docx", "A 38958-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsynsmail/A 38958-2024 tillsynsbegäran mail.docx", "A 38958-2024")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0380/fåglar/A 38958-2024 prioriterade fågelarter.docx", "A 38958-2024")</f>
         <v/>
       </c>
     </row>
@@ -1252,7 +1254,7 @@
         <v>45082</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,7 +1363,7 @@
         <v>45728</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1476,7 @@
         <v>45715.38824074074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1589,7 @@
         <v>45882.73309027778</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1690,7 @@
         <v>45812.55136574074</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1791,7 @@
         <v>44971</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1885,7 +1887,7 @@
         <v>45086</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,7 +1990,7 @@
         <v>44222</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,7 +2090,7 @@
         <v>45202</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2196,7 +2198,7 @@
         <v>44623</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,7 +2298,7 @@
         <v>45803.55260416667</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2403,7 +2405,7 @@
         <v>45803.55737268519</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2510,7 +2512,7 @@
         <v>44575</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2608,7 +2610,7 @@
         <v>45758</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,14 +2701,14 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28450-2021</t>
+          <t>A 27281-2025</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>44356</v>
+        <v>45812</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2719,13 +2721,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>11.8</v>
+        <v>2.8</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
         <v>2</v>
@@ -2752,6 +2754,103 @@
         <v>9</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Vedtrappmossa
+Grön sköldmossa
+Svart trolldruva
+Vedticka
+Vårärt
+Kungsfågel
+Nattviol
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="S22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0380/artfynd/A 27281-2025 artfynd.xlsx", "A 27281-2025")</f>
+        <v/>
+      </c>
+      <c r="T22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0380/kartor/A 27281-2025 karta.png", "A 27281-2025")</f>
+        <v/>
+      </c>
+      <c r="V22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomål/A 27281-2025 FSC-klagomål.docx", "A 27281-2025")</f>
+        <v/>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomålsmail/A 27281-2025 FSC-klagomål mail.docx", "A 27281-2025")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsyn/A 27281-2025 tillsynsbegäran.docx", "A 27281-2025")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsynsmail/A 27281-2025 tillsynsbegäran mail.docx", "A 27281-2025")</f>
+        <v/>
+      </c>
+      <c r="Z22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0380/fåglar/A 27281-2025 prioriterade fågelarter.docx", "A 27281-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 28450-2021</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>44356</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>45886</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>UPPSALA</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9</v>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>Platt spretmossa
 Vedtrappmossa
@@ -2764,91 +2863,91 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="S22">
+      <c r="S23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/artfynd/A 28450-2021 artfynd.xlsx", "A 28450-2021")</f>
         <v/>
       </c>
-      <c r="T22">
+      <c r="T23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/kartor/A 28450-2021 karta.png", "A 28450-2021")</f>
         <v/>
       </c>
-      <c r="U22">
+      <c r="U23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/knärot/A 28450-2021 karta knärot.png", "A 28450-2021")</f>
         <v/>
       </c>
-      <c r="V22">
+      <c r="V23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomål/A 28450-2021 FSC-klagomål.docx", "A 28450-2021")</f>
         <v/>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomålsmail/A 28450-2021 FSC-klagomål mail.docx", "A 28450-2021")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsyn/A 28450-2021 tillsynsbegäran.docx", "A 28450-2021")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsynsmail/A 28450-2021 tillsynsbegäran mail.docx", "A 28450-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 46162-2023</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B24" s="1" t="n">
         <v>45196</v>
       </c>
-      <c r="C23" s="1" t="n">
-        <v>45885</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>UPPSALA</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
+      <c r="C24" s="1" t="n">
+        <v>45886</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>UPPSALA</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
         <v>5.5</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>1</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>4</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>3</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K24" t="n">
         <v>2</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>5</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P24" t="n">
         <v>2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q24" t="n">
         <v>9</v>
       </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Rynkskinn
@@ -2861,96 +2960,96 @@
 Vågbandad barkbock</t>
         </is>
       </c>
-      <c r="S23">
+      <c r="S24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/artfynd/A 46162-2023 artfynd.xlsx", "A 46162-2023")</f>
         <v/>
       </c>
-      <c r="T23">
+      <c r="T24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/kartor/A 46162-2023 karta.png", "A 46162-2023")</f>
         <v/>
       </c>
-      <c r="U23">
+      <c r="U24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/knärot/A 46162-2023 karta knärot.png", "A 46162-2023")</f>
         <v/>
       </c>
-      <c r="V23">
+      <c r="V24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomål/A 46162-2023 FSC-klagomål.docx", "A 46162-2023")</f>
         <v/>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomålsmail/A 46162-2023 FSC-klagomål mail.docx", "A 46162-2023")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsyn/A 46162-2023 tillsynsbegäran.docx", "A 46162-2023")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsynsmail/A 46162-2023 tillsynsbegäran mail.docx", "A 46162-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 66979-2020</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B25" s="1" t="n">
         <v>44180</v>
       </c>
-      <c r="C24" s="1" t="n">
-        <v>45885</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>UPPSALA</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="C25" s="1" t="n">
+        <v>45886</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>UPPSALA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="G25" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H25" t="n">
         <v>1</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I25" t="n">
         <v>4</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>2</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>3</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q25" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>Rynkskinn
 Tallticka
@@ -2962,87 +3061,87 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="S24">
+      <c r="S25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/artfynd/A 66979-2020 artfynd.xlsx", "A 66979-2020")</f>
         <v/>
       </c>
-      <c r="T24">
+      <c r="T25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/kartor/A 66979-2020 karta.png", "A 66979-2020")</f>
         <v/>
       </c>
-      <c r="V24">
+      <c r="V25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomål/A 66979-2020 FSC-klagomål.docx", "A 66979-2020")</f>
         <v/>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomålsmail/A 66979-2020 FSC-klagomål mail.docx", "A 66979-2020")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsyn/A 66979-2020 tillsynsbegäran.docx", "A 66979-2020")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsynsmail/A 66979-2020 tillsynsbegäran mail.docx", "A 66979-2020")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 21674-2024</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B26" s="1" t="n">
         <v>45442</v>
       </c>
-      <c r="C25" s="1" t="n">
-        <v>45885</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>UPPSALA</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
+      <c r="C26" s="1" t="n">
+        <v>45886</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>UPPSALA</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
         <v>0.9</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H26" t="n">
         <v>8</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>4</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L26" t="n">
         <v>2</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
         <v>7</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P26" t="n">
         <v>3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q26" t="n">
         <v>8</v>
       </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Tornseglare
@@ -3054,91 +3153,91 @@
 Sångsvan</t>
         </is>
       </c>
-      <c r="S25">
+      <c r="S26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/artfynd/A 21674-2024 artfynd.xlsx", "A 21674-2024")</f>
         <v/>
       </c>
-      <c r="T25">
+      <c r="T26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/kartor/A 21674-2024 karta.png", "A 21674-2024")</f>
         <v/>
       </c>
-      <c r="V25">
+      <c r="V26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomål/A 21674-2024 FSC-klagomål.docx", "A 21674-2024")</f>
         <v/>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomålsmail/A 21674-2024 FSC-klagomål mail.docx", "A 21674-2024")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsyn/A 21674-2024 tillsynsbegäran.docx", "A 21674-2024")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsynsmail/A 21674-2024 tillsynsbegäran mail.docx", "A 21674-2024")</f>
         <v/>
       </c>
-      <c r="Z25">
+      <c r="Z26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/fåglar/A 21674-2024 prioriterade fågelarter.docx", "A 21674-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>A 26460-2023</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B27" s="1" t="n">
         <v>45092</v>
       </c>
-      <c r="C26" s="1" t="n">
-        <v>45885</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>UPPSALA</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
+      <c r="C27" s="1" t="n">
+        <v>45886</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>UPPSALA</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
         <v>6.3</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H27" t="n">
         <v>1</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I27" t="n">
         <v>6</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
         <v>2</v>
       </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>8</v>
       </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>Blek fingersvamp
 Grön aspvedbock
@@ -3150,128 +3249,32 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="S26">
+      <c r="S27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/artfynd/A 26460-2023 artfynd.xlsx", "A 26460-2023")</f>
         <v/>
       </c>
-      <c r="T26">
+      <c r="T27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/kartor/A 26460-2023 karta.png", "A 26460-2023")</f>
         <v/>
       </c>
-      <c r="U26">
+      <c r="U27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/knärot/A 26460-2023 karta knärot.png", "A 26460-2023")</f>
         <v/>
       </c>
-      <c r="V26">
+      <c r="V27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomål/A 26460-2023 FSC-klagomål.docx", "A 26460-2023")</f>
         <v/>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomålsmail/A 26460-2023 FSC-klagomål mail.docx", "A 26460-2023")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsyn/A 26460-2023 tillsynsbegäran.docx", "A 26460-2023")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsynsmail/A 26460-2023 tillsynsbegäran mail.docx", "A 26460-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 27281-2025</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>45812</v>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>45885</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>UPPSALA</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H27" t="n">
-        <v>4</v>
-      </c>
-      <c r="I27" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>8</v>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Vedtrappmossa
-Grön sköldmossa
-Svart trolldruva
-Vedticka
-Kungsfågel
-Nattviol
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="S27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0380/artfynd/A 27281-2025 artfynd.xlsx", "A 27281-2025")</f>
-        <v/>
-      </c>
-      <c r="T27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0380/kartor/A 27281-2025 karta.png", "A 27281-2025")</f>
-        <v/>
-      </c>
-      <c r="V27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomål/A 27281-2025 FSC-klagomål.docx", "A 27281-2025")</f>
-        <v/>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0380/klagomålsmail/A 27281-2025 FSC-klagomål mail.docx", "A 27281-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsyn/A 27281-2025 tillsynsbegäran.docx", "A 27281-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0380/tillsynsmail/A 27281-2025 tillsynsbegäran mail.docx", "A 27281-2025")</f>
-        <v/>
-      </c>
-      <c r="Z27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0380/fåglar/A 27281-2025 prioriterade fågelarter.docx", "A 27281-2025")</f>
         <v/>
       </c>
     </row>
@@ -3285,7 +3288,7 @@
         <v>44497</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3385,7 +3388,7 @@
         <v>45799.60315972222</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3476,7 +3479,7 @@
         <v>45013</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3571,7 +3574,7 @@
         <v>44792</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3669,7 @@
         <v>45803.61035879629</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3769,7 +3772,7 @@
         <v>44532</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3863,7 +3866,7 @@
         <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3956,7 +3959,7 @@
         <v>44351</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4049,7 +4052,7 @@
         <v>45316</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4147,7 +4150,7 @@
         <v>44574</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4240,7 +4243,7 @@
         <v>45107</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4329,7 +4332,7 @@
         <v>45097</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4422,7 +4425,7 @@
         <v>45736.53695601852</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4516,7 +4519,7 @@
         <v>44719</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4604,7 +4607,7 @@
         <v>44664</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4692,7 +4695,7 @@
         <v>44974</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4780,7 +4783,7 @@
         <v>45442</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4873,7 +4876,7 @@
         <v>44659</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4966,7 +4969,7 @@
         <v>45841.64539351852</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,7 +5062,7 @@
         <v>44740</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5147,7 +5150,7 @@
         <v>45371</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5240,7 +5243,7 @@
         <v>44791</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5327,7 +5330,7 @@
         <v>45090</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5423,7 +5426,7 @@
         <v>45803.55535879629</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5523,7 +5526,7 @@
         <v>44684</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5610,7 +5613,7 @@
         <v>45831.55982638889</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5705,7 +5708,7 @@
         <v>44495</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5792,7 +5795,7 @@
         <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5879,7 +5882,7 @@
         <v>45222</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5965,7 +5968,7 @@
         <v>45694.55559027778</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6051,7 +6054,7 @@
         <v>45035.44672453704</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6146,7 +6149,7 @@
         <v>45474</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6240,7 +6243,7 @@
         <v>45666</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6326,7 +6329,7 @@
         <v>45715.38105324074</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6412,7 +6415,7 @@
         <v>45293</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6498,7 +6501,7 @@
         <v>44489</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6588,7 +6591,7 @@
         <v>45841.80690972223</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6683,7 +6686,7 @@
         <v>45762.62260416667</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6773,7 +6776,7 @@
         <v>45189</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6867,7 +6870,7 @@
         <v>45168.50667824074</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6962,7 +6965,7 @@
         <v>44967</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7048,7 +7051,7 @@
         <v>44614</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7133,7 +7136,7 @@
         <v>44379</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7218,7 +7221,7 @@
         <v>44651</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7308,7 +7311,7 @@
         <v>45694.49650462963</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7393,7 +7396,7 @@
         <v>45783</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7478,7 +7481,7 @@
         <v>45687</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7567,7 +7570,7 @@
         <v>45107</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7657,7 +7660,7 @@
         <v>45167</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7746,7 +7749,7 @@
         <v>44963</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7831,7 +7834,7 @@
         <v>45803.61554398148</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7921,7 +7924,7 @@
         <v>45805.41232638889</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8011,7 +8014,7 @@
         <v>45464</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8096,7 +8099,7 @@
         <v>44081</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8181,7 +8184,7 @@
         <v>45098</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8266,7 +8269,7 @@
         <v>44909</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8355,7 +8358,7 @@
         <v>44487</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8440,7 +8443,7 @@
         <v>45273</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8525,7 +8528,7 @@
         <v>45358</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8619,7 +8622,7 @@
         <v>45811.38710648148</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8709,7 +8712,7 @@
         <v>45679</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8799,7 +8802,7 @@
         <v>45818.60254629629</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8889,7 +8892,7 @@
         <v>45817.34614583333</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8979,7 +8982,7 @@
         <v>45763.52524305556</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9064,7 +9067,7 @@
         <v>45817</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9153,7 +9156,7 @@
         <v>45736.49902777778</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9243,7 +9246,7 @@
         <v>45820.84516203704</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9333,7 +9336,7 @@
         <v>44673.47858796296</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9422,7 +9425,7 @@
         <v>45336</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9512,7 +9515,7 @@
         <v>45874.69282407407</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9597,7 +9600,7 @@
         <v>45874</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9682,7 +9685,7 @@
         <v>45665</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9771,7 +9774,7 @@
         <v>44917.59298611111</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9861,7 +9864,7 @@
         <v>45314.55579861111</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9946,7 +9949,7 @@
         <v>44897</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10035,7 +10038,7 @@
         <v>44645</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10125,7 +10128,7 @@
         <v>44849</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10210,7 +10213,7 @@
         <v>44958</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10295,7 +10298,7 @@
         <v>44467</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10385,7 +10388,7 @@
         <v>45757.49934027778</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10470,7 +10473,7 @@
         <v>44917</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10560,7 +10563,7 @@
         <v>44855</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10650,7 +10653,7 @@
         <v>45107</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10744,7 +10747,7 @@
         <v>45762.57244212963</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10829,7 +10832,7 @@
         <v>45385</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10914,7 +10917,7 @@
         <v>44144</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10971,7 +10974,7 @@
         <v>44063</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11028,7 +11031,7 @@
         <v>44119</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11085,7 +11088,7 @@
         <v>44583.61803240741</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11147,7 +11150,7 @@
         <v>44602</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11204,7 +11207,7 @@
         <v>44602</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11261,7 +11264,7 @@
         <v>44517</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11318,7 +11321,7 @@
         <v>44567.81241898148</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11380,7 +11383,7 @@
         <v>44407</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11442,7 +11445,7 @@
         <v>44544</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11499,7 +11502,7 @@
         <v>44526</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11561,7 +11564,7 @@
         <v>44489</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11618,7 +11621,7 @@
         <v>44083</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11675,7 +11678,7 @@
         <v>44609.61430555556</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11732,7 +11735,7 @@
         <v>44583.62121527778</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11794,7 +11797,7 @@
         <v>44323.58961805556</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11851,7 +11854,7 @@
         <v>44299</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11913,7 +11916,7 @@
         <v>44714</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11970,7 +11973,7 @@
         <v>44491.50769675926</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12032,7 +12035,7 @@
         <v>44252</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12089,7 +12092,7 @@
         <v>44569.5340625</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12151,7 +12154,7 @@
         <v>44662.56783564815</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12213,7 +12216,7 @@
         <v>44486</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12270,7 +12273,7 @@
         <v>44603</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12327,7 +12330,7 @@
         <v>44659.70381944445</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12384,7 +12387,7 @@
         <v>44572.39640046296</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12446,7 +12449,7 @@
         <v>44230</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12503,7 +12506,7 @@
         <v>44494</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12565,7 +12568,7 @@
         <v>44700</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12622,7 +12625,7 @@
         <v>44839</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12679,7 +12682,7 @@
         <v>44784</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12736,7 +12739,7 @@
         <v>44369.65428240741</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12798,7 +12801,7 @@
         <v>44612</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12855,7 +12858,7 @@
         <v>44720</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12912,7 +12915,7 @@
         <v>44886</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12974,7 +12977,7 @@
         <v>44883.56321759259</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13036,7 +13039,7 @@
         <v>44598</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13093,7 +13096,7 @@
         <v>44314</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13155,7 +13158,7 @@
         <v>44610</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13217,7 +13220,7 @@
         <v>44865.43494212963</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13274,7 +13277,7 @@
         <v>44167</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13331,7 +13334,7 @@
         <v>44357</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13393,7 +13396,7 @@
         <v>44742</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13450,7 +13453,7 @@
         <v>44704</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13507,7 +13510,7 @@
         <v>44533.4678587963</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13564,7 +13567,7 @@
         <v>44764</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13626,7 +13629,7 @@
         <v>44453</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13683,7 +13686,7 @@
         <v>44297</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13740,7 +13743,7 @@
         <v>44153</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13802,7 +13805,7 @@
         <v>44349.49666666667</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13864,7 +13867,7 @@
         <v>44351</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13926,7 +13929,7 @@
         <v>44584.63190972222</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13988,7 +13991,7 @@
         <v>44609</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14050,7 +14053,7 @@
         <v>44490.64313657407</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14107,7 +14110,7 @@
         <v>44091</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14169,7 +14172,7 @@
         <v>44281.4499537037</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14231,7 +14234,7 @@
         <v>44610</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14293,7 +14296,7 @@
         <v>44335.52201388889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14350,7 +14353,7 @@
         <v>44512</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14407,7 +14410,7 @@
         <v>44740.68142361111</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14469,7 +14472,7 @@
         <v>44816</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14526,7 +14529,7 @@
         <v>44297</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14588,7 +14591,7 @@
         <v>44705.78475694444</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14645,7 +14648,7 @@
         <v>44705.83326388889</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14702,7 +14705,7 @@
         <v>44722.30703703704</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14764,7 +14767,7 @@
         <v>44692.87630787037</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14821,7 +14824,7 @@
         <v>44599.43265046296</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14878,7 +14881,7 @@
         <v>44543</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14940,7 +14943,7 @@
         <v>44685.6212037037</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15002,7 +15005,7 @@
         <v>44461</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15064,7 +15067,7 @@
         <v>44383</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15126,7 +15129,7 @@
         <v>44378.69857638889</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15188,7 +15191,7 @@
         <v>44865</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15245,7 +15248,7 @@
         <v>44461.73350694445</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15302,7 +15305,7 @@
         <v>44702.70721064815</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15359,7 +15362,7 @@
         <v>44442.35195601852</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15416,7 +15419,7 @@
         <v>44442</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15473,7 +15476,7 @@
         <v>44504.59193287037</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15535,7 +15538,7 @@
         <v>44643.51446759259</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15592,7 +15595,7 @@
         <v>44750.45800925926</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15649,7 +15652,7 @@
         <v>44076</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15706,7 +15709,7 @@
         <v>44593</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15763,7 +15766,7 @@
         <v>44733.43420138889</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15825,7 +15828,7 @@
         <v>44711</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15887,7 +15890,7 @@
         <v>44095</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15944,7 +15947,7 @@
         <v>44846</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16001,7 +16004,7 @@
         <v>44743</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16058,7 +16061,7 @@
         <v>44551.59704861111</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16115,7 +16118,7 @@
         <v>44134</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16177,7 +16180,7 @@
         <v>44446.47693287037</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16234,7 +16237,7 @@
         <v>44623.4572337963</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16296,7 +16299,7 @@
         <v>44571.44563657408</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16353,7 +16356,7 @@
         <v>44103</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16410,7 +16413,7 @@
         <v>44838.40635416667</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16467,7 +16470,7 @@
         <v>44479</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16524,7 +16527,7 @@
         <v>44491.54116898148</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16586,7 +16589,7 @@
         <v>44459</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16648,7 +16651,7 @@
         <v>44676</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16705,7 +16708,7 @@
         <v>44489</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16762,7 +16765,7 @@
         <v>44543.34697916666</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16819,7 +16822,7 @@
         <v>44476.61263888889</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16876,7 +16879,7 @@
         <v>44495</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16933,7 +16936,7 @@
         <v>44729</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16990,7 +16993,7 @@
         <v>44847.35622685185</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17047,7 +17050,7 @@
         <v>44160</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17109,7 +17112,7 @@
         <v>44705.84535879629</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17166,7 +17169,7 @@
         <v>44517</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17223,7 +17226,7 @@
         <v>44634</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17280,7 +17283,7 @@
         <v>44144</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17337,7 +17340,7 @@
         <v>44266.57917824074</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17399,7 +17402,7 @@
         <v>44294.37555555555</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17461,7 +17464,7 @@
         <v>44522.55518518519</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17518,7 +17521,7 @@
         <v>44886.58890046296</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17575,7 +17578,7 @@
         <v>44659.57912037037</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17637,7 +17640,7 @@
         <v>44791.38336805555</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17699,7 +17702,7 @@
         <v>44649</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17756,7 +17759,7 @@
         <v>44698.67151620371</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17818,7 +17821,7 @@
         <v>44623</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17880,7 +17883,7 @@
         <v>44762</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17942,7 +17945,7 @@
         <v>44277.65263888889</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17999,7 +18002,7 @@
         <v>44847</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18056,7 +18059,7 @@
         <v>44799.36359953704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18113,7 +18116,7 @@
         <v>44798</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18170,7 +18173,7 @@
         <v>44144</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18227,7 +18230,7 @@
         <v>44583.61555555555</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18289,7 +18292,7 @@
         <v>44575</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18346,7 +18349,7 @@
         <v>44750.678125</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18408,7 +18411,7 @@
         <v>44883</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18470,7 +18473,7 @@
         <v>44866</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18527,7 +18530,7 @@
         <v>45050.49392361111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18584,7 +18587,7 @@
         <v>44575.4366087963</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18646,7 +18649,7 @@
         <v>45119</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18703,7 +18706,7 @@
         <v>44328.57100694445</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18760,7 +18763,7 @@
         <v>44966</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18822,7 +18825,7 @@
         <v>44369</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18879,7 +18882,7 @@
         <v>45741.45114583334</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18936,7 +18939,7 @@
         <v>44501.71344907407</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18998,7 +19001,7 @@
         <v>45756.44024305556</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19055,7 +19058,7 @@
         <v>45756.50738425926</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19112,7 +19115,7 @@
         <v>45699.71063657408</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19169,7 +19172,7 @@
         <v>45729</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19226,7 +19229,7 @@
         <v>45763.52744212963</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19283,7 +19286,7 @@
         <v>45187.61136574074</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19345,7 +19348,7 @@
         <v>45743.50744212963</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19402,7 +19405,7 @@
         <v>45175.57060185185</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19459,7 +19462,7 @@
         <v>45644</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19516,7 +19519,7 @@
         <v>44847</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19573,7 +19576,7 @@
         <v>45695.59197916667</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19635,7 +19638,7 @@
         <v>45371.50738425926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19697,7 +19700,7 @@
         <v>44548</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19754,7 +19757,7 @@
         <v>44550.37994212963</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19816,7 +19819,7 @@
         <v>45259.52809027778</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19878,7 +19881,7 @@
         <v>44446</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19935,7 +19938,7 @@
         <v>45644.47723379629</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19992,7 +19995,7 @@
         <v>45679</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20049,7 +20052,7 @@
         <v>45006</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20106,7 +20109,7 @@
         <v>44980</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20163,7 +20166,7 @@
         <v>45096</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20220,7 +20223,7 @@
         <v>45337.58318287037</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20282,7 +20285,7 @@
         <v>45307</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20339,7 +20342,7 @@
         <v>45614</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20396,7 +20399,7 @@
         <v>45723</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20453,7 +20456,7 @@
         <v>44831</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20510,7 +20513,7 @@
         <v>45327</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20567,7 +20570,7 @@
         <v>45758</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20624,7 +20627,7 @@
         <v>45254.49552083333</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20681,7 +20684,7 @@
         <v>45208.46130787037</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20738,7 +20741,7 @@
         <v>45300</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20795,7 +20798,7 @@
         <v>44809.92752314815</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20852,7 +20855,7 @@
         <v>44810</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20909,7 +20912,7 @@
         <v>45611</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20966,7 +20969,7 @@
         <v>45670</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21028,7 +21031,7 @@
         <v>44371.49178240741</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21085,7 +21088,7 @@
         <v>45344.64759259259</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21147,7 +21150,7 @@
         <v>44859.36896990741</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21204,7 +21207,7 @@
         <v>44328</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21266,7 +21269,7 @@
         <v>45776.48275462963</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21328,7 +21331,7 @@
         <v>45776</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21385,7 +21388,7 @@
         <v>45107</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21442,7 +21445,7 @@
         <v>45107</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21499,7 +21502,7 @@
         <v>45107</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21556,7 +21559,7 @@
         <v>44832</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21613,7 +21616,7 @@
         <v>45344.69567129629</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21675,7 +21678,7 @@
         <v>44816</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21737,7 +21740,7 @@
         <v>45776.45263888889</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21799,7 +21802,7 @@
         <v>45107.55574074074</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21856,7 +21859,7 @@
         <v>45776.6415162037</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21918,7 +21921,7 @@
         <v>45133</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21975,7 +21978,7 @@
         <v>45096</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22032,7 +22035,7 @@
         <v>45098.62966435185</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22089,7 +22092,7 @@
         <v>45777.37119212963</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22151,7 +22154,7 @@
         <v>45152</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22213,7 +22216,7 @@
         <v>45777.34894675926</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22275,7 +22278,7 @@
         <v>45777.32731481481</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22337,7 +22340,7 @@
         <v>45777.52655092593</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22394,7 +22397,7 @@
         <v>45777</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22451,7 +22454,7 @@
         <v>45520</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22508,7 +22511,7 @@
         <v>44544</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22565,7 +22568,7 @@
         <v>45574</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22622,7 +22625,7 @@
         <v>44519</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22679,7 +22682,7 @@
         <v>45779.6665162037</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22741,7 +22744,7 @@
         <v>45335</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22803,7 +22806,7 @@
         <v>45293</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22860,7 +22863,7 @@
         <v>45779.65787037037</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22922,7 +22925,7 @@
         <v>45163.59913194444</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22979,7 +22982,7 @@
         <v>45096</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23036,7 +23039,7 @@
         <v>45779.49085648148</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23098,7 +23101,7 @@
         <v>45294.5666550926</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23160,7 +23163,7 @@
         <v>45783.61053240741</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23217,7 +23220,7 @@
         <v>44553</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23274,7 +23277,7 @@
         <v>45784.57266203704</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23336,7 +23339,7 @@
         <v>44569.49344907407</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23398,7 +23401,7 @@
         <v>45407.49721064815</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23455,7 +23458,7 @@
         <v>45784.80497685185</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23512,7 +23515,7 @@
         <v>45329</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23569,7 +23572,7 @@
         <v>45177.79766203704</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23631,7 +23634,7 @@
         <v>44603</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23688,7 +23691,7 @@
         <v>45161</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23745,7 +23748,7 @@
         <v>45558.42498842593</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23802,7 +23805,7 @@
         <v>45562</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23859,7 +23862,7 @@
         <v>45524</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23921,7 +23924,7 @@
         <v>45368.64787037037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23983,7 +23986,7 @@
         <v>44629.57741898148</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24045,7 +24048,7 @@
         <v>45468</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24102,7 +24105,7 @@
         <v>44569.69358796296</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24164,7 +24167,7 @@
         <v>45037</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24226,7 +24229,7 @@
         <v>45134.57021990741</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24288,7 +24291,7 @@
         <v>45684</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24345,7 +24348,7 @@
         <v>44533.46665509259</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24402,7 +24405,7 @@
         <v>45426</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24459,7 +24462,7 @@
         <v>45254</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24516,7 +24519,7 @@
         <v>45021.29524305555</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24578,7 +24581,7 @@
         <v>44395</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24635,7 +24638,7 @@
         <v>45583</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24697,7 +24700,7 @@
         <v>45583</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24759,7 +24762,7 @@
         <v>44535</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24816,7 +24819,7 @@
         <v>44637.35744212963</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24873,7 +24876,7 @@
         <v>45036</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24930,7 +24933,7 @@
         <v>45624</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24987,7 +24990,7 @@
         <v>45726</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25044,7 +25047,7 @@
         <v>45371.67368055556</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25101,7 +25104,7 @@
         <v>45790.51040509259</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25158,7 +25161,7 @@
         <v>45162</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25220,7 +25223,7 @@
         <v>45159.44694444445</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25277,7 +25280,7 @@
         <v>45091</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25339,7 +25342,7 @@
         <v>45790.44972222222</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25396,7 +25399,7 @@
         <v>45583.48449074074</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25458,7 +25461,7 @@
         <v>45145</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25515,7 +25518,7 @@
         <v>45584.60038194444</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25572,7 +25575,7 @@
         <v>45625.58501157408</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25634,7 +25637,7 @@
         <v>45790.51186342593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25691,7 +25694,7 @@
         <v>45201.62318287037</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25748,7 +25751,7 @@
         <v>45358</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25805,7 +25808,7 @@
         <v>44522</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25862,7 +25865,7 @@
         <v>44616</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25924,7 +25927,7 @@
         <v>45181.33571759259</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25981,7 +25984,7 @@
         <v>44516</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26038,7 +26041,7 @@
         <v>45177.56940972222</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26095,7 +26098,7 @@
         <v>45736.60863425926</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26157,7 +26160,7 @@
         <v>45525</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26214,7 +26217,7 @@
         <v>45335.66331018518</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26276,7 +26279,7 @@
         <v>45195.64807870371</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26333,7 +26336,7 @@
         <v>45838.42870370371</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26390,7 +26393,7 @@
         <v>45763</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26447,7 +26450,7 @@
         <v>45838.43577546296</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26504,7 +26507,7 @@
         <v>45636</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26561,7 +26564,7 @@
         <v>44277.65650462963</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26618,7 +26621,7 @@
         <v>45838.43185185185</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26675,7 +26678,7 @@
         <v>44095</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26732,7 +26735,7 @@
         <v>45644</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26789,7 +26792,7 @@
         <v>45159.45748842593</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26846,7 +26849,7 @@
         <v>45490</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26903,7 +26906,7 @@
         <v>44551.76711805556</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26965,7 +26968,7 @@
         <v>45643</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27022,7 +27025,7 @@
         <v>44678.3315625</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27084,7 +27087,7 @@
         <v>44610</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27146,7 +27149,7 @@
         <v>45615</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27203,7 +27206,7 @@
         <v>45638</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27260,7 +27263,7 @@
         <v>45439</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27322,7 +27325,7 @@
         <v>45429</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27379,7 +27382,7 @@
         <v>45644</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27436,7 +27439,7 @@
         <v>45188</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27498,7 +27501,7 @@
         <v>45797.45900462963</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27560,7 +27563,7 @@
         <v>44832.49594907407</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27617,7 +27620,7 @@
         <v>45798.42252314815</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27674,7 +27677,7 @@
         <v>45366.42888888889</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27736,7 +27739,7 @@
         <v>45798.41734953703</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27793,7 +27796,7 @@
         <v>45797.42777777778</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27850,7 +27853,7 @@
         <v>45338.49412037037</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27907,7 +27910,7 @@
         <v>45799.53348379629</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27969,7 +27972,7 @@
         <v>45693</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28026,7 +28029,7 @@
         <v>45721.35173611111</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28083,7 +28086,7 @@
         <v>45742.49414351852</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28140,7 +28143,7 @@
         <v>45799.53803240741</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28202,7 +28205,7 @@
         <v>45799.5421875</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28264,7 +28267,7 @@
         <v>45799.57714120371</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28321,7 +28324,7 @@
         <v>45799.64877314815</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28383,7 +28386,7 @@
         <v>45799.67806712963</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28445,7 +28448,7 @@
         <v>45733.62903935185</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28502,7 +28505,7 @@
         <v>45148</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28559,7 +28562,7 @@
         <v>45148</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28616,7 +28619,7 @@
         <v>45799.68190972223</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28678,7 +28681,7 @@
         <v>45148</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28735,7 +28738,7 @@
         <v>44588</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28792,7 +28795,7 @@
         <v>45799.675</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28854,7 +28857,7 @@
         <v>45799.53947916667</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28916,7 +28919,7 @@
         <v>45799.54104166666</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28978,7 +28981,7 @@
         <v>45737.40503472222</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29035,7 +29038,7 @@
         <v>45323.55914351852</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29097,7 +29100,7 @@
         <v>45799.65021990741</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29159,7 +29162,7 @@
         <v>45799.6527199074</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29221,7 +29224,7 @@
         <v>45194</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29283,7 +29286,7 @@
         <v>45799.43496527777</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29345,7 +29348,7 @@
         <v>45086.7037037037</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29407,7 +29410,7 @@
         <v>45744</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29464,7 +29467,7 @@
         <v>45601</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29526,7 +29529,7 @@
         <v>45341</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29583,7 +29586,7 @@
         <v>45608</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29640,7 +29643,7 @@
         <v>44594</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29697,7 +29700,7 @@
         <v>45638</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29754,7 +29757,7 @@
         <v>45327</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29811,7 +29814,7 @@
         <v>45803.36384259259</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29873,7 +29876,7 @@
         <v>45371</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29935,7 +29938,7 @@
         <v>45677</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29992,7 +29995,7 @@
         <v>45845.53202546296</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30049,7 +30052,7 @@
         <v>45190</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30106,7 +30109,7 @@
         <v>44629.42423611111</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30163,7 +30166,7 @@
         <v>45803.63395833333</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30220,7 +30223,7 @@
         <v>45762.49243055555</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30277,7 +30280,7 @@
         <v>45805.4094675926</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30339,7 +30342,7 @@
         <v>45351.54596064815</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30401,7 +30404,7 @@
         <v>45805.41010416667</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30463,7 +30466,7 @@
         <v>45684</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30520,7 +30523,7 @@
         <v>45054.9271875</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30577,7 +30580,7 @@
         <v>45805.41813657407</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30639,7 +30642,7 @@
         <v>45231.54601851852</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30696,7 +30699,7 @@
         <v>45805.43402777778</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30758,7 +30761,7 @@
         <v>45646.50211805556</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30815,7 +30818,7 @@
         <v>45173</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30872,7 +30875,7 @@
         <v>44594</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30929,7 +30932,7 @@
         <v>45194.60876157408</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30991,7 +30994,7 @@
         <v>45805.4255787037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31053,7 +31056,7 @@
         <v>45259</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31110,7 +31113,7 @@
         <v>44819.62</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31167,7 +31170,7 @@
         <v>45259</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31224,7 +31227,7 @@
         <v>45055</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31281,7 +31284,7 @@
         <v>45310.53418981482</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31343,7 +31346,7 @@
         <v>45182</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31400,7 +31403,7 @@
         <v>45182</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31457,7 +31460,7 @@
         <v>45511</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31514,7 +31517,7 @@
         <v>45849.49259259259</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31571,7 +31574,7 @@
         <v>45093.46706018518</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31633,7 +31636,7 @@
         <v>44130</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31690,7 +31693,7 @@
         <v>45851.62179398148</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31752,7 +31755,7 @@
         <v>45407.69575231482</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31809,7 +31812,7 @@
         <v>45810.44339120371</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31871,7 +31874,7 @@
         <v>45188.42052083334</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31928,7 +31931,7 @@
         <v>45809</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31990,7 +31993,7 @@
         <v>45852.39642361111</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32047,7 +32050,7 @@
         <v>44883</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32104,7 +32107,7 @@
         <v>45851.62018518519</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32166,7 +32169,7 @@
         <v>45231.62840277778</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32223,7 +32226,7 @@
         <v>44849</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32280,7 +32283,7 @@
         <v>45215.44233796297</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32337,7 +32340,7 @@
         <v>45677</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32394,7 +32397,7 @@
         <v>45695.8391550926</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32456,7 +32459,7 @@
         <v>45695.84078703704</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32518,7 +32521,7 @@
         <v>44209</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32575,7 +32578,7 @@
         <v>44894.57065972222</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32637,7 +32640,7 @@
         <v>45705.2953125</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32699,7 +32702,7 @@
         <v>45341</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32761,7 +32764,7 @@
         <v>45775.46377314815</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32823,7 +32826,7 @@
         <v>45851.60097222222</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32885,7 +32888,7 @@
         <v>45852.36871527778</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32942,7 +32945,7 @@
         <v>45341.63811342593</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32999,7 +33002,7 @@
         <v>45216</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33056,7 +33059,7 @@
         <v>45216</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33118,7 +33121,7 @@
         <v>45173</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33175,7 +33178,7 @@
         <v>45624</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33232,7 +33235,7 @@
         <v>45694</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33289,7 +33292,7 @@
         <v>45809</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33351,7 +33354,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33408,7 +33411,7 @@
         <v>45729</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33465,7 +33468,7 @@
         <v>45729</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33522,7 +33525,7 @@
         <v>45809</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33584,7 +33587,7 @@
         <v>45208.4350462963</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33641,7 +33644,7 @@
         <v>44935</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33698,7 +33701,7 @@
         <v>45614.65928240741</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33755,7 +33758,7 @@
         <v>45453.69339120371</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33817,7 +33820,7 @@
         <v>45705</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33874,7 +33877,7 @@
         <v>45852.68978009259</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33936,7 +33939,7 @@
         <v>45810.44299768518</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33998,7 +34001,7 @@
         <v>45852.72965277778</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34060,7 +34063,7 @@
         <v>45809</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34117,7 +34120,7 @@
         <v>45180.40255787037</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34179,7 +34182,7 @@
         <v>44504</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34236,7 +34239,7 @@
         <v>44614.59027777778</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34293,7 +34296,7 @@
         <v>45852</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34355,7 +34358,7 @@
         <v>44435.38657407407</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34412,7 +34415,7 @@
         <v>44602</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34469,7 +34472,7 @@
         <v>45853.76976851852</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34526,7 +34529,7 @@
         <v>45854.44017361111</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34588,7 +34591,7 @@
         <v>44679.68706018518</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34650,7 +34653,7 @@
         <v>45812.48032407407</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34707,7 +34710,7 @@
         <v>45149.56928240741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34769,7 +34772,7 @@
         <v>45181.36815972222</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34826,7 +34829,7 @@
         <v>45810.45960648148</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34888,7 +34891,7 @@
         <v>44977</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34945,7 +34948,7 @@
         <v>44679.66694444444</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35007,7 +35010,7 @@
         <v>44223</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35064,7 +35067,7 @@
         <v>45856.34959490741</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35126,7 +35129,7 @@
         <v>45721.34715277778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35183,7 +35186,7 @@
         <v>45814</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35240,7 +35243,7 @@
         <v>45813</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35297,7 +35300,7 @@
         <v>45182</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35354,7 +35357,7 @@
         <v>45182</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35411,7 +35414,7 @@
         <v>45813.46034722222</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35468,7 +35471,7 @@
         <v>44131</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35530,7 +35533,7 @@
         <v>45856.34034722222</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35592,7 +35595,7 @@
         <v>45856.34231481481</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35654,7 +35657,7 @@
         <v>44624.64538194444</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35716,7 +35719,7 @@
         <v>45856.36153935185</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35778,7 +35781,7 @@
         <v>45618.71140046296</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35835,7 +35838,7 @@
         <v>44637.56178240741</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35897,7 +35900,7 @@
         <v>45175</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35959,7 +35962,7 @@
         <v>45453</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36016,7 +36019,7 @@
         <v>44140</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36073,7 +36076,7 @@
         <v>45524</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36135,7 +36138,7 @@
         <v>44109</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36192,7 +36195,7 @@
         <v>44967</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36249,7 +36252,7 @@
         <v>45818.57910879629</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36311,7 +36314,7 @@
         <v>44909</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36368,7 +36371,7 @@
         <v>44599.42277777778</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36425,7 +36428,7 @@
         <v>44593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36487,7 +36490,7 @@
         <v>44593.61355324074</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36549,7 +36552,7 @@
         <v>45344</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36611,7 +36614,7 @@
         <v>44946</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36668,7 +36671,7 @@
         <v>45425.94947916667</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36725,7 +36728,7 @@
         <v>45699</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36782,7 +36785,7 @@
         <v>45664</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36844,7 +36847,7 @@
         <v>45194.63479166666</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36901,7 +36904,7 @@
         <v>45152</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36963,7 +36966,7 @@
         <v>45694.49037037037</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37020,7 +37023,7 @@
         <v>45817</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37077,7 +37080,7 @@
         <v>44699</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37139,7 +37142,7 @@
         <v>44426</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37196,7 +37199,7 @@
         <v>44106</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37253,7 +37256,7 @@
         <v>44608</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37315,7 +37318,7 @@
         <v>45614</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37372,7 +37375,7 @@
         <v>45202.4997337963</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37434,7 +37437,7 @@
         <v>44222</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37491,7 +37494,7 @@
         <v>45225.46480324074</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37548,7 +37551,7 @@
         <v>45820</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37605,7 +37608,7 @@
         <v>45820</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37662,7 +37665,7 @@
         <v>45131</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37719,7 +37722,7 @@
         <v>45817</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37781,7 +37784,7 @@
         <v>45820</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37838,7 +37841,7 @@
         <v>45259</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37900,7 +37903,7 @@
         <v>45236.47697916667</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37957,7 +37960,7 @@
         <v>45863.44648148148</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38014,7 +38017,7 @@
         <v>45821.45905092593</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38071,7 +38074,7 @@
         <v>45824.43798611111</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38133,7 +38136,7 @@
         <v>45821.44101851852</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38190,7 +38193,7 @@
         <v>45863.45355324074</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38247,7 +38250,7 @@
         <v>45299</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38304,7 +38307,7 @@
         <v>45267</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38366,7 +38369,7 @@
         <v>45552</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38423,7 +38426,7 @@
         <v>45236</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38480,7 +38483,7 @@
         <v>44960</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38537,7 +38540,7 @@
         <v>44960.66233796296</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38594,7 +38597,7 @@
         <v>45825.44482638889</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38656,7 +38659,7 @@
         <v>45726</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38713,7 +38716,7 @@
         <v>45825.49060185185</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38775,7 +38778,7 @@
         <v>45511</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38837,7 +38840,7 @@
         <v>45827.62096064815</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38894,7 +38897,7 @@
         <v>45852.67366898148</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38956,7 +38959,7 @@
         <v>45827.64092592592</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39013,7 +39016,7 @@
         <v>45719.42197916667</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39075,7 +39078,7 @@
         <v>45719.43646990741</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39137,7 +39140,7 @@
         <v>44553</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39194,7 +39197,7 @@
         <v>45827.46288194445</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39256,7 +39259,7 @@
         <v>45874.705</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39313,7 +39316,7 @@
         <v>45831.42365740741</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39370,7 +39373,7 @@
         <v>45831.42616898148</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39427,7 +39430,7 @@
         <v>44799.36695601852</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39484,7 +39487,7 @@
         <v>45831.73</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39546,7 +39549,7 @@
         <v>44126</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39603,7 +39606,7 @@
         <v>45231</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39660,7 +39663,7 @@
         <v>44575</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39717,7 +39720,7 @@
         <v>45254</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39774,7 +39777,7 @@
         <v>45321</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39831,7 +39834,7 @@
         <v>45097</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39888,7 +39891,7 @@
         <v>45317</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39945,7 +39948,7 @@
         <v>45361.57299768519</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40007,7 +40010,7 @@
         <v>44200</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40064,7 +40067,7 @@
         <v>45831.46731481481</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40121,7 +40124,7 @@
         <v>45832.35590277778</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -40183,7 +40186,7 @@
         <v>44893</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40240,7 +40243,7 @@
         <v>45831.40671296296</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40297,7 +40300,7 @@
         <v>45369</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40354,7 +40357,7 @@
         <v>44155</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40411,7 +40414,7 @@
         <v>45164.82913194445</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40473,7 +40476,7 @@
         <v>44904</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40535,7 +40538,7 @@
         <v>45351.48662037037</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40592,7 +40595,7 @@
         <v>45832.35545138889</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40654,7 +40657,7 @@
         <v>44659</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40716,7 +40719,7 @@
         <v>45707</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40778,7 +40781,7 @@
         <v>44930</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40835,7 +40838,7 @@
         <v>45831.72686342592</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40897,7 +40900,7 @@
         <v>45310</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40954,7 +40957,7 @@
         <v>44438</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41016,7 +41019,7 @@
         <v>45874</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41073,7 +41076,7 @@
         <v>45876</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41130,7 +41133,7 @@
         <v>45358</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -41192,7 +41195,7 @@
         <v>45876</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41249,7 +41252,7 @@
         <v>45091.69766203704</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41306,7 +41309,7 @@
         <v>45751.32001157408</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41363,7 +41366,7 @@
         <v>45379</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41420,7 +41423,7 @@
         <v>44912.29869212963</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41477,7 +41480,7 @@
         <v>44614.69730324074</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41539,7 +41542,7 @@
         <v>45691</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41601,7 +41604,7 @@
         <v>45880.68200231482</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41658,7 +41661,7 @@
         <v>45443</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41720,7 +41723,7 @@
         <v>45835.62752314815</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41782,7 +41785,7 @@
         <v>45736.45847222222</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41844,7 +41847,7 @@
         <v>45880.32907407408</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41901,7 +41904,7 @@
         <v>45693</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41958,7 +41961,7 @@
         <v>44967.55960648148</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42015,7 +42018,7 @@
         <v>45867.58056712963</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42072,7 +42075,7 @@
         <v>45523</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42129,7 +42132,7 @@
         <v>44788</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -42186,7 +42189,7 @@
         <v>45761.47540509259</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42243,7 +42246,7 @@
         <v>45761.47748842592</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42300,7 +42303,7 @@
         <v>45880.43200231482</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42357,7 +42360,7 @@
         <v>45877.57847222222</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42414,7 +42417,7 @@
         <v>45877.62969907407</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42471,7 +42474,7 @@
         <v>45880.34064814815</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42528,7 +42531,7 @@
         <v>45693</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42585,7 +42588,7 @@
         <v>45881.45898148148</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42642,7 +42645,7 @@
         <v>45721.60894675926</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42699,7 +42702,7 @@
         <v>44817</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42756,7 +42759,7 @@
         <v>45254</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42813,7 +42816,7 @@
         <v>45839</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42870,7 +42873,7 @@
         <v>45839</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42947,7 +42950,7 @@
         <v>45881.44938657407</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43004,7 +43007,7 @@
         <v>45882.47538194444</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43061,7 +43064,7 @@
         <v>45216.39040509259</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43118,7 +43121,7 @@
         <v>45882.37202546297</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -43175,7 +43178,7 @@
         <v>45202</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43237,7 +43240,7 @@
         <v>45839</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43294,7 +43297,7 @@
         <v>45821.31292824074</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43351,7 +43354,7 @@
         <v>45840.68518518518</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43408,7 +43411,7 @@
         <v>45840</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43465,7 +43468,7 @@
         <v>45882.52290509259</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43522,7 +43525,7 @@
         <v>45478</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43584,7 +43587,7 @@
         <v>45841.81555555556</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43646,7 +43649,7 @@
         <v>45841.5847337963</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43703,7 +43706,7 @@
         <v>45599</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43760,7 +43763,7 @@
         <v>45642.63524305556</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43817,7 +43820,7 @@
         <v>44512</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43874,7 +43877,7 @@
         <v>45646.61892361111</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43931,7 +43934,7 @@
         <v>44159</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43993,7 +43996,7 @@
         <v>44984.69216435185</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44055,7 +44058,7 @@
         <v>44379.56163194445</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44112,7 +44115,7 @@
         <v>45390</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -44169,7 +44172,7 @@
         <v>44617.48311342593</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44226,7 +44229,7 @@
         <v>44245</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44283,7 +44286,7 @@
         <v>45391.37361111111</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44340,7 +44343,7 @@
         <v>45679</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44402,7 +44405,7 @@
         <v>44977</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44464,7 +44467,7 @@
         <v>44063</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44521,7 +44524,7 @@
         <v>45842.74049768518</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44578,7 +44581,7 @@
         <v>45446.78256944445</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44640,7 +44643,7 @@
         <v>45520</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44697,7 +44700,7 @@
         <v>44581.60254629629</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44759,7 +44762,7 @@
         <v>44568.67040509259</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44821,7 +44824,7 @@
         <v>45769.6009375</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44878,7 +44881,7 @@
         <v>45698.65606481482</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44935,7 +44938,7 @@
         <v>45693</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44992,7 +44995,7 @@
         <v>44123</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45049,7 +45052,7 @@
         <v>44908.425625</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45106,7 +45109,7 @@
         <v>45426</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45163,7 +45166,7 @@
         <v>44993</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45220,7 +45223,7 @@
         <v>44358.63490740741</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45277,7 +45280,7 @@
         <v>44733</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45334,7 +45337,7 @@
         <v>44949.4708912037</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45391,7 +45394,7 @@
         <v>44403.29719907408</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45453,7 +45456,7 @@
         <v>44946.43564814814</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45510,7 +45513,7 @@
         <v>45033</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45567,7 +45570,7 @@
         <v>44994</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45624,7 +45627,7 @@
         <v>44531</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45681,7 +45684,7 @@
         <v>44665</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45743,7 +45746,7 @@
         <v>45068.58563657408</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45800,7 +45803,7 @@
         <v>45426.34148148148</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45857,7 +45860,7 @@
         <v>44105</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45919,7 +45922,7 @@
         <v>44209</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45976,7 +45979,7 @@
         <v>45363.54878472222</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46038,7 +46041,7 @@
         <v>44273</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46095,7 +46098,7 @@
         <v>44967.80034722222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46152,7 +46155,7 @@
         <v>44967</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46209,7 +46212,7 @@
         <v>44960.65061342593</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46266,7 +46269,7 @@
         <v>44960</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46323,7 +46326,7 @@
         <v>44929</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46380,7 +46383,7 @@
         <v>44593.64863425926</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46442,7 +46445,7 @@
         <v>44928</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46504,7 +46507,7 @@
         <v>45730.43966435185</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46566,7 +46569,7 @@
         <v>45614</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46628,7 +46631,7 @@
         <v>45552</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46685,7 +46688,7 @@
         <v>45121</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46747,7 +46750,7 @@
         <v>44819.50233796296</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46809,7 +46812,7 @@
         <v>45583</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46871,7 +46874,7 @@
         <v>44616</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46928,7 +46931,7 @@
         <v>44886</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46985,7 +46988,7 @@
         <v>45042</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47042,7 +47045,7 @@
         <v>44608</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47099,7 +47102,7 @@
         <v>44909.51885416666</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47161,7 +47164,7 @@
         <v>44560</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47218,7 +47221,7 @@
         <v>45600</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47280,7 +47283,7 @@
         <v>45107.53688657407</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47337,7 +47340,7 @@
         <v>45456.59535879629</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47394,7 +47397,7 @@
         <v>44600</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47456,7 +47459,7 @@
         <v>44623.41775462963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47518,7 +47521,7 @@
         <v>44623.5571875</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47580,7 +47583,7 @@
         <v>45167.3721412037</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47637,7 +47640,7 @@
         <v>45089</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47694,7 +47697,7 @@
         <v>44965</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47751,7 +47754,7 @@
         <v>44965</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47808,7 +47811,7 @@
         <v>45308.63298611111</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47865,7 +47868,7 @@
         <v>45212.34997685185</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47922,7 +47925,7 @@
         <v>44886.5928125</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47979,7 +47982,7 @@
         <v>45293</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48036,7 +48039,7 @@
         <v>45181.58055555556</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48098,7 +48101,7 @@
         <v>45670</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48160,7 +48163,7 @@
         <v>45520</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48217,7 +48220,7 @@
         <v>44742</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48279,7 +48282,7 @@
         <v>45231</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48336,7 +48339,7 @@
         <v>45341</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48398,7 +48401,7 @@
         <v>45474.41729166666</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48460,7 +48463,7 @@
         <v>45594</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48522,7 +48525,7 @@
         <v>45644.62677083333</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48579,7 +48582,7 @@
         <v>45300.55028935185</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48636,7 +48639,7 @@
         <v>45642</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48698,7 +48701,7 @@
         <v>45097</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48755,7 +48758,7 @@
         <v>45695.83655092592</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48817,7 +48820,7 @@
         <v>45707</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48879,7 +48882,7 @@
         <v>44969</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48936,7 +48939,7 @@
         <v>45645</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48998,7 +49001,7 @@
         <v>44944</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49055,7 +49058,7 @@
         <v>45113</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49112,7 +49115,7 @@
         <v>45113.80170138889</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49169,7 +49172,7 @@
         <v>45601</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49226,7 +49229,7 @@
         <v>45154.35092592592</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49283,7 +49286,7 @@
         <v>44652</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49340,7 +49343,7 @@
         <v>45678</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49397,7 +49400,7 @@
         <v>44679</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49454,7 +49457,7 @@
         <v>45757.6997337963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49511,7 +49514,7 @@
         <v>45757</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49568,7 +49571,7 @@
         <v>45631.44464120371</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49625,7 +49628,7 @@
         <v>45656</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49687,7 +49690,7 @@
         <v>45694</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49744,7 +49747,7 @@
         <v>45693</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49801,7 +49804,7 @@
         <v>44806</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49858,7 +49861,7 @@
         <v>45719.4094212963</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49920,7 +49923,7 @@
         <v>45049.66025462963</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49977,7 +49980,7 @@
         <v>45719.43872685185</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50039,7 +50042,7 @@
         <v>44644.37548611111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50101,7 +50104,7 @@
         <v>45679</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50158,7 +50161,7 @@
         <v>44574</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50215,7 +50218,7 @@
         <v>44645.39157407408</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50277,7 +50280,7 @@
         <v>44497.4666087963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50334,7 +50337,7 @@
         <v>44400.6750925926</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50396,7 +50399,7 @@
         <v>44403.3119212963</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50458,7 +50461,7 @@
         <v>45152</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50515,7 +50518,7 @@
         <v>44964.65261574074</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50572,7 +50575,7 @@
         <v>44599.44832175926</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50629,7 +50632,7 @@
         <v>44980</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50686,7 +50689,7 @@
         <v>45481.83684027778</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50743,7 +50746,7 @@
         <v>45638</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50800,7 +50803,7 @@
         <v>45000.44666666666</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50857,7 +50860,7 @@
         <v>44508.44033564815</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50919,7 +50922,7 @@
         <v>44519.64902777778</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50976,7 +50979,7 @@
         <v>45762.61341435185</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51033,7 +51036,7 @@
         <v>45713.44519675926</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51090,7 +51093,7 @@
         <v>45442</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51147,7 +51150,7 @@
         <v>45656</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51209,7 +51212,7 @@
         <v>45327.61831018519</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51266,7 +51269,7 @@
         <v>45098.63572916666</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51323,7 +51326,7 @@
         <v>45352</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51380,7 +51383,7 @@
         <v>45694</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51437,7 +51440,7 @@
         <v>44820.47935185185</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51499,7 +51502,7 @@
         <v>44944</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51556,7 +51559,7 @@
         <v>45065.43013888889</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51613,7 +51616,7 @@
         <v>45637</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51675,7 +51678,7 @@
         <v>44532</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51732,7 +51735,7 @@
         <v>45266</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51789,7 +51792,7 @@
         <v>45691</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51846,7 +51849,7 @@
         <v>44872</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51903,7 +51906,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51960,7 +51963,7 @@
         <v>45691</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52017,7 +52020,7 @@
         <v>45719.43755787037</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52079,7 +52082,7 @@
         <v>45054.95675925926</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52136,7 +52139,7 @@
         <v>45513.51815972223</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52198,7 +52201,7 @@
         <v>45772.77188657408</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52255,7 +52258,7 @@
         <v>45617.59006944444</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52312,7 +52315,7 @@
         <v>45049</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52369,7 +52372,7 @@
         <v>44560</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52426,7 +52429,7 @@
         <v>45336.53908564815</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52483,7 +52486,7 @@
         <v>45047.31793981481</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52540,7 +52543,7 @@
         <v>45614.67020833334</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52597,7 +52600,7 @@
         <v>44888</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52659,7 +52662,7 @@
         <v>44207</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52721,7 +52724,7 @@
         <v>45127</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52778,7 +52781,7 @@
         <v>44379.5745949074</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52835,7 +52838,7 @@
         <v>45770.61341435185</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52897,7 +52900,7 @@
         <v>45677.39440972222</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52954,7 +52957,7 @@
         <v>45048.55349537037</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53011,7 +53014,7 @@
         <v>45169</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53073,7 +53076,7 @@
         <v>45244.52202546296</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53135,7 +53138,7 @@
         <v>44848</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53192,7 +53195,7 @@
         <v>45435.34778935185</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53254,7 +53257,7 @@
         <v>45259</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53311,7 +53314,7 @@
         <v>45763</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53368,7 +53371,7 @@
         <v>45548.42854166667</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53425,7 +53428,7 @@
         <v>45223</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53482,7 +53485,7 @@
         <v>44420</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53539,7 +53542,7 @@
         <v>44993</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53596,7 +53599,7 @@
         <v>45714.55368055555</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53653,7 +53656,7 @@
         <v>44532</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53710,7 +53713,7 @@
         <v>45190</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53767,7 +53770,7 @@
         <v>45723.63290509259</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53824,7 +53827,7 @@
         <v>45763.52995370371</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53881,7 +53884,7 @@
         <v>44531</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53938,7 +53941,7 @@
         <v>44977</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53995,7 +53998,7 @@
         <v>45336.54270833333</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54052,7 +54055,7 @@
         <v>44532</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54109,7 +54112,7 @@
         <v>45110</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54166,7 +54169,7 @@
         <v>45194</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54228,7 +54231,7 @@
         <v>45757.67611111111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54285,7 +54288,7 @@
         <v>45078</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54347,7 +54350,7 @@
         <v>45474</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54404,7 +54407,7 @@
         <v>44378.56137731481</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54461,7 +54464,7 @@
         <v>45611</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54518,7 +54521,7 @@
         <v>44123</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54575,7 +54578,7 @@
         <v>44139</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54632,7 +54635,7 @@
         <v>45300.55680555556</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54689,7 +54692,7 @@
         <v>45589</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54746,7 +54749,7 @@
         <v>45589</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54803,7 +54806,7 @@
         <v>44609.60171296296</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54865,7 +54868,7 @@
         <v>45202</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54922,7 +54925,7 @@
         <v>44503</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -54979,7 +54982,7 @@
         <v>44624.35083333333</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55041,7 +55044,7 @@
         <v>45456.58491898148</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55098,7 +55101,7 @@
         <v>44897</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55155,7 +55158,7 @@
         <v>45638</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55212,7 +55215,7 @@
         <v>44900.54711805555</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55269,7 +55272,7 @@
         <v>45580</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55326,7 +55329,7 @@
         <v>44944</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55383,7 +55386,7 @@
         <v>45729</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55440,7 +55443,7 @@
         <v>45729</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55497,7 +55500,7 @@
         <v>45555.5727662037</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55554,7 +55557,7 @@
         <v>45295</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55616,7 +55619,7 @@
         <v>44168.55746527778</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55673,7 +55676,7 @@
         <v>45327</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55730,7 +55733,7 @@
         <v>45014</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55787,7 +55790,7 @@
         <v>45222</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55844,7 +55847,7 @@
         <v>44593</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55901,7 +55904,7 @@
         <v>45685.5778125</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55958,7 +55961,7 @@
         <v>45695.59805555556</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56020,7 +56023,7 @@
         <v>45460</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56082,7 +56085,7 @@
         <v>45345.56</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56139,7 +56142,7 @@
         <v>44914.67600694444</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56196,7 +56199,7 @@
         <v>45554</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56253,7 +56256,7 @@
         <v>45061</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56310,7 +56313,7 @@
         <v>44210</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56367,7 +56370,7 @@
         <v>45757</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56424,7 +56427,7 @@
         <v>45583.47836805556</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56486,7 +56489,7 @@
         <v>44912</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56543,7 +56546,7 @@
         <v>44816</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56600,7 +56603,7 @@
         <v>45763.6503125</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56657,7 +56660,7 @@
         <v>44967.78984953704</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56714,7 +56717,7 @@
         <v>45316</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56776,7 +56779,7 @@
         <v>45317</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56833,7 +56836,7 @@
         <v>45075.51982638889</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56890,7 +56893,7 @@
         <v>45349</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56947,7 +56950,7 @@
         <v>45307</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -57004,7 +57007,7 @@
         <v>45104.6828125</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57061,7 +57064,7 @@
         <v>45720.60410879629</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57118,7 +57121,7 @@
         <v>45642</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57180,7 +57183,7 @@
         <v>45699</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57237,7 +57240,7 @@
         <v>45733.63099537037</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57294,7 +57297,7 @@
         <v>45426.61569444444</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57351,7 +57354,7 @@
         <v>45478.60802083334</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57413,7 +57416,7 @@
         <v>45719.40723379629</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57475,7 +57478,7 @@
         <v>45154.34931712963</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -567,7 +567,7 @@
         <v>45603</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>45812.47355324074</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>45827.64737268518</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>45548</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>44377</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>45313</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45082</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45728</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>45715.38824074074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>45882.73309027778</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45812.55136574074</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>44971</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>45086</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>44222</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45202</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>44623</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>45803.55260416667</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45803.55737268519</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>44575</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45758</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>45812</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>44356</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>45196</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>44180</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>45442</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>45092</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44497</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>45799.60315972222</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45013</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>44792</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45803.61035879629</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>44532</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>44351</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>45316</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>44574</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>45107</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45097</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45736.53695601852</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>44719</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44664</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>44974</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>45442</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>44659</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>45841.64539351852</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>44740</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>45371</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>44791</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>45090</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>45803.55535879629</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>44684</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>45831.55982638889</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>44495</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45222</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>45694.55559027778</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>45035.44672453704</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>45474</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>45666</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>45715.38105324074</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45293</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>44489</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45841.80690972223</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>45762.62260416667</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>45189</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>45168.50667824074</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>44967</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>44614</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44379</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>44651</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>45694.49650462963</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>45783</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45687</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>45107</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45167</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>44963</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>45803.61554398148</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>45805.41232638889</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45464</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>44081</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>45098</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44909</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44487</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>45273</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>45358</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>45811.38710648148</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>45679</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>45818.60254629629</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>45817.34614583333</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>45763.52524305556</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>45817</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>45736.49902777778</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>45820.84516203704</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>44673.47858796296</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>45336</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>45874.69282407407</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>45874</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>45665</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>44917.59298611111</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45314.55579861111</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>44897</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>44645</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>44849</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>44958</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44467</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>45757.49934027778</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44917</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>44855</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>45107</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>45762.57244212963</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45385</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>44144</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>44063</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>44119</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44583.61803240741</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>44602</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>44602</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>44517</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44567.81241898148</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44407</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44544</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>44526</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>44489</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44083</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>44609.61430555556</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44583.62121527778</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>44323.58961805556</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>44299</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>44714</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44491.50769675926</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44252</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>44569.5340625</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44662.56783564815</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>44486</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>44603</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44659.70381944445</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>44572.39640046296</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>44230</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>44494</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44700</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44839</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44784</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44369.65428240741</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44612</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>44720</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>44886</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>44883.56321759259</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>44598</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>44314</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>44610</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>44865.43494212963</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>44167</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44357</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>44742</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>44704</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>44533.4678587963</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>44764</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44453</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>44297</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>44153</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>44349.49666666667</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>44351</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>44584.63190972222</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>44609</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>44490.64313657407</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>44091</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>44281.4499537037</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>44610</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44335.52201388889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>44512</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>44740.68142361111</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>44816</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>44297</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>44705.78475694444</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>44705.83326388889</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>44722.30703703704</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>44692.87630787037</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>44599.43265046296</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>44543</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>44685.6212037037</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>44461</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>44383</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>44378.69857638889</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44865</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>44461.73350694445</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44702.70721064815</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>44442.35195601852</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>44442</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>44504.59193287037</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>44643.51446759259</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>44750.45800925926</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44076</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>44593</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44733.43420138889</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44711</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>44095</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>44846</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>44743</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>44551.59704861111</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>44134</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>44446.47693287037</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>44623.4572337963</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>44571.44563657408</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44103</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>44838.40635416667</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>44479</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>44491.54116898148</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44459</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>44676</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>44489</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>44543.34697916666</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>44476.61263888889</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>44495</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>44729</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44847.35622685185</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>44160</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>44705.84535879629</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>44517</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>44634</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>44144</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>44266.57917824074</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>44294.37555555555</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>44522.55518518519</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>44886.58890046296</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44659.57912037037</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44791.38336805555</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44649</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44698.67151620371</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>44623</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>44762</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44277.65263888889</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>44847</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44799.36359953704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>44798</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>44144</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>44583.61555555555</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>44575</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>44750.678125</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>44883</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>44866</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>45050.49392361111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>44575.4366087963</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>45119</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>44328.57100694445</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>44966</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>44369</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>45741.45114583334</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44501.71344907407</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45756.44024305556</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>45756.50738425926</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45699.71063657408</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>45729</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>45763.52744212963</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45187.61136574074</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45743.50744212963</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>45175.57060185185</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>45644</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>44847</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45695.59197916667</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45371.50738425926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44548</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>44550.37994212963</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45259.52809027778</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>44446</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>45644.47723379629</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>45679</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>45006</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44980</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>45096</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45337.58318287037</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>45307</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>45614</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45723</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44831</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>45327</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>45758</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>45254.49552083333</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>45208.46130787037</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45300</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44809.92752314815</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>44810</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>45611</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>45670</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44371.49178240741</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>45344.64759259259</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>44859.36896990741</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>44328</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>45776.48275462963</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45776</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>45107</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>45107</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45107</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>44832</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45344.69567129629</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>44816</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45776.45263888889</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>45107.55574074074</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45776.6415162037</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>45133</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>45096</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>45098.62966435185</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>45777.37119212963</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45152</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>45777.34894675926</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45777.32731481481</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>45777.52655092593</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>45777</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45520</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44544</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>45574</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44519</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>45779.6665162037</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>45335</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>45293</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45779.65787037037</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45163.59913194444</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>45096</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>45779.49085648148</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45294.5666550926</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>45783.61053240741</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44553</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45784.57266203704</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>44569.49344907407</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>45407.49721064815</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45784.80497685185</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>45329</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45177.79766203704</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>44603</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45161</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45558.42498842593</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>45562</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>45524</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>45368.64787037037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>44629.57741898148</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>45468</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>44569.69358796296</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>45037</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>45134.57021990741</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45684</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>44533.46665509259</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>45426</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>45254</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45021.29524305555</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>44395</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>45583</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45583</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>44535</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>44637.35744212963</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45036</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45624</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>45726</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>45371.67368055556</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45790.51040509259</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45162</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45159.44694444445</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>45091</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>45790.44972222222</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>45583.48449074074</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>45145</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>45584.60038194444</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25575,7 +25575,7 @@
         <v>45625.58501157408</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45790.51186342593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>45201.62318287037</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>45358</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>44522</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>44616</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45181.33571759259</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>44516</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>45177.56940972222</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>45736.60863425926</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26160,7 +26160,7 @@
         <v>45525</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>45335.66331018518</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>45195.64807870371</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>45838.42870370371</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>45763</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>45838.43577546296</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>45636</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44277.65650462963</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>45838.43185185185</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44095</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45644</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45159.45748842593</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>45490</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44551.76711805556</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26968,7 +26968,7 @@
         <v>45643</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>44678.3315625</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27087,7 +27087,7 @@
         <v>44610</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>45615</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45638</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45439</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>45429</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45644</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45188</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>45797.45900462963</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44832.49594907407</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>45798.42252314815</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>45366.42888888889</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>45798.41734953703</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>45797.42777777778</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45338.49412037037</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         <v>45799.53348379629</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>45693</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>45721.35173611111</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>45742.49414351852</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>45799.53803240741</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>45799.5421875</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45799.57714120371</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>45799.64877314815</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>45799.67806712963</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45733.62903935185</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>45148</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>45148</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>45799.68190972223</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>45148</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>44588</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45799.675</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45799.53947916667</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>45799.54104166666</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>45737.40503472222</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45323.55914351852</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>45799.65021990741</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>45799.6527199074</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>45194</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>45799.43496527777</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45086.7037037037</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>45744</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45601</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>45341</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>45608</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>44594</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>45638</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>45327</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>45803.36384259259</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>45371</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>45677</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>45845.53202546296</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>45190</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>44629.42423611111</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45803.63395833333</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30223,7 +30223,7 @@
         <v>45762.49243055555</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45805.4094675926</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30342,7 +30342,7 @@
         <v>45351.54596064815</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>45805.41010416667</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30466,7 +30466,7 @@
         <v>45684</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>45054.9271875</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>45805.41813657407</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>45231.54601851852</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>45805.43402777778</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45646.50211805556</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>45173</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>44594</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>45194.60876157408</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         <v>45805.4255787037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>45259</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>44819.62</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>45259</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45055</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>45310.53418981482</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>45182</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>45182</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>45511</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31517,7 +31517,7 @@
         <v>45849.49259259259</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>45093.46706018518</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>44130</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>45851.62179398148</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>45407.69575231482</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>45810.44339120371</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>45188.42052083334</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>45809</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>45852.39642361111</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44883</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>45851.62018518519</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>45231.62840277778</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>44849</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>45215.44233796297</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>45677</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>45695.8391550926</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>45695.84078703704</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32521,7 +32521,7 @@
         <v>44209</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32578,7 +32578,7 @@
         <v>44894.57065972222</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>45705.2953125</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>45341</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>45775.46377314815</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>45851.60097222222</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45852.36871527778</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>45341.63811342593</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>45216</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>45216</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>45173</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>45624</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>45694</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>45809</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>45729</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         <v>45729</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>45809</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33587,7 +33587,7 @@
         <v>45208.4350462963</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>44935</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45614.65928240741</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45453.69339120371</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>45705</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>45852.68978009259</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>45810.44299768518</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45852.72965277778</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>45809</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45180.40255787037</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44504</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>44614.59027777778</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>45852</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34358,7 +34358,7 @@
         <v>44435.38657407407</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>44602</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34472,7 +34472,7 @@
         <v>45853.76976851852</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>45854.44017361111</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>44679.68706018518</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>45812.48032407407</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>45149.56928240741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>45181.36815972222</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>45810.45960648148</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>44977</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>44679.66694444444</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44223</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>45856.34959490741</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45721.34715277778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>45814</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35243,7 +35243,7 @@
         <v>45813</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35300,7 +35300,7 @@
         <v>45182</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>45182</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>45813.46034722222</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>44131</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>45856.34034722222</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45856.34231481481</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         <v>44624.64538194444</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35719,7 +35719,7 @@
         <v>45856.36153935185</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35781,7 +35781,7 @@
         <v>45618.71140046296</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>44637.56178240741</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>45175</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45453</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>44140</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45524</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>44109</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>44967</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45818.57910879629</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>44909</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>44599.42277777778</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>44593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>44593.61355324074</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45344</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>44946</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45425.94947916667</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45699</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45664</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45194.63479166666</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45152</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>45694.49037037037</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>45817</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37080,7 +37080,7 @@
         <v>44699</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>44426</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>44106</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>44608</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45614</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45202.4997337963</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>44222</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>45225.46480324074</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>45820</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>45820</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>45131</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>45817</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37784,7 +37784,7 @@
         <v>45820</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>45259</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>45236.47697916667</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>45863.44648148148</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>45821.45905092593</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>45824.43798611111</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45821.44101851852</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>45863.45355324074</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>45299</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>45267</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>45552</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38426,7 +38426,7 @@
         <v>45236</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>44960</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>44960.66233796296</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38597,7 +38597,7 @@
         <v>45825.44482638889</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>45726</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45825.49060185185</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38778,7 +38778,7 @@
         <v>45511</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>45827.62096064815</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>45852.67366898148</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         <v>45827.64092592592</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>45719.42197916667</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>45719.43646990741</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>44553</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39197,7 +39197,7 @@
         <v>45827.46288194445</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>45874.705</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45831.42365740741</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>45831.42616898148</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>44799.36695601852</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>45831.73</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>44126</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>45231</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>44575</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45254</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>45321</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39834,7 +39834,7 @@
         <v>45097</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45317</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>45361.57299768519</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>44200</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40067,7 +40067,7 @@
         <v>45831.46731481481</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45832.35590277778</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>44893</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>45831.40671296296</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>45369</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>44155</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>45164.82913194445</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>44904</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45351.48662037037</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45832.35545138889</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>44659</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40719,7 +40719,7 @@
         <v>45707</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>44930</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>45831.72686342592</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>45310</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40957,7 +40957,7 @@
         <v>44438</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>45874</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>45876</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
         <v>45358</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>45876</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45091.69766203704</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45751.32001157408</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45379</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>44912.29869212963</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>44614.69730324074</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45691</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45880.68200231482</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>45443</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45835.62752314815</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45736.45847222222</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45880.32907407408</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>45693</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>44967.55960648148</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45867.58056712963</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45523</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>44788</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>45761.47540509259</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45761.47748842592</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45880.43200231482</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45877.57847222222</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45877.62969907407</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45880.34064814815</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45693</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>45881.45898148148</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>45721.60894675926</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>44817</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42759,7 +42759,7 @@
         <v>45254</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>45839</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42873,7 +42873,7 @@
         <v>45839</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42950,7 +42950,7 @@
         <v>45881.44938657407</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>45882.47538194444</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>45216.39040509259</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45882.37202546297</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -43178,7 +43178,7 @@
         <v>45202</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43240,7 +43240,7 @@
         <v>45839</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43297,7 +43297,7 @@
         <v>45821.31292824074</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43354,7 +43354,7 @@
         <v>45840.68518518518</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>45840</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45882.52290509259</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>45478</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>45841.81555555556</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>45841.5847337963</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45599</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>45642.63524305556</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>44512</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>45646.61892361111</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>44159</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>44984.69216435185</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>44379.56163194445</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44115,7 +44115,7 @@
         <v>45390</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -44172,7 +44172,7 @@
         <v>44617.48311342593</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44229,7 +44229,7 @@
         <v>44245</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>45391.37361111111</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45679</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>44977</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>44063</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45842.74049768518</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45446.78256944445</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44643,7 +44643,7 @@
         <v>45520</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>44581.60254629629</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>44568.67040509259</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>45769.6009375</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>45698.65606481482</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>45693</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>44123</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45052,7 +45052,7 @@
         <v>44908.425625</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45109,7 +45109,7 @@
         <v>45426</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>44993</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>44358.63490740741</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>44733</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45337,7 +45337,7 @@
         <v>44949.4708912037</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>44403.29719907408</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>44946.43564814814</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45033</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>44994</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45627,7 +45627,7 @@
         <v>44531</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>44665</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45068.58563657408</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45803,7 +45803,7 @@
         <v>45426.34148148148</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>44105</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45922,7 +45922,7 @@
         <v>44209</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>45363.54878472222</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46041,7 +46041,7 @@
         <v>44273</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>44967.80034722222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46155,7 +46155,7 @@
         <v>44967</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46212,7 +46212,7 @@
         <v>44960.65061342593</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46269,7 +46269,7 @@
         <v>44960</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46326,7 +46326,7 @@
         <v>44929</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>44593.64863425926</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>44928</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>45730.43966435185</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46569,7 +46569,7 @@
         <v>45614</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>45552</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46688,7 +46688,7 @@
         <v>45121</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>44819.50233796296</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>45583</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>44616</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>44886</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45042</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>44608</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>44909.51885416666</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>44560</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>45600</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>45107.53688657407</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>45456.59535879629</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47397,7 +47397,7 @@
         <v>44600</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>44623.41775462963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>44623.5571875</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47583,7 +47583,7 @@
         <v>45167.3721412037</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>45089</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>44965</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47754,7 +47754,7 @@
         <v>44965</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45308.63298611111</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>45212.34997685185</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>44886.5928125</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45293</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>45181.58055555556</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>45670</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45520</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>44742</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>45231</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48339,7 +48339,7 @@
         <v>45341</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45474.41729166666</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>45594</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45644.62677083333</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>45300.55028935185</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48639,7 +48639,7 @@
         <v>45642</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48701,7 +48701,7 @@
         <v>45097</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48758,7 +48758,7 @@
         <v>45695.83655092592</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45707</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>44969</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45645</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -49001,7 +49001,7 @@
         <v>44944</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49058,7 +49058,7 @@
         <v>45113</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>45113.80170138889</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49172,7 +49172,7 @@
         <v>45601</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49229,7 +49229,7 @@
         <v>45154.35092592592</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49286,7 +49286,7 @@
         <v>44652</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49343,7 +49343,7 @@
         <v>45678</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49400,7 +49400,7 @@
         <v>44679</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49457,7 +49457,7 @@
         <v>45757.6997337963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49514,7 +49514,7 @@
         <v>45757</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49571,7 +49571,7 @@
         <v>45631.44464120371</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49628,7 +49628,7 @@
         <v>45656</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49690,7 +49690,7 @@
         <v>45694</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49747,7 +49747,7 @@
         <v>45693</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49804,7 +49804,7 @@
         <v>44806</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49861,7 +49861,7 @@
         <v>45719.4094212963</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45049.66025462963</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45719.43872685185</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50042,7 +50042,7 @@
         <v>44644.37548611111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45679</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>44574</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>44645.39157407408</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>44497.4666087963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>44400.6750925926</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>44403.3119212963</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50461,7 +50461,7 @@
         <v>45152</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50518,7 +50518,7 @@
         <v>44964.65261574074</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50575,7 +50575,7 @@
         <v>44599.44832175926</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50632,7 +50632,7 @@
         <v>44980</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50689,7 +50689,7 @@
         <v>45481.83684027778</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45638</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50803,7 +50803,7 @@
         <v>45000.44666666666</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50860,7 +50860,7 @@
         <v>44508.44033564815</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>44519.64902777778</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45762.61341435185</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45713.44519675926</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45442</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45656</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45327.61831018519</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>45098.63572916666</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51326,7 +51326,7 @@
         <v>45352</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45694</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>44820.47935185185</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51502,7 +51502,7 @@
         <v>44944</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51559,7 +51559,7 @@
         <v>45065.43013888889</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51616,7 +51616,7 @@
         <v>45637</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51678,7 +51678,7 @@
         <v>44532</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>45266</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51792,7 +51792,7 @@
         <v>45691</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>44872</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51906,7 +51906,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51963,7 +51963,7 @@
         <v>45691</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52020,7 +52020,7 @@
         <v>45719.43755787037</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>45054.95675925926</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>45513.51815972223</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52201,7 +52201,7 @@
         <v>45772.77188657408</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52258,7 +52258,7 @@
         <v>45617.59006944444</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52315,7 +52315,7 @@
         <v>45049</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52372,7 +52372,7 @@
         <v>44560</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52429,7 +52429,7 @@
         <v>45336.53908564815</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52486,7 +52486,7 @@
         <v>45047.31793981481</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>45614.67020833334</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52600,7 +52600,7 @@
         <v>44888</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52662,7 +52662,7 @@
         <v>44207</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45127</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>44379.5745949074</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45770.61341435185</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45677.39440972222</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45048.55349537037</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53014,7 +53014,7 @@
         <v>45169</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53076,7 +53076,7 @@
         <v>45244.52202546296</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53138,7 +53138,7 @@
         <v>44848</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53195,7 +53195,7 @@
         <v>45435.34778935185</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45259</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45763</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45548.42854166667</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45223</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>44420</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>44993</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45714.55368055555</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>44532</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>45190</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53770,7 +53770,7 @@
         <v>45723.63290509259</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45763.52995370371</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53884,7 +53884,7 @@
         <v>44531</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>44977</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>45336.54270833333</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         <v>44532</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54112,7 +54112,7 @@
         <v>45110</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>45194</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54231,7 +54231,7 @@
         <v>45757.67611111111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>45078</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54350,7 +54350,7 @@
         <v>45474</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54407,7 +54407,7 @@
         <v>44378.56137731481</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54464,7 +54464,7 @@
         <v>45611</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54521,7 +54521,7 @@
         <v>44123</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54578,7 +54578,7 @@
         <v>44139</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54635,7 +54635,7 @@
         <v>45300.55680555556</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54692,7 +54692,7 @@
         <v>45589</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54749,7 +54749,7 @@
         <v>45589</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54806,7 +54806,7 @@
         <v>44609.60171296296</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54868,7 +54868,7 @@
         <v>45202</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54925,7 +54925,7 @@
         <v>44503</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -54982,7 +54982,7 @@
         <v>44624.35083333333</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55044,7 +55044,7 @@
         <v>45456.58491898148</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55101,7 +55101,7 @@
         <v>44897</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55158,7 +55158,7 @@
         <v>45638</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55215,7 +55215,7 @@
         <v>44900.54711805555</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55272,7 +55272,7 @@
         <v>45580</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55329,7 +55329,7 @@
         <v>44944</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55386,7 +55386,7 @@
         <v>45729</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55443,7 +55443,7 @@
         <v>45729</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55500,7 +55500,7 @@
         <v>45555.5727662037</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55557,7 +55557,7 @@
         <v>45295</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55619,7 +55619,7 @@
         <v>44168.55746527778</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55676,7 +55676,7 @@
         <v>45327</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55733,7 +55733,7 @@
         <v>45014</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55790,7 +55790,7 @@
         <v>45222</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55847,7 +55847,7 @@
         <v>44593</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55904,7 +55904,7 @@
         <v>45685.5778125</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55961,7 +55961,7 @@
         <v>45695.59805555556</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>45460</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56085,7 +56085,7 @@
         <v>45345.56</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56142,7 +56142,7 @@
         <v>44914.67600694444</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56199,7 +56199,7 @@
         <v>45554</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56256,7 +56256,7 @@
         <v>45061</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56313,7 +56313,7 @@
         <v>44210</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56370,7 +56370,7 @@
         <v>45757</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56427,7 +56427,7 @@
         <v>45583.47836805556</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>44912</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>44816</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>45763.6503125</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56660,7 +56660,7 @@
         <v>44967.78984953704</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>45316</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45317</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56836,7 +56836,7 @@
         <v>45075.51982638889</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>45349</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56950,7 +56950,7 @@
         <v>45307</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -57007,7 +57007,7 @@
         <v>45104.6828125</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>45720.60410879629</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57121,7 +57121,7 @@
         <v>45642</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57183,7 +57183,7 @@
         <v>45699</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57240,7 +57240,7 @@
         <v>45733.63099537037</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57297,7 +57297,7 @@
         <v>45426.61569444444</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57354,7 +57354,7 @@
         <v>45478.60802083334</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57416,7 +57416,7 @@
         <v>45719.40723379629</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45154.34931712963</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -567,7 +567,7 @@
         <v>45603</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>45812.47355324074</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>45548</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>45827.64737268518</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44377</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>45313</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45715.38824074074</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45082</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>45728</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45812.55136574074</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45882.73309027778</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>44971</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>44623</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44222</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45086</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45202</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44575</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>45803.55737268519</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45803.55260416667</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>45812</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>44356</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45196</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>45758</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44180</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>44497</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45442</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45092</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>45013</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>45799.60315972222</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44792</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>45803.61035879629</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>44532</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>45316</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>45736.53695601852</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>45097</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>44351</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>45107</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44574</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44719</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44664</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44659</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>44974</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45442</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45841.64539351852</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>44740</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>45371</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44791</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>45090</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>44804</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>45803.55535879629</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>44495</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>45831.55982638889</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>44684</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44967</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>45222</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>45762.62260416667</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>45694.55559027778</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>45189</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>45168.50667824074</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>45715.38105324074</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>45666</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45293</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44489</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>45474</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>45841.80690972223</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>45035.44672453704</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>44614</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>44379</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>44651</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44487</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>45763.52524305556</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>45273</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>45757.49934027778</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>45385</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>45358</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>45107</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>44917.59298611111</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>44645</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>45665</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>45336</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>45783</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>45694.49650462963</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45687</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>45803.61554398148</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>45805.41232638889</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>44917</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44081</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>44855</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>45811.38710648148</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>45098</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44958</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45314.55579861111</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>45679</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>45817</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45817.34614583333</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>45464</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>45818.60254629629</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>45736.49902777778</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>45820.84516203704</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>44467</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44673.47858796296</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>45874</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>45874.69282407407</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>45167</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>45762.57244212963</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>45107</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>44909</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44897</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>44963</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44849</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>44144</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>44602</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>44583.61803240741</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>44119</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>44602</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>44517</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>44567.81241898148</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>44407</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44544</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44526</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44489</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44083</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>44609.61430555556</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>44583.62121527778</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>44323.58961805556</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44299</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>44714</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44491.50769675926</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>44252</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>44569.5340625</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>44486</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>44662.56783564815</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>44572.39640046296</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44230</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>44494</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>44659.70381944445</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>44700</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>44603</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>44839</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>44784</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>44369.65428240741</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>44612</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44720</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44886</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>44598</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>44883.56321759259</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>44314</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44610</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>44865.43494212963</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>44167</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>44357</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44742</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>44533.4678587963</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44764</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>44453</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>44297</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>44153</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>44351</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44349.49666666667</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>44584.63190972222</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44609</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>44490.64313657407</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>44091</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44610</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>44281.4499537037</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>44335.52201388889</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>44512</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>44740.68142361111</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>44816</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>44297</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>44705.78475694444</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44705.83326388889</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>44722.30703703704</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>44583.61555555555</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>44575</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>44649</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>44692.87630787037</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>44698.67151620371</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>44277.65263888889</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>44847</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15130,7 +15130,7 @@
         <v>44575.4366087963</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>44599.43265046296</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>44328.57100694445</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>44750.678125</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>44369</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>44543</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>44461</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>44865</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44461.73350694445</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>44383</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>44685.6212037037</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>44378.69857638889</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>44702.70721064815</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>44593</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>44442.35195601852</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>44442</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>44733.43420138889</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>44711</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>44504.59193287037</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>44643.51446759259</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44750.45800925926</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>44076</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>44095</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>44743</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>44846</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>44551.59704861111</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>44623.4572337963</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>44571.44563657408</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44103</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>44479</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44134</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>44838.40635416667</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         <v>44489</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>44459</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>44446.47693287037</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>44543.34697916666</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>44495</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>44729</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>44160</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>44491.54116898148</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>44676</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>44517</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>44634</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>44144</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>44266.57917824074</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44294.37555555555</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>44476.61263888889</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>44886.58890046296</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>44847.35622685185</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>44659.57912037037</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>44705.84535879629</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>44791.38336805555</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>44522.55518518519</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>44623</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>44762</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>44798</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>44144</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>45645</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>44659</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>44614.69730324074</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>45259</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>44593</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>44593.61355324074</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45358</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>44623.41775462963</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45678</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>45644.47723379629</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>44893</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>44245</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>45075.51982638889</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>45589</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>45589</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45695.84078703704</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45695.59197916667</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45614.67020833334</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45478</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>45293</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45148</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45148</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>45182</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19845,7 +19845,7 @@
         <v>45194.63479166666</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45194.60876157408</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44799.36359953704</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45266</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45646.61892361111</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>45599</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45691</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>45089</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45775.46377314815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>44652</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45600</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>45583</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>45583</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45223</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>44665</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45345.56</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45699</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>45695.8391550926</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>45131</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>45694</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>44109</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>45091.69766203704</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>44581.60254629629</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45741.45114583334</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44624.35083333333</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>45154.34931712963</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>44599.42277777778</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45685.5778125</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45443</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>44599.44832175926</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45310</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45327.61831018519</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>44435.38657407407</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>44967.78984953704</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>44637.35744212963</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>45615</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>44637.56178240741</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45097</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>45695.59805555556</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>45327</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>44519</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>45729</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>45729</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>45294.5666550926</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>45756.44024305556</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>45321</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44608</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>44816</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44403.3119212963</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45694.49037037037</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>44420</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45435.34778935185</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>45554</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>45310.53418981482</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>44897</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45317</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>45366.42888888889</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>44993</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45351.54596064815</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>45180.40255787037</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45611</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>45677</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45730.43966435185</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>44593</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45723.63290509259</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45049.66025462963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45520</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45175.57060185185</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>44909.51885416666</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>45159.44694444445</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>45729</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45729</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>45181.36815972222</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44900.54711805555</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45713.44519675926</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>45254.49552083333</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         <v>44872</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>44553</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>45344.64759259259</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>45190</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44550.37994212963</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>44379.56163194445</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>45048.55349537037</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45212.34997685185</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>44532</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>44209</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>45107.53688657407</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>45769.6009375</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>44928</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>44944</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>45093.46706018518</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>45061</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>45762.61341435185</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44969</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45033</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44610</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45656</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>44977</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>44159</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>45167.3721412037</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>45468</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>44679.66694444444</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>45119</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>45763.52995370371</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>44139</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45231</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45316</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>45614.65928240741</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>45169</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>44531</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>45216</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45327</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>45344.69567129629</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44980</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>45552</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         <v>45694</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
         <v>44508.44033564815</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>44644.37548611111</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>45425.94947916667</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45426.61569444444</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45244.52202546296</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44095</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>45691</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>45614</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44960.65061342593</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>44960</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>45583</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45295</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>45187.61136574074</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45453</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>45638</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>45776.6415162037</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>44531</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>44400.6750925926</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>44532</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>45369</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45520</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>45777.37119212963</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>45777</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28040,7 +28040,7 @@
         <v>45107.55574074074</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>45776.45263888889</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45733.63099537037</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>45777.52655092593</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45363.54878472222</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         <v>45777.34894675926</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>45574</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>45776.48275462963</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28516,7 +28516,7 @@
         <v>45776</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>45777.32731481481</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>45779.49085648148</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>44809.92752314815</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>45779.6665162037</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>45638</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>45779.65787037037</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>45783.61053240741</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>45300.55028935185</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>44944</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>44617.48311342593</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45161</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29220,7 +29220,7 @@
         <v>45618.71140046296</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45548.42854166667</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>45784.80497685185</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29391,7 +29391,7 @@
         <v>44742</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>45583.47836805556</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>44519.64902777778</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>45736.60863425926</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>45784.57266203704</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45107</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44123</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45107</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>44967</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45558.42498842593</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>44569.69358796296</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>45254</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>45368.64787037037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44949.4708912037</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>45584.60038194444</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44568.67040509259</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45054.9271875</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44859.36896990741</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30452,7 +30452,7 @@
         <v>45693</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>44832</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>45091</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>45371.67368055556</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>45684</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>45601</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>45407.49721064815</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>45149.56928240741</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>44395</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>45562</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>45177.79766203704</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>44548</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>45625.58501157408</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>45426</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>45133</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>45523</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>45329</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44569.49344907407</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>45583.48449074074</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>44645.39157407408</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45371.50738425926</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44594</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>44616</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45743.50744212963</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>45078</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>45721.60894675926</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>45624</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>45042</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>45790.44972222222</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45047.31793981481</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>44624.64538194444</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45555.5727662037</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>45726</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>45790.51186342593</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>45790.51040509259</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>45182</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>45182</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>45327</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>45050.49392361111</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44273</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>44616</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>45037</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45490</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45195.64807870371</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>45719.40723379629</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>45644</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         <v>45644</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>45300</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33253,7 +33253,7 @@
         <v>44533.46665509259</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33310,7 +33310,7 @@
         <v>45646.50211805556</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33367,7 +33367,7 @@
         <v>44200</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>45055</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>45162</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33543,7 +33543,7 @@
         <v>45154.35092592592</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>45439</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>44912</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33719,7 +33719,7 @@
         <v>45693</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>45335.66331018518</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33838,7 +33838,7 @@
         <v>45611</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45691</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33952,7 +33952,7 @@
         <v>45636</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34009,7 +34009,7 @@
         <v>45797.42777777778</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>44849</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45677</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>45698.65606481482</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>45407.69575231482</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>44277.65650462963</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>45757.6997337963</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45757</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34465,7 +34465,7 @@
         <v>45307</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>45617.59006944444</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>45797.45900462963</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>44512</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>44977</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45525</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45429</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45097</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45719.43755787037</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>45799.53803240741</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>45799.53348379629</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>45799.68190972223</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>45799.67806712963</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45798.41734953703</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35298,7 +35298,7 @@
         <v>45799.57714120371</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45182</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>44993</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>44904</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44106</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44130</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>44426</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>45068.58563657408</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>44819.50233796296</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>44929</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>44105</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35940,7 +35940,7 @@
         <v>45726</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>45664</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>45733.62903935185</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>45799.65021990741</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>45799.6527199074</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44600</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>45456.59535879629</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>45694</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>44806</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>44847</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>45737.40503472222</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45338.49412037037</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>45799.53947916667</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>45799.54104166666</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>45693</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>45799.43496527777</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>45601</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>45799.5421875</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45799.64877314815</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45798.42252314815</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>45236</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>44544</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45159.45748842593</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>45624</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45803.36384259259</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45086.7037037037</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>45803.63395833333</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>45608</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>45341</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45762.49243055555</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45744</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>44131</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>44883</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>45127</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>44799.36695601852</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>45216</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>45805.4094675926</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>44909</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45805.41813657407</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>45805.4255787037</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38305,7 +38305,7 @@
         <v>45805.43402777778</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45805.41010416667</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45202.4997337963</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45614</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38553,7 +38553,7 @@
         <v>45145</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>44602</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38667,7 +38667,7 @@
         <v>45164.82913194445</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38729,7 +38729,7 @@
         <v>44140</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>45809</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>45215.44233796297</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38905,7 +38905,7 @@
         <v>45810.44339120371</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38967,7 +38967,7 @@
         <v>45809</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
         <v>45852.36871527778</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39081,7 +39081,7 @@
         <v>44551.76711805556</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39143,7 +39143,7 @@
         <v>45208.4350462963</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39200,7 +39200,7 @@
         <v>45065.43013888889</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39257,7 +39257,7 @@
         <v>45852.68978009259</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>45426.34148148148</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>44371.49178240741</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39433,7 +39433,7 @@
         <v>45810.45960648148</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>45809</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>45723</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39614,7 +39614,7 @@
         <v>45699</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39671,7 +39671,7 @@
         <v>44967.80034722222</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>44967</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>45809</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45236.47697916667</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45453.69339120371</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>45851.62018518519</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45853.76976851852</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>45511</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>45851.62179398148</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45852.39642361111</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>45810.44299768518</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>45851.60097222222</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45631.44464120371</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>45852</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45852.72965277778</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>45341</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>44503</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>45000.44666666666</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>44966</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>45006</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>45202</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45474.41729166666</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45188</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>45177.56940972222</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>44560</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>44946</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>44522</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>45036</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>44593.64863425926</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45677.39440972222</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>45152</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45812.48032407407</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>45299</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>44126</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44403.29719907408</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>45021.29524305555</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44699</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45813.46034722222</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45642</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45854.44017361111</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         <v>45813</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>45307</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45351.48662037037</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>45188.42052083334</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45721.35173611111</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>44886</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>45371</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>44516</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45300.55680555556</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>44155</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45721.34715277778</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45814</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45208.46130787037</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>44358.63490740741</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>44908.425625</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45817</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45163.59913194444</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>45173</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45181.58055555556</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45134.57021990741</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45856.34959490741</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>44866</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43320,7 +43320,7 @@
         <v>45152</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43377,7 +43377,7 @@
         <v>45856.34034722222</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>45856.34231481481</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>45818.57910879629</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43563,7 +43563,7 @@
         <v>45817</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45194</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>45231</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>44886.5928125</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>45520</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43858,7 +43858,7 @@
         <v>45201.62318287037</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>44810</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>45341.63811342593</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44029,7 +44029,7 @@
         <v>45446.78256944445</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45863.44648148148</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45820</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>44210</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>45524</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44324,7 +44324,7 @@
         <v>45820</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>45820</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44438,7 +44438,7 @@
         <v>45821.44101851852</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44495,7 +44495,7 @@
         <v>45121</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44557,7 +44557,7 @@
         <v>45863.45355324074</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>45614</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>45720.60410879629</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>45729</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>45344</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45824.43798611111</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44909,7 +44909,7 @@
         <v>45637</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>45825.49060185185</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>45825.44482638889</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45821.45905092593</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>44817</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>44831</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45391.37361111111</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>44629.42423611111</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45380,7 +45380,7 @@
         <v>44832.49594907407</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45827.64092592592</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>45317</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>45827.46288194445</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>44574</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>45096</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>45254</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>45580</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45293</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45656</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45960,7 +45960,7 @@
         <v>45757.67611111111</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>45763</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46074,7 +46074,7 @@
         <v>45827.62096064815</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46131,7 +46131,7 @@
         <v>44560</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46188,7 +46188,7 @@
         <v>45831.40671296296</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46245,7 +46245,7 @@
         <v>44446</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>44935</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46359,7 +46359,7 @@
         <v>44594</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46416,7 +46416,7 @@
         <v>45222</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45852.67366898148</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45552</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45831.72686342592</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45426</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46711,7 +46711,7 @@
         <v>45831.73</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46773,7 +46773,7 @@
         <v>45831.46731481481</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46830,7 +46830,7 @@
         <v>45831.42365740741</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         <v>45831.42616898148</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>45216.39040509259</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>44912.29869212963</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
         <v>45695.83655092592</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>44967.55960648148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45832.35545138889</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45832.35590277778</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>44614.59027777778</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>45638</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>44930</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45098.62966435185</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>45756.50738425926</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47586,7 +47586,7 @@
         <v>45014</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45874.705</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>44678.3315625</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47762,7 +47762,7 @@
         <v>44501.71344907407</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47824,7 +47824,7 @@
         <v>45175</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>45474</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>45874</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>44588</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48057,7 +48057,7 @@
         <v>45259</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>45194</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45231.62840277778</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>45877.57847222222</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48290,7 +48290,7 @@
         <v>45877.62969907407</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48347,7 +48347,7 @@
         <v>45442</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45705</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45259.52809027778</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>44819.62</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48580,7 +48580,7 @@
         <v>45335</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45341</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48704,7 +48704,7 @@
         <v>45642</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48766,7 +48766,7 @@
         <v>45390</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>45190</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48880,7 +48880,7 @@
         <v>45054.95675925926</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>44575</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48994,7 +48994,7 @@
         <v>45714.55368055555</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45719.42197916667</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45719.43646990741</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>44994</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>44679.68706018518</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45643</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>45876</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>45835.62752314815</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>44733</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45876</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45880.68200231482</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>44168.55746527778</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>45719.4094212963</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49760,7 +49760,7 @@
         <v>45719.43872685185</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>44914.67600694444</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49879,7 +49879,7 @@
         <v>45880.32907407408</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45049</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49993,7 +49993,7 @@
         <v>45202</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>45259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50117,7 +50117,7 @@
         <v>45821.31292824074</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>44984.69216435185</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50236,7 +50236,7 @@
         <v>44379.5745949074</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>45839</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50350,7 +50350,7 @@
         <v>45881.44938657407</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50407,7 +50407,7 @@
         <v>45880.34064814815</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50464,7 +50464,7 @@
         <v>45867.58056712963</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50521,7 +50521,7 @@
         <v>45839</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50578,7 +50578,7 @@
         <v>45881.45898148148</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>45839</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>44207</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50774,7 +50774,7 @@
         <v>45841.5847337963</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50831,7 +50831,7 @@
         <v>45524</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50893,7 +50893,7 @@
         <v>45840</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>44623.5571875</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>44960</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>44960.66233796296</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45882.52290509259</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>44328</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51245,7 +51245,7 @@
         <v>45882.47538194444</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51302,7 +51302,7 @@
         <v>45736.45847222222</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51364,7 +51364,7 @@
         <v>45267</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51426,7 +51426,7 @@
         <v>44532</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51483,7 +51483,7 @@
         <v>44820.47935185185</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>45882.37202546297</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51602,7 +51602,7 @@
         <v>45757</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51659,7 +51659,7 @@
         <v>45840.68518518518</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>45352</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51773,7 +51773,7 @@
         <v>45181.33571759259</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51830,7 +51830,7 @@
         <v>45358</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51887,7 +51887,7 @@
         <v>45751.32001157408</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51944,7 +51944,7 @@
         <v>45758</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52001,7 +52001,7 @@
         <v>44894.57065972222</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52063,7 +52063,7 @@
         <v>45842.74049768518</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52120,7 +52120,7 @@
         <v>44378.56137731481</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52177,7 +52177,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52239,7 +52239,7 @@
         <v>45763</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>45679</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52353,7 +52353,7 @@
         <v>44944</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>44504</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52467,7 +52467,7 @@
         <v>45638</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52524,7 +52524,7 @@
         <v>44222</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52581,7 +52581,7 @@
         <v>45225.46480324074</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52638,7 +52638,7 @@
         <v>45763.52744212963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52695,7 +52695,7 @@
         <v>45880</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52752,7 +52752,7 @@
         <v>45254</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52809,7 +52809,7 @@
         <v>44603</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52866,7 +52866,7 @@
         <v>45113.80170138889</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52923,7 +52923,7 @@
         <v>45845.53202546296</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52980,7 +52980,7 @@
         <v>45513.51815972223</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53042,7 +53042,7 @@
         <v>45841.81555555556</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53104,7 +53104,7 @@
         <v>44848</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>44438</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53223,7 +53223,7 @@
         <v>45693</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53280,7 +53280,7 @@
         <v>44964.65261574074</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>45379</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53394,7 +53394,7 @@
         <v>44123</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53451,7 +53451,7 @@
         <v>45670</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53513,7 +53513,7 @@
         <v>45323.55914351852</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53575,7 +53575,7 @@
         <v>45856</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53637,7 +53637,7 @@
         <v>45113</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53694,7 +53694,7 @@
         <v>44588</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53751,7 +53751,7 @@
         <v>44883</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53813,7 +53813,7 @@
         <v>45693</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53870,7 +53870,7 @@
         <v>44553</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53927,7 +53927,7 @@
         <v>44788</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>45098.63572916666</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54041,7 +54041,7 @@
         <v>45884</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54098,7 +54098,7 @@
         <v>45670</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54160,7 +54160,7 @@
         <v>45770.61341435185</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54222,7 +54222,7 @@
         <v>45705.2953125</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54284,7 +54284,7 @@
         <v>45707</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>45890</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54408,7 +54408,7 @@
         <v>45891.33204861111</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54465,7 +54465,7 @@
         <v>45838</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54522,7 +54522,7 @@
         <v>45838</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54579,7 +54579,7 @@
         <v>45096</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54636,7 +54636,7 @@
         <v>45838</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>45891.4865625</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>45361.57299768519</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>45849.49259259259</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45891.46827546296</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45456.58491898148</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>45644.62677083333</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45148</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55097,7 +55097,7 @@
         <v>44980</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>45104.6828125</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45478.60802083334</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55273,7 +55273,7 @@
         <v>45259</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55330,7 +55330,7 @@
         <v>45460</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55392,7 +55392,7 @@
         <v>45642.63524305556</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55449,7 +55449,7 @@
         <v>45763.6503125</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>45096</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55563,7 +55563,7 @@
         <v>44977</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         <v>45231.54601851852</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55677,7 +55677,7 @@
         <v>44609.60171296296</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>45761.47540509259</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55796,7 +55796,7 @@
         <v>45761.47748842592</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55853,7 +55853,7 @@
         <v>45173</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55910,7 +55910,7 @@
         <v>45699.71063657408</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55967,7 +55967,7 @@
         <v>44816</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56024,7 +56024,7 @@
         <v>45308.63298611111</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56081,7 +56081,7 @@
         <v>45107</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>44888</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56200,7 +56200,7 @@
         <v>44535</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>45110</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56314,7 +56314,7 @@
         <v>44629.57741898148</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56376,7 +56376,7 @@
         <v>44608</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56438,7 +56438,7 @@
         <v>45594</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56500,7 +56500,7 @@
         <v>44209</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56557,7 +56557,7 @@
         <v>45707</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56619,7 +56619,7 @@
         <v>45644</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56676,7 +56676,7 @@
         <v>44497.4666087963</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56733,7 +56733,7 @@
         <v>44946.43564814814</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>44965</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>44965</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56904,7 +56904,7 @@
         <v>44679</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56961,7 +56961,7 @@
         <v>45336.53908564815</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -57018,7 +57018,7 @@
         <v>45336.54270833333</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57075,7 +57075,7 @@
         <v>45679</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45349</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57194,7 +57194,7 @@
         <v>44223</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -567,7 +567,7 @@
         <v>45603</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>45812.47355324074</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>45882.73309027778</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>45548</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>45827.64737268518</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>44377</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45313</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45082</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>45882.47538194444</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>45715.38824074074</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>45728</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45812.55136574074</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>44971</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>45803.55260416667</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>45803.55737268519</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45086</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44222</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>45202</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>44623</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44575</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45812</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>45758</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>44356</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45196</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>44180</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45442</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45092</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44497</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45799.60315972222</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>44792</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>45803.61035879629</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44532</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>44351</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>45316</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44574</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45107</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>45736.53695601852</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>45097</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>44719</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44664</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>44974</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>45442</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>45841.64539351852</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44659</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>44740</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>45371</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>44791</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>45090</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45803.55535879629</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>44684</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>45831.55982638889</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>44495</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>45694.55559027778</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>45222</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45035.44672453704</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>45474</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>45803.61554398148</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>45715.38105324074</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>45762.62260416667</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>44489</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>45841.80690972223</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>45293</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>45189</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>45168.50667824074</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44967</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44614</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44379</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>44651</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>45694.49650462963</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>45783</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>44963</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>45464</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>45687</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>44081</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44909</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>45273</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>45107</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45167</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>45805.41232638889</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>45098</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>44673.47858796296</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>45811.38710648148</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>45679</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>45818.60254629629</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>45817.34614583333</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>45817</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>45736.49902777778</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45820.84516203704</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44897</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>45358</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>45874.69282407407</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>44645</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>45874</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>45763.52524305556</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>44958</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>45336</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>45665</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>44917.59298611111</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>45896.47487268518</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>45314.55579861111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>44849</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>44467</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>45757.49934027778</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>44917</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>44855</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45107</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>45762.57244212963</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>45385</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>44144</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>44119</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>44583.61803240741</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44602</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>44602</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>44517</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>44567.81241898148</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>44407</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>44544</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>44526</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44489</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>44609.61430555556</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44083</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>44583.62121527778</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>44323.58961805556</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>44299</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44714</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44491.50769675926</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>44252</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>44486</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>44662.56783564815</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>44569.5340625</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>44659.70381944445</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>44572.39640046296</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>44230</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>44603</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>44494</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>44700</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>44839</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44784</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         <v>44369.65428240741</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>44612</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>44720</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44886</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>44598</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>44883.56321759259</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>44314</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>44610</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>44865.43494212963</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>44167</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>44357</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>44742</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>44704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>44533.4678587963</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>44764</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44453</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>44297</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44153</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>44351</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>44349.49666666667</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>44584.63190972222</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>44609</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>44490.64313657407</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>44091</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>44610</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44281.4499537037</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>44512</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>44335.52201388889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>44740.68142361111</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>44816</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>44297</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44722.30703703704</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>44705.78475694444</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44705.83326388889</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>44692.87630787037</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>44698.67151620371</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>44328.57100694445</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44277.65263888889</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44369</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44750.678125</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>44599.43265046296</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>44543</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>44461</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>44383</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>44685.6212037037</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44378.69857638889</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>44702.70721064815</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44865</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>44461.73350694445</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>44442.35195601852</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44442</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>44504.59193287037</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>44643.51446759259</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44750.45800925926</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44076</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44593</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44733.43420138889</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44095</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>44711</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44846</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>44551.59704861111</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>44743</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>44134</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44446.47693287037</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44571.44563657408</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44103</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44838.40635416667</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44459</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>44623.4572337963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>44491.54116898148</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44479</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44676</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44489</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>44543.34697916666</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>44476.61263888889</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>44160</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>44847.35622685185</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>44517</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>44495</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>44705.84535879629</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44729</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44634</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44144</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44266.57917824074</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44886.58890046296</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44522.55518518519</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44294.37555555555</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>44659.57912037037</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>44791.38336805555</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>44649</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>44799.36359953704</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>44623</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>44762</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>44847</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>44798</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>45723</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>44583.61555555555</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>44144</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>44575</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>45208.46130787037</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>45119</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>44859.36896990741</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>44328</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>44832</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45050.49392361111</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>44966</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>44575.4366087963</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44883</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>44866</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>45699.71063657408</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45729</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>44501.71344907407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>45743.50744212963</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>45756.44024305556</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45756.50738425926</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>45187.61136574074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45175.57060185185</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45695.59197916667</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45371.50738425926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45741.45114583334</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>45644.47723379629</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>45006</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45644</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>45307</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>44548</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45614</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44550.37994212963</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45327</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>44847</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45300</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45670</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44980</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>45259.52809027778</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>44446</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45096</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>45776.48275462963</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45776</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45776.45263888889</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45107.55574074074</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>45776.6415162037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45254.49552083333</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45611</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45777.37119212963</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45777.34894675926</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>45777.32731481481</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45777.52655092593</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>45777</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>45520</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>44831</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>45574</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45344.64759259259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45779.6665162037</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>45758</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45779.65787037037</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>44809.92752314815</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>44810</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>45107</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>45107</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45107</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45344.69567129629</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>44816</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>44371.49178240741</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45779.49085648148</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45133</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45096</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45098.62966435185</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45783.61053240741</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>44544</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>44519</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>44395</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45335</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>45293</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>45163.59913194444</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>45784.57266203704</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>45096</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>44569.49344907407</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45407.49721064815</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45294.5666550926</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45784.80497685185</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45329</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45177.79766203704</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>44095</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>44551.76711805556</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45327</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45558.42498842593</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>45562</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45368.64787037037</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>44553</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>44569.69358796296</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45231.54601851852</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45684</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>45259</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45259</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>45254</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>45310.53418981482</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44603</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45161</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44883</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>44849</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>45524</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44629.57741898148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45468</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45037</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45726</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>45371.67368055556</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>45790.51040509259</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>45134.57021990741</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>45091</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>45790.44972222222</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>45583.48449074074</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>44533.46665509259</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>45584.60038194444</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45625.58501157408</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>45790.51186342593</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>44894.57065972222</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>45021.29524305555</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>45583</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>45583</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>44535</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>44637.35744212963</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>45036</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>45624</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>45341</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45162</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>45159.44694444445</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>45145</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>45201.62318287037</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>45358</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44522</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44616</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>45181.33571759259</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>44516</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>45525</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>45341.63811342593</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>45335.66331018518</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>45195.64807870371</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>44935</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>45177.56940972222</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45614.65928240741</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45636</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>44277.65650462963</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>45736.60863425926</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>44504</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>45490</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44435.38657407407</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>44602</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>45439</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45429</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>45763</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>45797.45900462963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>44977</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>45644</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45159.45748842593</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45798.42252314815</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45798.41734953703</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45797.42777777778</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45643</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45799.53348379629</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>44678.3315625</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>44610</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>45615</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>45693</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44131</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45638</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>44624.64538194444</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45618.71140046296</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45799.53803240741</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45799.5421875</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44637.56178240741</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>45799.57714120371</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>45799.64877314815</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45799.67806712963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>45733.62903935185</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>45644</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>45799.68190972223</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45188</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45453</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45799.53947916667</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>45799.54104166666</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>44140</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45524</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>44109</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>45737.40503472222</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>44967</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>45799.65021990741</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>45799.6527199074</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>45799.43496527777</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44832.49594907407</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>44909</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>45086.7037037037</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>44599.42277777778</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45744</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>45366.42888888889</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45341</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45608</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>44593</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>44593.61355324074</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>45803.36384259259</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45344</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>44946</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>45425.94947916667</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45338.49412037037</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>45664</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>45803.63395833333</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45194.63479166666</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>45762.49243055555</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45805.4094675926</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45721.35173611111</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>45805.41010416667</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>44426</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45148</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45148</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45148</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>44588</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44106</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>44608</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45805.41813657407</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45614</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31444,7 +31444,7 @@
         <v>45805.43402777778</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>45202.4997337963</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>45805.4255787037</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>45323.55914351852</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>45194</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>45511</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>45552</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>45601</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45810.44339120371</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>45809</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>44594</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45638</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>45371</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>45215.44233796297</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>45677</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>45190</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>44629.42423611111</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>45351.54596064815</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45809</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>45809</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>45054.9271875</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>45453.69339120371</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>45810.44299768518</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>45809</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>44960</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>44960.66233796296</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45812.48032407407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>45726</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>45810.45960648148</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>45646.50211805556</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45173</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>44594</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>45194.60876157408</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>44819.62</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45721.34715277778</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>45814</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33576,7 +33576,7 @@
         <v>45813</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45813.46034722222</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45055</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>44553</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>45182</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>45182</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45093.46706018518</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>44126</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
         <v>44130</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>45231</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>44575</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>45097</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45818.57910879629</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45407.69575231482</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>44200</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45188.42052083334</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45231.62840277778</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>44893</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>45369</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44155</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44904</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45817</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>45677</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44659</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45707</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>45820</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>45820</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45817</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45695.8391550926</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>45695.84078703704</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>45358</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>45379</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44912.29869212963</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44209</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44614.69730324074</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>45691</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>45820</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>45443</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>45863.44648148148</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35859,7 +35859,7 @@
         <v>44967.55960648148</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45523</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45821.45905092593</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>45824.43798611111</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>45821.44101851852</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45863.45355324074</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>45721.60894675926</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>45254</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>45705.2953125</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>45775.46377314815</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45202</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45216</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45216</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45173</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45624</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45825.44482638889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45694</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>45825.49060185185</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45827.62096064815</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>44588</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45729</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45729</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45208.4350462963</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>45827.64092592592</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>44512</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45705</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>44159</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>45827.46288194445</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45390</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>44617.48311342593</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45874.705</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45180.40255787037</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>44245</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>45831.42365740741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>45831.42616898148</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45831.73</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>44614.59027777778</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38023,7 +38023,7 @@
         <v>44977</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45446.78256944445</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>44679.68706018518</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45149.56928240741</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>45769.6009375</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38328,7 +38328,7 @@
         <v>45698.65606481482</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>45693</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>45831.46731481481</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>45832.35590277778</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>45831.40671296296</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>45181.36815972222</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>45426</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>44993</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>45832.35545138889</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45831.72686342592</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>44679.66694444444</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>44223</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45874</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>44733</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>45876</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>45182</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39260,7 +39260,7 @@
         <v>45182</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>45876</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>44994</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45175</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>44665</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>45068.58563657408</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45426.34148148148</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39669,7 +39669,7 @@
         <v>45699</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39726,7 +39726,7 @@
         <v>45152</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>45694.49037037037</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>44699</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39907,7 +39907,7 @@
         <v>45363.54878472222</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>44967.80034722222</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40026,7 +40026,7 @@
         <v>44967</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40083,7 +40083,7 @@
         <v>44222</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40140,7 +40140,7 @@
         <v>45225.46480324074</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>44929</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40254,7 +40254,7 @@
         <v>45131</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>45880.68200231482</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>45730.43966435185</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>45835.62752314815</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>45880.32907407408</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>45614</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>45259</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>45867.58056712963</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>45236.47697916667</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         <v>45583</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>45877.57847222222</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>45877.62969907407</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>45880.34064814815</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>45042</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>45881.45898148148</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>44608</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>44909.51885416666</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45839</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45299</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45839</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         <v>45881.44938657407</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>45600</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>45267</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41625,7 +41625,7 @@
         <v>45107.53688657407</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45456.59535879629</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41739,7 +41739,7 @@
         <v>45882.37202546297</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41796,7 +41796,7 @@
         <v>45236</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41853,7 +41853,7 @@
         <v>45839</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41910,7 +41910,7 @@
         <v>45821.31292824074</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>45840.68518518518</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>45840</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>45882.52290509259</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>45719.42197916667</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -42200,7 +42200,7 @@
         <v>45719.43646990741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>44799.36695601852</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45841.81555555556</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>45841.5847337963</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45254</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>45321</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>45089</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>45317</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45520</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>45361.57299768519</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45842.74049768518</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>45164.82913194445</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42904,7 +42904,7 @@
         <v>45679</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42961,7 +42961,7 @@
         <v>45351.48662037037</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>44930</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43075,7 +43075,7 @@
         <v>45310</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>45474.41729166666</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>44438</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>45763.52744212963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43313,7 +43313,7 @@
         <v>45152</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43375,7 +43375,7 @@
         <v>45880</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>45845.53202546296</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45091.69766203704</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43546,7 +43546,7 @@
         <v>45890</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>45642</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>45751.32001157408</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>45695.83655092592</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43789,7 +43789,7 @@
         <v>45707</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>45645</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43913,7 +43913,7 @@
         <v>45113</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>45113.80170138889</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -44027,7 +44027,7 @@
         <v>45851.60097222222</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>45851.62179398148</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45757.6997337963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>45757</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45631.44464120371</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45736.45847222222</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>45851.62018518519</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44446,7 +44446,7 @@
         <v>45644.62677083333</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44503,7 +44503,7 @@
         <v>45693</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>45426</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44617,7 +44617,7 @@
         <v>45849.49259259259</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>45852.67366898148</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45852.39642361111</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45852.36871527778</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>45884</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>45852.68978009259</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>44788</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>45761.47540509259</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45761.47748842592</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>45891.46827546296</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45197,7 +45197,7 @@
         <v>45891.4865625</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45852</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45316,7 +45316,7 @@
         <v>45852.72965277778</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45891.33204861111</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45693</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45719.4094212963</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45853.76976851852</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45854.44017361111</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45719.43872685185</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45693</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45896</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45896.57368055556</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>44644.37548611111</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>44817</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45896.61050925926</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45896.57171296296</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45216.39040509259</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45896</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>44400.6750925926</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>44403.3119212963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>45838</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>45838</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46491,7 +46491,7 @@
         <v>45898.46040509259</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45897</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46605,7 +46605,7 @@
         <v>45856.34959490741</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45856</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45478</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>44980</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45838</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46905,7 +46905,7 @@
         <v>45856.34034722222</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>45856.34231481481</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -47029,7 +47029,7 @@
         <v>44508.44033564815</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>45599</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>44519.64902777778</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>45442</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>45642.63524305556</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>45646.61892361111</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45656</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47438,7 +47438,7 @@
         <v>44984.69216435185</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>44379.56163194445</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>45098.63572916666</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>45391.37361111111</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45694</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>45679</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45520</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>44820.47935185185</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>44581.60254629629</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45065.43013888889</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45637</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48090,7 +48090,7 @@
         <v>44532</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>45691</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>44568.67040509259</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48266,7 +48266,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48323,7 +48323,7 @@
         <v>44123</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
         <v>44908.425625</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48437,7 +48437,7 @@
         <v>45691</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48494,7 +48494,7 @@
         <v>45719.43755787037</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48556,7 +48556,7 @@
         <v>45054.95675925926</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>44358.63490740741</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48670,7 +48670,7 @@
         <v>45047.31793981481</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>44888</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48789,7 +48789,7 @@
         <v>44949.4708912037</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48846,7 +48846,7 @@
         <v>44403.29719907408</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>44207</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45127</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -49027,7 +49027,7 @@
         <v>44379.5745949074</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49084,7 +49084,7 @@
         <v>44946.43564814814</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49141,7 +49141,7 @@
         <v>45033</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49198,7 +49198,7 @@
         <v>44531</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49255,7 +49255,7 @@
         <v>45048.55349537037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>44848</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49369,7 +49369,7 @@
         <v>45259</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49426,7 +49426,7 @@
         <v>44105</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>44209</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49545,7 +49545,7 @@
         <v>44273</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49602,7 +49602,7 @@
         <v>44960.65061342593</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>44960</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49716,7 +49716,7 @@
         <v>44593.64863425926</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49778,7 +49778,7 @@
         <v>44928</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>45223</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49897,7 +49897,7 @@
         <v>44420</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45552</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
         <v>44993</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50068,7 +50068,7 @@
         <v>45121</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50130,7 +50130,7 @@
         <v>45714.55368055555</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>44819.50233796296</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50249,7 +50249,7 @@
         <v>44616</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>44886</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50363,7 +50363,7 @@
         <v>45723.63290509259</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50420,7 +50420,7 @@
         <v>45763.52995370371</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>44560</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50534,7 +50534,7 @@
         <v>44600</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50596,7 +50596,7 @@
         <v>44623.41775462963</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50658,7 +50658,7 @@
         <v>44623.5571875</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50720,7 +50720,7 @@
         <v>45167.3721412037</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50777,7 +50777,7 @@
         <v>44531</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50834,7 +50834,7 @@
         <v>44965</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50891,7 +50891,7 @@
         <v>44965</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50948,7 +50948,7 @@
         <v>45308.63298611111</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -51005,7 +51005,7 @@
         <v>44532</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51062,7 +51062,7 @@
         <v>45212.34997685185</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51119,7 +51119,7 @@
         <v>44886.5928125</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51176,7 +51176,7 @@
         <v>45293</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51233,7 +51233,7 @@
         <v>45181.58055555556</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51295,7 +51295,7 @@
         <v>45670</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>44742</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>45757.67611111111</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51476,7 +51476,7 @@
         <v>45078</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>44378.56137731481</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51595,7 +51595,7 @@
         <v>45231</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51652,7 +51652,7 @@
         <v>45341</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51714,7 +51714,7 @@
         <v>44123</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51771,7 +51771,7 @@
         <v>45594</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51833,7 +51833,7 @@
         <v>44139</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51890,7 +51890,7 @@
         <v>45202</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51947,7 +51947,7 @@
         <v>45300.55028935185</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -52004,7 +52004,7 @@
         <v>45638</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52061,7 +52061,7 @@
         <v>44900.54711805555</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>45580</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52175,7 +52175,7 @@
         <v>44944</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52232,7 +52232,7 @@
         <v>45097</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52289,7 +52289,7 @@
         <v>45555.5727662037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52346,7 +52346,7 @@
         <v>45295</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>44168.55746527778</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>44969</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>44944</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45601</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>45154.35092592592</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52693,7 +52693,7 @@
         <v>44652</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52750,7 +52750,7 @@
         <v>45678</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52807,7 +52807,7 @@
         <v>45554</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52864,7 +52864,7 @@
         <v>44679</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52921,7 +52921,7 @@
         <v>45757</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52978,7 +52978,7 @@
         <v>44816</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53035,7 +53035,7 @@
         <v>45763.6503125</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53092,7 +53092,7 @@
         <v>45316</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53154,7 +53154,7 @@
         <v>45317</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53211,7 +53211,7 @@
         <v>45656</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45694</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>44806</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>45307</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45104.6828125</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45642</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>45049.66025462963</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>44574</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53677,7 +53677,7 @@
         <v>44645.39157407408</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53739,7 +53739,7 @@
         <v>44497.4666087963</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53796,7 +53796,7 @@
         <v>45152</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>44964.65261574074</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53910,7 +53910,7 @@
         <v>44599.44832175926</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53967,7 +53967,7 @@
         <v>45638</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -54024,7 +54024,7 @@
         <v>45000.44666666666</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>45762.61341435185</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54138,7 +54138,7 @@
         <v>45713.44519675926</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54195,7 +54195,7 @@
         <v>45327.61831018519</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54252,7 +54252,7 @@
         <v>45352</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         <v>44944</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54366,7 +54366,7 @@
         <v>45266</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54423,7 +54423,7 @@
         <v>44872</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         <v>45513.51815972223</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54542,7 +54542,7 @@
         <v>45617.59006944444</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54599,7 +54599,7 @@
         <v>45049</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54656,7 +54656,7 @@
         <v>44560</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54713,7 +54713,7 @@
         <v>45336.53908564815</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54770,7 +54770,7 @@
         <v>45614.67020833334</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54827,7 +54827,7 @@
         <v>45770.61341435185</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>45677.39440972222</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>45169</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -55008,7 +55008,7 @@
         <v>45244.52202546296</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55070,7 +55070,7 @@
         <v>45435.34778935185</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55132,7 +55132,7 @@
         <v>45763</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55189,7 +55189,7 @@
         <v>45548.42854166667</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55246,7 +55246,7 @@
         <v>44532</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55303,7 +55303,7 @@
         <v>45190</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55360,7 +55360,7 @@
         <v>44977</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55417,7 +55417,7 @@
         <v>45336.54270833333</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55474,7 +55474,7 @@
         <v>45110</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55531,7 +55531,7 @@
         <v>45194</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55593,7 +55593,7 @@
         <v>45474</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55650,7 +55650,7 @@
         <v>45611</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45300.55680555556</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>45589</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>45589</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>44609.60171296296</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55940,7 +55940,7 @@
         <v>44503</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55997,7 +55997,7 @@
         <v>44624.35083333333</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56059,7 +56059,7 @@
         <v>45456.58491898148</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56116,7 +56116,7 @@
         <v>44897</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56173,7 +56173,7 @@
         <v>45729</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56230,7 +56230,7 @@
         <v>45729</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56287,7 +56287,7 @@
         <v>45327</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56344,7 +56344,7 @@
         <v>45014</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56401,7 +56401,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>44593</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>45685.5778125</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56572,7 +56572,7 @@
         <v>45695.59805555556</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45460</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56696,7 +56696,7 @@
         <v>45345.56</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>44914.67600694444</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56810,7 +56810,7 @@
         <v>45061</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56867,7 +56867,7 @@
         <v>44210</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>45583.47836805556</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56986,7 +56986,7 @@
         <v>44912</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>44967.78984953704</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>45075.51982638889</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>45349</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>45720.60410879629</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45699</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>45733.63099537037</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57385,7 +57385,7 @@
         <v>45426.61569444444</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57442,7 +57442,7 @@
         <v>45478.60802083334</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57504,7 +57504,7 @@
         <v>45719.40723379629</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -57566,7 +57566,7 @@
         <v>45154.34931712963</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -567,7 +567,7 @@
         <v>45603</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>45812.47355324074</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>45882.73309027778</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>45548</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>45827.64737268518</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>44377</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45313</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45082</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>45882.47538194444</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>45715.38824074074</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>45728</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45812.55136574074</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>44971</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>45803.55260416667</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>45803.55737268519</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45086</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44222</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>45202</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>44623</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44575</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45812</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>45758</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>44356</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45196</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>44180</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45442</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45092</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44497</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45799.60315972222</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>44792</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>45803.61035879629</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44532</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>44351</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>45316</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44574</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45107</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>45736.53695601852</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>45097</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>44719</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44664</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>44974</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>45442</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>45841.64539351852</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44659</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>44740</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>45371</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>44791</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>45090</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45803.55535879629</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>44684</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>45831.55982638889</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>44495</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>45694.55559027778</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>45222</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45035.44672453704</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>45474</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>45803.61554398148</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>45715.38105324074</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>45762.62260416667</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>44489</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>45841.80690972223</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>45293</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>45189</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>45168.50667824074</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44967</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44614</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44379</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>44651</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>45694.49650462963</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>45783</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>44963</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>45464</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>45687</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>44081</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44909</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>45273</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>45107</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45167</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>45805.41232638889</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>45098</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>44673.47858796296</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>45811.38710648148</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>45679</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>45818.60254629629</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>45817.34614583333</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>45817</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>45736.49902777778</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45820.84516203704</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44897</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>45358</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>45874.69282407407</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>44645</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>45874</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>45763.52524305556</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>44958</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>45336</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>45665</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>44917.59298611111</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>45896.47487268518</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>45314.55579861111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>44849</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>44467</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>45757.49934027778</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>44917</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>44855</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45107</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>45762.57244212963</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>45385</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>44144</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>44119</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>44583.61803240741</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44602</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>44602</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>44517</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>44567.81241898148</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>44407</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>44544</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>44526</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44489</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>44609.61430555556</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44083</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>44583.62121527778</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>44323.58961805556</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>44299</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44714</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44491.50769675926</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>44252</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>44486</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>44662.56783564815</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>44569.5340625</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>44659.70381944445</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>44572.39640046296</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>44230</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>44603</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>44494</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>44700</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>44839</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44784</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         <v>44369.65428240741</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>44612</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>44720</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44886</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>44598</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>44883.56321759259</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>44314</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>44610</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>44865.43494212963</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>44167</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>44357</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>44742</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>44704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>44533.4678587963</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>44764</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44453</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>44297</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44153</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>44351</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>44349.49666666667</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>44584.63190972222</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>44609</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>44490.64313657407</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>44091</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>44610</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44281.4499537037</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>44512</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>44335.52201388889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>44740.68142361111</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>44816</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>44297</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44722.30703703704</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>44705.78475694444</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44705.83326388889</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>44692.87630787037</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>44698.67151620371</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>44328.57100694445</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44277.65263888889</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44369</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44750.678125</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>44599.43265046296</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>44543</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>44461</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>44383</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>44685.6212037037</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44378.69857638889</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>44702.70721064815</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44865</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>44461.73350694445</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>44442.35195601852</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44442</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>44504.59193287037</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>44643.51446759259</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44750.45800925926</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44076</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44593</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44733.43420138889</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44095</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>44711</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44846</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>44551.59704861111</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>44743</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>44134</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44446.47693287037</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44571.44563657408</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44103</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44838.40635416667</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44459</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>44623.4572337963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>44491.54116898148</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44479</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44676</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44489</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>44543.34697916666</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>44476.61263888889</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>44160</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>44847.35622685185</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>44517</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>44495</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>44705.84535879629</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44729</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44634</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44144</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44266.57917824074</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44886.58890046296</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44522.55518518519</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44294.37555555555</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>44659.57912037037</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>44791.38336805555</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>44649</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>44799.36359953704</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>44623</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>44762</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>44847</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>44798</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>45723</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>44583.61555555555</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>44144</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>44575</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>45208.46130787037</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>45119</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>44859.36896990741</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>44328</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>44832</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45050.49392361111</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>44966</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>44575.4366087963</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44883</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>44866</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>45699.71063657408</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45729</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>44501.71344907407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>45743.50744212963</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>45756.44024305556</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45756.50738425926</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>45187.61136574074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45175.57060185185</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45695.59197916667</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45371.50738425926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45741.45114583334</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>45644.47723379629</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>45006</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45644</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>45307</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>44548</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45614</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44550.37994212963</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45327</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>44847</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45300</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45670</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44980</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>45259.52809027778</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>44446</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45096</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>45776.48275462963</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45776</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45776.45263888889</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45107.55574074074</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>45776.6415162037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45254.49552083333</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45611</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45777.37119212963</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45777.34894675926</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>45777.32731481481</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45777.52655092593</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>45777</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>45520</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>44831</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>45574</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45344.64759259259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45779.6665162037</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>45758</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45779.65787037037</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>44809.92752314815</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>44810</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>45107</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>45107</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45107</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45344.69567129629</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>44816</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>44371.49178240741</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45779.49085648148</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45133</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45096</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45098.62966435185</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45783.61053240741</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>44544</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>44519</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>44395</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45335</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>45293</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>45163.59913194444</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>45784.57266203704</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>45096</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>44569.49344907407</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45407.49721064815</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45294.5666550926</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45784.80497685185</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45329</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45177.79766203704</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>44095</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>44551.76711805556</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45327</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45558.42498842593</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>45562</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45368.64787037037</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>44553</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>44569.69358796296</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45231.54601851852</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45684</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>45259</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45259</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>45254</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>45310.53418981482</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44603</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45161</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44883</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>44849</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>45524</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44629.57741898148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45468</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45037</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45726</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>45371.67368055556</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>45790.51040509259</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>45134.57021990741</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>45091</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>45790.44972222222</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>45583.48449074074</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>44533.46665509259</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>45584.60038194444</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45625.58501157408</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>45790.51186342593</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>44894.57065972222</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>45021.29524305555</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>45583</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>45583</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>44535</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>44637.35744212963</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>45036</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>45624</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>45341</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45162</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>45159.44694444445</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>45145</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>45201.62318287037</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>45358</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44522</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44616</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>45181.33571759259</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>44516</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>45525</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>45341.63811342593</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>45335.66331018518</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>45195.64807870371</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>44935</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>45177.56940972222</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45614.65928240741</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45636</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>44277.65650462963</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>45736.60863425926</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>44504</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>45490</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44435.38657407407</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>44602</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>45439</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45429</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>45763</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>45797.45900462963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>44977</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>45644</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45159.45748842593</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45798.42252314815</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45798.41734953703</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45797.42777777778</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45643</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45799.53348379629</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>44678.3315625</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>44610</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>45615</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>45693</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44131</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45638</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>44624.64538194444</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45618.71140046296</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45799.53803240741</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45799.5421875</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44637.56178240741</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>45799.57714120371</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>45799.64877314815</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45799.67806712963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>45733.62903935185</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>45644</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>45799.68190972223</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45188</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45453</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45799.53947916667</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>45799.54104166666</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>44140</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45524</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>44109</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>45737.40503472222</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>44967</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>45799.65021990741</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>45799.6527199074</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>45799.43496527777</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44832.49594907407</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>44909</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>45086.7037037037</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>44599.42277777778</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45744</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>45366.42888888889</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45341</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45608</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>44593</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>44593.61355324074</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>45803.36384259259</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45344</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>44946</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>45425.94947916667</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45338.49412037037</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>45664</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>45803.63395833333</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45194.63479166666</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>45762.49243055555</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45805.4094675926</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45721.35173611111</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>45805.41010416667</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>44426</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45148</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45148</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45148</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>44588</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44106</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>44608</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45805.41813657407</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45614</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31444,7 +31444,7 @@
         <v>45805.43402777778</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>45202.4997337963</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>45805.4255787037</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>45323.55914351852</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>45194</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>45511</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>45552</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>45601</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45810.44339120371</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>45809</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>44594</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45638</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>45371</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>45215.44233796297</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>45677</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>45190</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>44629.42423611111</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>45351.54596064815</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45809</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>45809</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>45054.9271875</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>45453.69339120371</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>45810.44299768518</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>45809</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>44960</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>44960.66233796296</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45812.48032407407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>45726</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>45810.45960648148</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>45646.50211805556</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45173</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>44594</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>45194.60876157408</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>44819.62</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45721.34715277778</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>45814</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33576,7 +33576,7 @@
         <v>45813</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45813.46034722222</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45055</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>44553</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>45182</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>45182</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45093.46706018518</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>44126</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
         <v>44130</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>45231</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>44575</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>45097</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45818.57910879629</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45407.69575231482</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>44200</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45188.42052083334</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45231.62840277778</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>44893</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>45369</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44155</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44904</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45817</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>45677</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44659</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45707</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>45820</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>45820</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45817</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45695.8391550926</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>45695.84078703704</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>45358</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>45379</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44912.29869212963</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44209</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44614.69730324074</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>45691</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>45820</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>45443</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>45863.44648148148</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35859,7 +35859,7 @@
         <v>44967.55960648148</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45523</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45821.45905092593</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>45824.43798611111</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>45821.44101851852</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45863.45355324074</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>45721.60894675926</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>45254</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>45705.2953125</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>45775.46377314815</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45202</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45216</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45216</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45173</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45624</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45825.44482638889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45694</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>45825.49060185185</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45827.62096064815</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>44588</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45729</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45729</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45208.4350462963</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>45827.64092592592</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>44512</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45705</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>44159</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>45827.46288194445</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45390</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>44617.48311342593</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45874.705</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45180.40255787037</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>44245</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>45831.42365740741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>45831.42616898148</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45831.73</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>44614.59027777778</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38023,7 +38023,7 @@
         <v>44977</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45446.78256944445</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>44679.68706018518</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45149.56928240741</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>45769.6009375</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38328,7 +38328,7 @@
         <v>45698.65606481482</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>45693</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>45831.46731481481</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>45832.35590277778</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>45831.40671296296</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>45181.36815972222</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>45426</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>44993</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>45832.35545138889</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45831.72686342592</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>44679.66694444444</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>44223</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45874</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>44733</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>45876</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>45182</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39260,7 +39260,7 @@
         <v>45182</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>45876</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>44994</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45175</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>44665</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>45068.58563657408</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45426.34148148148</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39669,7 +39669,7 @@
         <v>45699</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39726,7 +39726,7 @@
         <v>45152</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>45694.49037037037</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>44699</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39907,7 +39907,7 @@
         <v>45363.54878472222</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>44967.80034722222</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40026,7 +40026,7 @@
         <v>44967</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40083,7 +40083,7 @@
         <v>44222</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40140,7 +40140,7 @@
         <v>45225.46480324074</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>44929</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40254,7 +40254,7 @@
         <v>45131</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>45880.68200231482</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>45730.43966435185</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>45835.62752314815</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>45880.32907407408</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>45614</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>45259</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>45867.58056712963</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>45236.47697916667</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         <v>45583</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>45877.57847222222</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>45877.62969907407</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>45880.34064814815</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>45042</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>45881.45898148148</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>44608</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>44909.51885416666</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45839</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45299</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45839</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         <v>45881.44938657407</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>45600</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>45267</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41625,7 +41625,7 @@
         <v>45107.53688657407</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45456.59535879629</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41739,7 +41739,7 @@
         <v>45882.37202546297</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41796,7 +41796,7 @@
         <v>45236</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41853,7 +41853,7 @@
         <v>45839</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41910,7 +41910,7 @@
         <v>45821.31292824074</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>45840.68518518518</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>45840</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>45882.52290509259</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>45719.42197916667</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -42200,7 +42200,7 @@
         <v>45719.43646990741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>44799.36695601852</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45841.81555555556</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>45841.5847337963</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45254</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>45321</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>45089</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>45317</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45520</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>45361.57299768519</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45842.74049768518</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>45164.82913194445</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42904,7 +42904,7 @@
         <v>45679</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42961,7 +42961,7 @@
         <v>45351.48662037037</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>44930</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43075,7 +43075,7 @@
         <v>45310</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>45474.41729166666</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>44438</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>45763.52744212963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43313,7 +43313,7 @@
         <v>45152</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43375,7 +43375,7 @@
         <v>45880</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>45845.53202546296</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45091.69766203704</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43546,7 +43546,7 @@
         <v>45890</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>45642</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>45751.32001157408</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>45695.83655092592</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43789,7 +43789,7 @@
         <v>45707</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>45645</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43913,7 +43913,7 @@
         <v>45113</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>45113.80170138889</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -44027,7 +44027,7 @@
         <v>45851.60097222222</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>45851.62179398148</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45757.6997337963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>45757</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45631.44464120371</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45736.45847222222</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>45851.62018518519</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44446,7 +44446,7 @@
         <v>45644.62677083333</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44503,7 +44503,7 @@
         <v>45693</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>45426</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44617,7 +44617,7 @@
         <v>45849.49259259259</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>45852.67366898148</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45852.39642361111</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45852.36871527778</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>45884</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>45852.68978009259</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>44788</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>45761.47540509259</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45761.47748842592</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>45891.46827546296</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45197,7 +45197,7 @@
         <v>45891.4865625</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45852</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45316,7 +45316,7 @@
         <v>45852.72965277778</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45891.33204861111</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45693</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45719.4094212963</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45853.76976851852</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45854.44017361111</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45719.43872685185</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45693</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45896</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45896.57368055556</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>44644.37548611111</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>44817</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45896.61050925926</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45896.57171296296</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45216.39040509259</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45896</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>44400.6750925926</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>44403.3119212963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>45838</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>45838</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46491,7 +46491,7 @@
         <v>45898.46040509259</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45897</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46605,7 +46605,7 @@
         <v>45856.34959490741</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45856</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45478</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>44980</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45838</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46905,7 +46905,7 @@
         <v>45856.34034722222</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>45856.34231481481</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -47029,7 +47029,7 @@
         <v>44508.44033564815</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>45599</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>44519.64902777778</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>45442</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>45642.63524305556</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>45646.61892361111</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45656</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47438,7 +47438,7 @@
         <v>44984.69216435185</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>44379.56163194445</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>45098.63572916666</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>45391.37361111111</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45694</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>45679</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45520</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>44820.47935185185</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>44581.60254629629</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45065.43013888889</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45637</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48090,7 +48090,7 @@
         <v>44532</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>45691</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>44568.67040509259</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48266,7 +48266,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48323,7 +48323,7 @@
         <v>44123</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
         <v>44908.425625</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48437,7 +48437,7 @@
         <v>45691</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48494,7 +48494,7 @@
         <v>45719.43755787037</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48556,7 +48556,7 @@
         <v>45054.95675925926</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>44358.63490740741</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48670,7 +48670,7 @@
         <v>45047.31793981481</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>44888</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48789,7 +48789,7 @@
         <v>44949.4708912037</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48846,7 +48846,7 @@
         <v>44403.29719907408</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>44207</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45127</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -49027,7 +49027,7 @@
         <v>44379.5745949074</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49084,7 +49084,7 @@
         <v>44946.43564814814</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49141,7 +49141,7 @@
         <v>45033</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49198,7 +49198,7 @@
         <v>44531</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49255,7 +49255,7 @@
         <v>45048.55349537037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>44848</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49369,7 +49369,7 @@
         <v>45259</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49426,7 +49426,7 @@
         <v>44105</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>44209</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49545,7 +49545,7 @@
         <v>44273</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49602,7 +49602,7 @@
         <v>44960.65061342593</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>44960</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49716,7 +49716,7 @@
         <v>44593.64863425926</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49778,7 +49778,7 @@
         <v>44928</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>45223</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49897,7 +49897,7 @@
         <v>44420</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45552</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
         <v>44993</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50068,7 +50068,7 @@
         <v>45121</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50130,7 +50130,7 @@
         <v>45714.55368055555</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>44819.50233796296</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50249,7 +50249,7 @@
         <v>44616</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>44886</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50363,7 +50363,7 @@
         <v>45723.63290509259</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50420,7 +50420,7 @@
         <v>45763.52995370371</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>44560</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50534,7 +50534,7 @@
         <v>44600</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50596,7 +50596,7 @@
         <v>44623.41775462963</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50658,7 +50658,7 @@
         <v>44623.5571875</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50720,7 +50720,7 @@
         <v>45167.3721412037</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50777,7 +50777,7 @@
         <v>44531</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50834,7 +50834,7 @@
         <v>44965</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50891,7 +50891,7 @@
         <v>44965</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50948,7 +50948,7 @@
         <v>45308.63298611111</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -51005,7 +51005,7 @@
         <v>44532</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51062,7 +51062,7 @@
         <v>45212.34997685185</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51119,7 +51119,7 @@
         <v>44886.5928125</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51176,7 +51176,7 @@
         <v>45293</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51233,7 +51233,7 @@
         <v>45181.58055555556</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51295,7 +51295,7 @@
         <v>45670</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>44742</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>45757.67611111111</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51476,7 +51476,7 @@
         <v>45078</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>44378.56137731481</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51595,7 +51595,7 @@
         <v>45231</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51652,7 +51652,7 @@
         <v>45341</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51714,7 +51714,7 @@
         <v>44123</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51771,7 +51771,7 @@
         <v>45594</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51833,7 +51833,7 @@
         <v>44139</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51890,7 +51890,7 @@
         <v>45202</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51947,7 +51947,7 @@
         <v>45300.55028935185</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -52004,7 +52004,7 @@
         <v>45638</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52061,7 +52061,7 @@
         <v>44900.54711805555</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>45580</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52175,7 +52175,7 @@
         <v>44944</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52232,7 +52232,7 @@
         <v>45097</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52289,7 +52289,7 @@
         <v>45555.5727662037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52346,7 +52346,7 @@
         <v>45295</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>44168.55746527778</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>44969</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>44944</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45601</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>45154.35092592592</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52693,7 +52693,7 @@
         <v>44652</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52750,7 +52750,7 @@
         <v>45678</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52807,7 +52807,7 @@
         <v>45554</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52864,7 +52864,7 @@
         <v>44679</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52921,7 +52921,7 @@
         <v>45757</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52978,7 +52978,7 @@
         <v>44816</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53035,7 +53035,7 @@
         <v>45763.6503125</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53092,7 +53092,7 @@
         <v>45316</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53154,7 +53154,7 @@
         <v>45317</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53211,7 +53211,7 @@
         <v>45656</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45694</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>44806</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>45307</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45104.6828125</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45642</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>45049.66025462963</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>44574</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53677,7 +53677,7 @@
         <v>44645.39157407408</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53739,7 +53739,7 @@
         <v>44497.4666087963</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53796,7 +53796,7 @@
         <v>45152</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>44964.65261574074</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53910,7 +53910,7 @@
         <v>44599.44832175926</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53967,7 +53967,7 @@
         <v>45638</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -54024,7 +54024,7 @@
         <v>45000.44666666666</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>45762.61341435185</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54138,7 +54138,7 @@
         <v>45713.44519675926</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54195,7 +54195,7 @@
         <v>45327.61831018519</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54252,7 +54252,7 @@
         <v>45352</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         <v>44944</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54366,7 +54366,7 @@
         <v>45266</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54423,7 +54423,7 @@
         <v>44872</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         <v>45513.51815972223</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54542,7 +54542,7 @@
         <v>45617.59006944444</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54599,7 +54599,7 @@
         <v>45049</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54656,7 +54656,7 @@
         <v>44560</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54713,7 +54713,7 @@
         <v>45336.53908564815</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54770,7 +54770,7 @@
         <v>45614.67020833334</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54827,7 +54827,7 @@
         <v>45770.61341435185</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>45677.39440972222</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>45169</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -55008,7 +55008,7 @@
         <v>45244.52202546296</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55070,7 +55070,7 @@
         <v>45435.34778935185</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55132,7 +55132,7 @@
         <v>45763</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55189,7 +55189,7 @@
         <v>45548.42854166667</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55246,7 +55246,7 @@
         <v>44532</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55303,7 +55303,7 @@
         <v>45190</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55360,7 +55360,7 @@
         <v>44977</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55417,7 +55417,7 @@
         <v>45336.54270833333</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55474,7 +55474,7 @@
         <v>45110</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55531,7 +55531,7 @@
         <v>45194</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55593,7 +55593,7 @@
         <v>45474</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55650,7 +55650,7 @@
         <v>45611</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45300.55680555556</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>45589</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>45589</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>44609.60171296296</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55940,7 +55940,7 @@
         <v>44503</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55997,7 +55997,7 @@
         <v>44624.35083333333</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56059,7 +56059,7 @@
         <v>45456.58491898148</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56116,7 +56116,7 @@
         <v>44897</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56173,7 +56173,7 @@
         <v>45729</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56230,7 +56230,7 @@
         <v>45729</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56287,7 +56287,7 @@
         <v>45327</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56344,7 +56344,7 @@
         <v>45014</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56401,7 +56401,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>44593</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>45685.5778125</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56572,7 +56572,7 @@
         <v>45695.59805555556</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45460</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56696,7 +56696,7 @@
         <v>45345.56</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>44914.67600694444</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56810,7 +56810,7 @@
         <v>45061</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56867,7 +56867,7 @@
         <v>44210</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>45583.47836805556</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56986,7 +56986,7 @@
         <v>44912</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>44967.78984953704</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>45075.51982638889</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>45349</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>45720.60410879629</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45699</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>45733.63099537037</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57385,7 +57385,7 @@
         <v>45426.61569444444</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57442,7 +57442,7 @@
         <v>45478.60802083334</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57504,7 +57504,7 @@
         <v>45719.40723379629</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -57566,7 +57566,7 @@
         <v>45154.34931712963</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -567,7 +567,7 @@
         <v>45603</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>45812.47355324074</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>45882.73309027778</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>45548</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>45827.64737268518</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>44377</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45313</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45715.38824074074</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45082</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>45882.47538194444</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>45728</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45812.55136574074</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>44971</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>44623</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>44222</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>45803.55737268519</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45803.55260416667</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45086</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45202</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44575</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45812</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>44356</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45196</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45758</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>44180</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45442</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45092</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44497</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45799.60315972222</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>44792</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>45803.61035879629</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44532</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>44500</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>45316</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45736.53695601852</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>45097</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>45841.64539351852</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>44574</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45107</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44351</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44719</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44664</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>44974</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>45442</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44740</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>45371</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>44659</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44791</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>45090</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>44804</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45803.55535879629</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45831.55982638889</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>44495</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>44684</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>44967</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>45222</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>45762.62260416667</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>45803.61554398148</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>45715.38105324074</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>45694.55559027778</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>45168.50667824074</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>44489</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>45841.80690972223</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>45189</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>45903</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>45293</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45474</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>45035.44672453704</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44614</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>44379</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>44651</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>45358</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>44487</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>45763.52524305556</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>45783</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>45107</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44645</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45336</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45687</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>45665</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>45694.49650462963</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>45805.41232638889</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>45811.38710648148</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>45098</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>45679</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>45817</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>45817.34614583333</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>45818.60254629629</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45736.49902777778</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>45314.55579861111</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>45820.84516203704</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>45874</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>45874.69282407407</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>44917</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>44081</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>44855</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45841.81555555556</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45853.76976851852</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>45896.47487268518</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>45901.66702546296</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>44958</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>44673.47858796296</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>45464</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>44467</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>45762.57244212963</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>45167</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45107</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>44909</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>44897</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>44963</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>45273</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44849</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>45757.49934027778</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45385</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>44917.59298611111</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>44144</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>44119</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>44583.61803240741</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>44602</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>44602</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>44517</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>44567.81241898148</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>44407</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44544</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>44526</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
         <v>44489</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>44083</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>44609.61430555556</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>44583.62121527778</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44323.58961805556</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44299</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>44714</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>44491.50769675926</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>44252</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>44569.5340625</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>44662.56783564815</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>44486</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>44659.70381944445</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>44572.39640046296</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         <v>44230</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>44494</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>44603</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44700</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>44839</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>44784</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>44369.65428240741</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44612</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>44720</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>44886</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>44883.56321759259</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>44598</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>44314</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>44610</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>44865.43494212963</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>44167</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>44357</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44742</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44704</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44533.4678587963</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>44764</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>44453</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>44297</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>44153</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>44351</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>44349.49666666667</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>44584.63190972222</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>44609</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>44490.64313657407</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>44091</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44610</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44281.4499537037</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44512</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44335.52201388889</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44740.68142361111</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>44816</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>44297</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>44722.30703703704</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44705.78475694444</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44705.83326388889</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>44692.87630787037</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>44599.43265046296</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>44543</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>44461</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>44383</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>44378.69857638889</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44865</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>44461.73350694445</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>44685.6212037037</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>44504.59193287037</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44702.70721064815</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>44643.51446759259</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>44593</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>44750.45800925926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44442.35195601852</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>44442</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>44095</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>44846</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>44733.43420138889</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44711</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>44551.59704861111</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44134</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>44446.47693287037</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>44743</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>44571.44563657408</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>44103</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>44491.54116898148</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44676</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44838.40635416667</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44459</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>44623.4572337963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>44476.61263888889</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>44479</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44160</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>44489</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>44517</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>44634</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>44729</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>44543.34697916666</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>44495</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>44144</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>44266.57917824074</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44886.58890046296</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44294.37555555555</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44847.35622685185</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44705.84535879629</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44522.55518518519</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44659.57912037037</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>44791.38336805555</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>44698.67151620371</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>44277.65263888889</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>44649</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44623</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>44762</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>44798</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44144</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>44967.78984953704</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>44637.35744212963</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45615</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>44637.56178240741</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>44799.36359953704</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45695.59805555556</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>44659</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>44847</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>44519</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>44583.61555555555</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44575</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44593</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>44593.61355324074</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>44750.678125</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>45358</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45294.5666550926</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>44209</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>45107.53688657407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>44575.4366087963</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>44928</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45061</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>44328.57100694445</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19699,7 +19699,7 @@
         <v>44369</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45756.44024305556</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45656</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>44977</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45678</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>44893</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45453</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45638</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>44245</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45167.3721412037</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45468</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45776.6415162037</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>45520</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>45777.37119212963</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>44679.66694444444</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>45777</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45107.55574074074</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45776.45263888889</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>45777.52655092593</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45777.34894675926</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44608</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45574</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>44816</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>45119</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21159,7 +21159,7 @@
         <v>45776.48275462963</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45776</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>45763.52995370371</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>44139</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>45777.32731481481</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45316</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45614.65928240741</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>44531</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45694.49037037037</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>45779.49085648148</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45779.6665162037</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45779.65787037037</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45366.42888888889</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         <v>44993</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21992,7 +21992,7 @@
         <v>45783.61053240741</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45351.54596064815</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45344.69567129629</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45694</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>44900.54711805555</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>44872</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>45784.80497685185</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45784.57266203704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45293</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>44379.56163194445</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>44508.44033564815</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>44644.37548611111</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>45775.46377314815</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>45212.34997685185</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>45426.61569444444</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>44532</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45558.42498842593</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>44569.69358796296</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44944</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45093.46706018518</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>45223</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45254</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>45368.64787037037</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>44969</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>45187.61136574074</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>44531</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>44400.6750925926</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44532</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>45033</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45584.60038194444</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>45091</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45371.67368055556</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45684</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>44159</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>45407.49721064815</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45562</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45177.79766203704</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>44944</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>45625.58501157408</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45695.8391550926</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>45161</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>45231</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>45329</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>44569.49344907407</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45169</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>45583.48449074074</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>45216</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>44109</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>45091.69766203704</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>44581.60254629629</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45618.71140046296</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>45548.42854166667</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>44599.42277777778</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>45327</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>44742</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>45583.47836805556</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>44519.64902777778</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>45736.60863425926</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>44980</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25470,7 +25470,7 @@
         <v>45552</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>44123</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>44967</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>45790.44972222222</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45425.94947916667</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>45726</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>45790.51186342593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>45244.52202546296</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>45790.51040509259</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>44095</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>45691</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>45614</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>44960.65061342593</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>44960</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45583</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>45295</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>44568.67040509259</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45054.9271875</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>44859.36896990741</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45369</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45693</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26687,7 +26687,7 @@
         <v>44832</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>45733.63099537037</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26801,7 +26801,7 @@
         <v>45363.54878472222</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>45601</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>44809.92752314815</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>45133</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>45638</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -27091,7 +27091,7 @@
         <v>45490</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         <v>45195.64807870371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>45523</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>44645.39157407408</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>45371.50738425926</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>44616</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45743.50744212963</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45439</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>45335.66331018518</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>45624</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>45042</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45300.55028935185</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45636</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>45797.42777777778</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>45047.31793981481</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44277.65650462963</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>44624.64538194444</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44617.48311342593</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>45797.45900462963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45107</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>45107</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45525</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45429</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45327</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>45050.49392361111</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45799.53803240741</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>45037</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45799.53348379629</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>45799.68190972223</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>44949.4708912037</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45799.67806712963</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>45798.41734953703</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>45799.57714120371</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45300</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>44533.46665509259</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>44200</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45733.62903935185</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>45162</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>45154.35092592592</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>45799.65021990741</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45799.6527199074</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29503,7 +29503,7 @@
         <v>45737.40503472222</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>45693</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>45149.56928240741</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>45799.53947916667</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45799.54104166666</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29803,7 +29803,7 @@
         <v>44395</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         <v>45691</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>45693</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45799.43496527777</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>45799.5421875</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44548</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>45799.64877314815</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>44849</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45798.42252314815</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>45677</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>45757.6997337963</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45757</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45617.59006944444</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>44594</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>44977</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>45078</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45721.60894675926</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>45803.36384259259</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>45086.7037037037</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>45555.5727662037</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45803.63395833333</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45608</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45341</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45762.49243055555</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45744</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45182</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>45182</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31377,7 +31377,7 @@
         <v>44273</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>44993</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>44616</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>45805.4094675926</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>44106</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>45068.58563657408</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31724,7 +31724,7 @@
         <v>45719.40723379629</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>45644</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>45644</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>44929</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>44105</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45805.41813657407</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>45805.4255787037</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>45646.50211805556</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>45055</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>45805.43402777778</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>44912</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32376,7 +32376,7 @@
         <v>44847</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45805.41010416667</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>45611</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>45601</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45698.65606481482</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45407.69575231482</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>45307</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>44544</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45159.45748842593</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>45624</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44512</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45809</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>45215.44233796297</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>45810.44339120371</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>45097</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>45719.43755787037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>45809</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44131</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>45127</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33489,7 +33489,7 @@
         <v>45216</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>45810.45960648148</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>45809</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>44909</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33732,7 +33732,7 @@
         <v>45809</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>45453.69339120371</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45511</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45810.44299768518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33975,7 +33975,7 @@
         <v>45182</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>45614</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>45145</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>44904</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>44140</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34270,7 +34270,7 @@
         <v>45812.48032407407</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>44551.76711805556</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34389,7 +34389,7 @@
         <v>45813.46034722222</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45813</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34503,7 +34503,7 @@
         <v>44130</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>44426</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45236.47697916667</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45341</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34736,7 +34736,7 @@
         <v>45721.34715277778</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34793,7 +34793,7 @@
         <v>45814</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>44819.50233796296</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34912,7 +34912,7 @@
         <v>45726</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45006</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>45664</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>45202</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>45817</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45474.41729166666</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>44946</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>44522</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>45818.57910879629</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45817</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44600</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>45456.59535879629</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>45694</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>44806</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>44593.64863425926</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>45338.49412037037</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>45236</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>45152</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45299</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>44126</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44403.29719907408</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45820</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>44883</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>45820</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>45820</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>45821.44101851852</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>45642</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>45307</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>45351.48662037037</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45371</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>45824.43798611111</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>45825.49060185185</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45825.44482638889</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>45821.45905092593</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>44799.36695601852</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>45827.64092592592</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>45827.46288194445</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45827.62096064815</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45831.40671296296</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>45831.72686342592</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>45831.73</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45831.42365740741</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45831.42616898148</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45202.4997337963</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37505,7 +37505,7 @@
         <v>45832.35545138889</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>44602</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>45832.35590277778</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37686,7 +37686,7 @@
         <v>45164.82913194445</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>45874.705</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>45874</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37862,7 +37862,7 @@
         <v>44358.63490740741</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>45877.57847222222</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37976,7 +37976,7 @@
         <v>45877.62969907407</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>45876</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>45835.62752314815</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>45876</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45880.68200231482</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>44908.425625</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>45880.32907407408</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>45163.59913194444</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45181.58055555556</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>45821.31292824074</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>45839</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>45881.44938657407</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>45880.34064814815</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45867.58056712963</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>45839</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38841,7 +38841,7 @@
         <v>45881.45898148148</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>45839</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>45841.5847337963</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45840</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>45882.52290509259</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>45208.4350462963</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>45065.43013888889</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39260,7 +39260,7 @@
         <v>45426.34148148148</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>45882.37202546297</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>45840.68518518518</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>44371.49178240741</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>45842.74049768518</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>45152</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39607,7 +39607,7 @@
         <v>45679</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>45134.57021990741</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39726,7 +39726,7 @@
         <v>45723</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>44866</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39840,7 +39840,7 @@
         <v>45152</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>45763.52744212963</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39954,7 +39954,7 @@
         <v>45699</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>45845.53202546296</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -40068,7 +40068,7 @@
         <v>44967.80034722222</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>44967</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>45884</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40239,7 +40239,7 @@
         <v>45341.63811342593</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>45890</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>45446.78256944445</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>45891.33204861111</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40477,7 +40477,7 @@
         <v>44210</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40534,7 +40534,7 @@
         <v>45631.44464120371</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40591,7 +40591,7 @@
         <v>45849.49259259259</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>45891.46827546296</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>45644.62677083333</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40762,7 +40762,7 @@
         <v>45852.39642361111</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>45426</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40876,7 +40876,7 @@
         <v>45852.72965277778</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40938,7 +40938,7 @@
         <v>45852</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45524</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>44503</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>45851.62018518519</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41181,7 +41181,7 @@
         <v>45852.68978009259</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41243,7 +41243,7 @@
         <v>45852.67366898148</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>45852.36871527778</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>45851.60097222222</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45896.61050925926</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45896</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45896</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>45896.57368055556</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45897</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45854.44017361111</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41771,7 +41771,7 @@
         <v>45896.57171296296</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>45000.44666666666</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41885,7 +41885,7 @@
         <v>44966</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>45188</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>45856.34034722222</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -42071,7 +42071,7 @@
         <v>45856.34231481481</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45901.41853009259</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>45177.56940972222</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44560</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>45901.67194444445</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>45898.46040509259</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>45901.41756944444</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>45856.34959490741</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>45856</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>45903.69358796296</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42671,7 +42671,7 @@
         <v>45838</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42728,7 +42728,7 @@
         <v>45902.42243055555</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>45880</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>45903.69096064815</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>45036</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>45838</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -43023,7 +43023,7 @@
         <v>45720.60410879629</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>45838</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45344</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43199,7 +43199,7 @@
         <v>45677.39440972222</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>45904.34862268518</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -43313,7 +43313,7 @@
         <v>45863.44648148148</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
         <v>45831.46731481481</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43427,7 +43427,7 @@
         <v>45021.29524305555</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45904.77746527778</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43546,7 +43546,7 @@
         <v>44699</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>44817</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>44831</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>45903</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>44629.42423611111</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43836,7 +43836,7 @@
         <v>45891.4865625</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45188.42052083334</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>45721.35173611111</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>44886</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>45905.64862268518</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -44121,7 +44121,7 @@
         <v>45905.5756712963</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>44516</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>44574</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -44292,7 +44292,7 @@
         <v>45863.45355324074</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44349,7 +44349,7 @@
         <v>45300.55680555556</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44406,7 +44406,7 @@
         <v>44155</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44463,7 +44463,7 @@
         <v>45096</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44520,7 +44520,7 @@
         <v>45905.62541666667</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
         <v>45580</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>45293</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>45656</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45851.62179398148</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44820,7 +44820,7 @@
         <v>45757.67611111111</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44877,7 +44877,7 @@
         <v>45208.46130787037</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>45905.62641203704</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44996,7 +44996,7 @@
         <v>44560</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -45053,7 +45053,7 @@
         <v>44446</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -45110,7 +45110,7 @@
         <v>45173</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45167,7 +45167,7 @@
         <v>44594</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45224,7 +45224,7 @@
         <v>45552</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45281,7 +45281,7 @@
         <v>45426</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45338,7 +45338,7 @@
         <v>44912.29869212963</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>45194</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45457,7 +45457,7 @@
         <v>45231</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>44967.55960648148</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>44886.5928125</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>45520</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>44614.59027777778</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45742,7 +45742,7 @@
         <v>45201.62318287037</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>44930</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45098.62966435185</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>45756.50738425926</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>44810</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45014</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45175</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46146,7 +46146,7 @@
         <v>45474</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>45194</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46265,7 +46265,7 @@
         <v>45442</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>45121</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46384,7 +46384,7 @@
         <v>44819.62</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46441,7 +46441,7 @@
         <v>45614</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46498,7 +46498,7 @@
         <v>45335</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45341</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46622,7 +46622,7 @@
         <v>45729</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>45637</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>45391.37361111111</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46798,7 +46798,7 @@
         <v>45714.55368055555</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>45719.42197916667</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46917,7 +46917,7 @@
         <v>45719.43646990741</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46979,7 +46979,7 @@
         <v>44832.49594907407</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>45317</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>45254</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47150,7 +47150,7 @@
         <v>45763</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47207,7 +47207,7 @@
         <v>44935</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47264,7 +47264,7 @@
         <v>45222</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47321,7 +47321,7 @@
         <v>45216.39040509259</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47378,7 +47378,7 @@
         <v>45695.83655092592</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47440,7 +47440,7 @@
         <v>45638</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47497,7 +47497,7 @@
         <v>44678.3315625</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47559,7 +47559,7 @@
         <v>44501.71344907407</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47621,7 +47621,7 @@
         <v>44588</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>45259</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         <v>45231.62840277778</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>44168.55746527778</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>45705</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45259.52809027778</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>44914.67600694444</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -48025,7 +48025,7 @@
         <v>44984.69216435185</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>44379.5745949074</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>44207</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45642</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>45390</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>45524</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48387,7 +48387,7 @@
         <v>45190</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48444,7 +48444,7 @@
         <v>44623.5571875</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48506,7 +48506,7 @@
         <v>45054.95675925926</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48563,7 +48563,7 @@
         <v>44960</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48620,7 +48620,7 @@
         <v>44960.66233796296</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48677,7 +48677,7 @@
         <v>44575</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>44994</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>44679.68706018518</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
         <v>45643</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48910,7 +48910,7 @@
         <v>45736.45847222222</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48972,7 +48972,7 @@
         <v>44733</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -49029,7 +49029,7 @@
         <v>44532</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -49086,7 +49086,7 @@
         <v>44820.47935185185</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49148,7 +49148,7 @@
         <v>45352</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49205,7 +49205,7 @@
         <v>45181.33571759259</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49262,7 +49262,7 @@
         <v>45719.4094212963</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>45719.43872685185</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45358</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45049</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>45202</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45259</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>44894.57065972222</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>44378.56137731481</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>44944</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>44504</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49857,7 +49857,7 @@
         <v>44222</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>45225.46480324074</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>45254</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>44603</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45513.51815972223</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>44848</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
         <v>44438</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50266,7 +50266,7 @@
         <v>45693</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50323,7 +50323,7 @@
         <v>45379</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50380,7 +50380,7 @@
         <v>44328</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50442,7 +50442,7 @@
         <v>45323.55914351852</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50504,7 +50504,7 @@
         <v>45267</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50566,7 +50566,7 @@
         <v>45757</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>44588</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50680,7 +50680,7 @@
         <v>45751.32001157408</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>44883</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45758</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45693</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>44553</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45770.61341435185</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -51032,7 +51032,7 @@
         <v>45705.2953125</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -51094,7 +51094,7 @@
         <v>45707</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51156,7 +51156,7 @@
         <v>45763</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51213,7 +51213,7 @@
         <v>45638</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51270,7 +51270,7 @@
         <v>45096</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51327,7 +51327,7 @@
         <v>45148</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45113.80170138889</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>44980</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51498,7 +51498,7 @@
         <v>45104.6828125</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51555,7 +51555,7 @@
         <v>44964.65261574074</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51612,7 +51612,7 @@
         <v>44123</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51669,7 +51669,7 @@
         <v>45670</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51731,7 +51731,7 @@
         <v>45478.60802083334</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51793,7 +51793,7 @@
         <v>45096</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51850,7 +51850,7 @@
         <v>44977</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51907,7 +51907,7 @@
         <v>45113</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         <v>45231.54601851852</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -52021,7 +52021,7 @@
         <v>44609.60171296296</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -52083,7 +52083,7 @@
         <v>45761.47540509259</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52140,7 +52140,7 @@
         <v>45761.47748842592</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>44788</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52254,7 +52254,7 @@
         <v>45098.63572916666</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52311,7 +52311,7 @@
         <v>45173</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52368,7 +52368,7 @@
         <v>45670</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45699.71063657408</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52487,7 +52487,7 @@
         <v>45361.57299768519</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52549,7 +52549,7 @@
         <v>44888</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>45456.58491898148</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52668,7 +52668,7 @@
         <v>45110</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52725,7 +52725,7 @@
         <v>45594</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52787,7 +52787,7 @@
         <v>45259</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52844,7 +52844,7 @@
         <v>45460</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52906,7 +52906,7 @@
         <v>45642.63524305556</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52963,7 +52963,7 @@
         <v>45763.6503125</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -53020,7 +53020,7 @@
         <v>44623.41775462963</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -53082,7 +53082,7 @@
         <v>45644.47723379629</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53139,7 +53139,7 @@
         <v>45075.51982638889</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53196,7 +53196,7 @@
         <v>45614.67020833334</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53253,7 +53253,7 @@
         <v>45148</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53310,7 +53310,7 @@
         <v>45148</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53367,7 +53367,7 @@
         <v>45182</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53424,7 +53424,7 @@
         <v>45266</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53481,7 +53481,7 @@
         <v>45646.61892361111</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>44816</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53595,7 +53595,7 @@
         <v>45308.63298611111</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45691</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53714,7 +53714,7 @@
         <v>45089</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53771,7 +53771,7 @@
         <v>45107</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53828,7 +53828,7 @@
         <v>44535</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53885,7 +53885,7 @@
         <v>44652</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53942,7 +53942,7 @@
         <v>44629.57741898148</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         <v>44608</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -54066,7 +54066,7 @@
         <v>45583</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -54128,7 +54128,7 @@
         <v>45583</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>44209</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54247,7 +54247,7 @@
         <v>45707</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         <v>45644</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54366,7 +54366,7 @@
         <v>44497.4666087963</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54423,7 +54423,7 @@
         <v>44946.43564814814</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         <v>44965</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>44965</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>44679</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45336.53908564815</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>45336.54270833333</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>45699</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>45679</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54884,7 +54884,7 @@
         <v>45349</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54941,7 +54941,7 @@
         <v>44223</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54998,7 +54998,7 @@
         <v>45131</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -55055,7 +55055,7 @@
         <v>45694</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -55112,7 +55112,7 @@
         <v>44624.35083333333</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55174,7 +55174,7 @@
         <v>45685.5778125</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55231,7 +55231,7 @@
         <v>45645</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55293,7 +55293,7 @@
         <v>44614.69730324074</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55355,7 +55355,7 @@
         <v>45259</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55412,7 +55412,7 @@
         <v>45589</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55469,7 +55469,7 @@
         <v>45589</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55526,7 +55526,7 @@
         <v>45695.84078703704</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55588,7 +55588,7 @@
         <v>45097</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45695.59197916667</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45478</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45194.63479166666</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>45194.60876157408</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45599</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55945,7 +55945,7 @@
         <v>45600</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>45435.34778935185</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>45310.53418981482</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -56131,7 +56131,7 @@
         <v>44665</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56193,7 +56193,7 @@
         <v>44897</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56250,7 +56250,7 @@
         <v>45317</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56307,7 +56307,7 @@
         <v>45345.56</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>45180.40255787037</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56426,7 +56426,7 @@
         <v>45611</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56483,7 +56483,7 @@
         <v>45741.45114583334</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56540,7 +56540,7 @@
         <v>45154.34931712963</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45723.63290509259</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56654,7 +56654,7 @@
         <v>45049.66025462963</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>45159.44694444445</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56768,7 +56768,7 @@
         <v>45443</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>44599.44832175926</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56887,7 +56887,7 @@
         <v>45254.49552083333</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45310</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -57001,7 +57001,7 @@
         <v>45327.61831018519</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45344.64759259259</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -57120,7 +57120,7 @@
         <v>44435.38657407407</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -57177,7 +57177,7 @@
         <v>45327</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>45729</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57291,7 +57291,7 @@
         <v>45729</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57348,7 +57348,7 @@
         <v>45769.6009375</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57405,7 +57405,7 @@
         <v>45762.61341435185</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57462,7 +57462,7 @@
         <v>45321</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>44610</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57581,7 +57581,7 @@
         <v>44403.3119212963</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57643,7 +57643,7 @@
         <v>44420</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -57700,7 +57700,7 @@
         <v>45554</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45677</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -57814,7 +57814,7 @@
         <v>45730.43966435185</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -57876,7 +57876,7 @@
         <v>44593</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -57933,7 +57933,7 @@
         <v>45520</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45175.57060185185</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -58047,7 +58047,7 @@
         <v>44909.51885416666</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -58109,7 +58109,7 @@
         <v>45729</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -58166,7 +58166,7 @@
         <v>45729</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -58223,7 +58223,7 @@
         <v>45181.36815972222</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -58280,7 +58280,7 @@
         <v>45713.44519675926</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -58337,7 +58337,7 @@
         <v>44553</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -58394,7 +58394,7 @@
         <v>45190</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -58451,7 +58451,7 @@
         <v>44550.37994212963</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -58513,7 +58513,7 @@
         <v>45048.55349537037</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -567,7 +567,7 @@
         <v>45603</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>45812.47355324074</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>45882.73309027778</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>45548</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>45827.64737268518</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>44377</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45313</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45082</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>45715.38824074074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>45728</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>45882.47538194444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45812.55136574074</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>44971</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>45803.55260416667</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>45803.55737268519</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45086</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44222</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>45202</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>44623</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44575</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45812</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>45758</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45196</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>44356</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>44180</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45442</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45092</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44497</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45799.60315972222</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>44792</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>45803.61035879629</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45841.64539351852</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>44532</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44500</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>44351</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>45316</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>44574</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45107</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>45736.53695601852</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45097</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>44719</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44664</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>44974</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>45442</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>44740</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44659</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>45371</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>44791</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45090</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>45803.55535879629</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>44684</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45831.55982638889</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>44495</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>45222</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45694.55559027778</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>45035.44672453704</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45474</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>45803.61554398148</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>45715.38105324074</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45762.62260416667</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>45293</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>44489</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>45841.80690972223</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>45168.50667824074</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45189</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>45903</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>44967</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44614</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44379</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>44651</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>45694.49650462963</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45783</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>44963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>45464</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45687</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>44909</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>44487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45273</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>45107</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>45167</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>45805.41232638889</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>45098</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>44673.47858796296</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>45811.38710648148</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>45679</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>45818.60254629629</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>45817.34614583333</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>45358</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>45817</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>45736.49902777778</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>45820.84516203704</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45763.52524305556</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>44897</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>45874.69282407407</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45874</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>44645</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>45336</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>44958</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>45841.81555555556</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45665</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44917.59298611111</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>45314.55579861111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>44467</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>45757.49934027778</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44917</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>44855</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>45107</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>45762.57244212963</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>44849</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>45853.76976851852</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45896.47487268518</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45901.66702546296</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>45385</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>44144</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>44602</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>44602</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>44583.61803240741</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>44517</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44119</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44407</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>44567.81241898148</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>44544</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44526</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44609.61430555556</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44489</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>44323.58961805556</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>44299</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>44714</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>44491.50769675926</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44252</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44569.5340625</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44486</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44662.56783564815</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>44572.39640046296</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>44659.70381944445</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44603</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44700</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44839</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>44230</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44494</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44784</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44369.65428240741</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>44612</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>44720</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44886</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44598</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>44883.56321759259</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44314</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44610</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44865.43494212963</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44167</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44357</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44742</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>44704</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44533.4678587963</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>44764</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44453</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44297</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>44153</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44351</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>44349.49666666667</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44584.63190972222</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>44609</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>44490.64313657407</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>44091</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>44281.4499537037</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>44610</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>44335.52201388889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>44512</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>44740.68142361111</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>44816</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         <v>44297</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>44705.78475694444</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>44705.83326388889</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>44692.87630787037</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44722.30703703704</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>44328.57100694445</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44369</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44698.67151620371</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44750.678125</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>44277.65263888889</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>44685.6212037037</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>44543</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>44461</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>44383</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>44702.70721064815</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>44378.69857638889</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44442.35195601852</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44442</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44733.43420138889</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>44504.59193287037</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>44711</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>44643.51446759259</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>44750.45800925926</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>44095</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>44599.43265046296</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>44551.59704861111</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>44743</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>44846</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>44623.4572337963</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>44865</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>44461.73350694445</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44134</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>44446.47693287037</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>44571.44563657408</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>44103</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>44593</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>44838.40635416667</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>44491.54116898148</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>44676</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>44459</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>44729</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44160</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>44476.61263888889</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>44144</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>44266.57917824074</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>44847.35622685185</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>44517</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>44705.84535879629</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>44634</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>44294.37555555555</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44659.57912037037</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>44886.58890046296</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>44791.38336805555</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>44623</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>44762</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44798</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45187.61136574074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45371.50738425926</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>44144</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45723</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45208.46130787037</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>44859.36896990741</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>44328</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>44832</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>44799.36359953704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>45050.49392361111</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>44883</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>44866</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>44583.61555555555</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18730,7 +18730,7 @@
         <v>44575</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>44479</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>45741.45114583334</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>44575.4366087963</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>45119</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>44847</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>44966</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>45699.71063657408</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>45729</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45743.50744212963</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45259.52809027778</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>44446</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45175.57060185185</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45096</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>44501.71344907407</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45756.44024305556</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45756.50738425926</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>45695.59197916667</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>45644.47723379629</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45006</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>44489</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45644</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45307</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>44548</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>45614</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45327</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>44550.37994212963</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>44543.34697916666</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         <v>44831</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45300</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>45758</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>44980</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20584,7 +20584,7 @@
         <v>44809.92752314815</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>45670</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>44810</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>44371.49178240741</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>45776.48275462963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45776</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45776.45263888889</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>45107.55574074074</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>45254.49552083333</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>45776.6415162037</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>45611</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45777.37119212963</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45344.64759259259</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45777.34894675926</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45777.32731481481</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45777.52655092593</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>45107</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>45107</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>45107</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>45777</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45344.69567129629</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>44816</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45520</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>45574</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45779.6665162037</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45133</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45096</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>44395</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45098.62966435185</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45779.65787037037</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>45779.49085648148</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>44495</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44544</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44519</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>45783.61053240741</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>45335</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>45293</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>45163.59913194444</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>45096</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>45294.5666550926</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>45784.57266203704</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>44095</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>44551.76711805556</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>44553</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>45327</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>44569.49344907407</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45407.49721064815</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45784.80497685185</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45329</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45177.79766203704</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45558.42498842593</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>45562</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>45368.64787037037</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>45231.54601851852</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>44569.69358796296</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23824,7 +23824,7 @@
         <v>44603</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>45161</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>45259</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>45259</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45524</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>44629.57741898148</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>45468</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45684</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45037</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>45134.57021990741</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>45254</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>44533.46665509259</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>45021.29524305555</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45583</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45583</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44535</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44637.35744212963</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>45036</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>45624</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>44883</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>44849</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45726</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>45371.67368055556</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>45790.51040509259</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45091</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>45162</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>45159.44694444445</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>45790.44972222222</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>44522.55518518519</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>45583.48449074074</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45145</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>45584.60038194444</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45625.58501157408</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45790.51186342593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44894.57065972222</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>45201.62318287037</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25936,7 +25936,7 @@
         <v>45358</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>44522</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>44616</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>45181.33571759259</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>44516</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>45341</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>45177.56940972222</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>45736.60863425926</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45341.63811342593</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>45525</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>44935</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>45614.65928240741</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45335.66331018518</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>45195.64807870371</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45763</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>45636</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44277.65650462963</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44504</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44435.38657407407</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44602</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45644</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>45159.45748842593</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45643</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44678.3315625</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>44610</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>45615</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45490</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45638</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>44649</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45439</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>45429</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>45644</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>45188</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>44977</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>44832.49594907407</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45797.45900462963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>45338.49412037037</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44131</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45721.35173611111</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45798.42252314815</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>45798.41734953703</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44624.64538194444</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>45797.42777777778</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>45799.53348379629</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
         <v>45618.71140046296</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>45693</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>44637.56178240741</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>45148</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>45148</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45148</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>44588</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28908,7 +28908,7 @@
         <v>45323.55914351852</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45453</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>45194</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>45799.53803240741</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45799.5421875</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>45799.57714120371</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>45799.64877314815</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29332,7 +29332,7 @@
         <v>45799.67806712963</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45733.62903935185</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45799.68190972223</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>44140</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45524</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>45601</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>44109</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>44847</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>45799.53947916667</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45799.54104166666</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>44594</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>45638</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44967</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45737.40503472222</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45371</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45799.65021990741</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45799.6527199074</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>45799.43496527777</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30408,7 +30408,7 @@
         <v>44909</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>45086.7037037037</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>45677</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>45190</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>44629.42423611111</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>44599.42277777778</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>45744</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45341</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45608</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>44593</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>44593.61355324074</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>45803.36384259259</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>45344</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45351.54596064815</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>45803.63395833333</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>44946</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45425.94947916667</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>45762.49243055555</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45805.4094675926</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>45054.9271875</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>45664</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>45194.63479166666</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45805.41010416667</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>45805.41813657407</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>44426</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45646.50211805556</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45173</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44106</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>44608</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>44594</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>45194.60876157408</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>45805.43402777778</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>44819.62</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>45614</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45202.4997337963</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45055</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>45805.4255787037</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45182</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45182</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>45093.46706018518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>45511</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>44130</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45552</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45810.44339120371</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45809</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -33063,7 +33063,7 @@
         <v>45407.69575231482</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -33120,7 +33120,7 @@
         <v>45188.42052083334</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>45231.62840277778</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>45215.44233796297</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>44960</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>44960.66233796296</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>45677</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45726</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>45695.8391550926</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33581,7 +33581,7 @@
         <v>45695.84078703704</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>44209</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45809</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45809</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45453.69339120371</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>45810.44299768518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>45809</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45812.48032407407</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>44553</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>45810.45960648148</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45705.2953125</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         <v>44126</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45775.46377314815</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45231</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44575</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45097</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>45216</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>45216</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>44200</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>45721.34715277778</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>45814</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>45813</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34880,7 +34880,7 @@
         <v>45813.46034722222</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34937,7 +34937,7 @@
         <v>45173</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>45624</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>45694</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>44893</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45369</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>44155</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>44588</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45729</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>45729</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>44904</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45208.4350462963</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>44659</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>45707</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35693,7 +35693,7 @@
         <v>45705</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>45818.57910879629</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>45180.40255787037</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>44614.59027777778</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45817</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>44679.68706018518</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>45149.56928240741</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>45358</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45379</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36231,7 +36231,7 @@
         <v>44912.29869212963</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36288,7 +36288,7 @@
         <v>45181.36815972222</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>44614.69730324074</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45691</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36469,7 +36469,7 @@
         <v>45820</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45820</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45443</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         <v>45817</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36707,7 +36707,7 @@
         <v>44967.55960648148</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>45523</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>44679.66694444444</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36883,7 +36883,7 @@
         <v>45820</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>44223</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>45721.60894675926</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>45254</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>45182</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45182</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45821.45905092593</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45175</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>45824.43798611111</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45821.44101851852</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45699</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45152</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>45694.49037037037</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>45202</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>44699</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>45825.44482638889</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>45825.49060185185</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37887,7 +37887,7 @@
         <v>45827.62096064815</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>44222</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -38001,7 +38001,7 @@
         <v>45225.46480324074</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -38058,7 +38058,7 @@
         <v>45131</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38115,7 +38115,7 @@
         <v>45827.64092592592</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>45259</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38234,7 +38234,7 @@
         <v>45827.46288194445</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>44512</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>45236.47697916667</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>45874.705</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38467,7 +38467,7 @@
         <v>45831.42365740741</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38524,7 +38524,7 @@
         <v>45831.42616898148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>45831.73</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>44159</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38705,7 +38705,7 @@
         <v>45390</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38762,7 +38762,7 @@
         <v>44617.48311342593</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>44245</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>45299</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45832.35590277778</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>44977</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>45831.40671296296</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>45446.78256944445</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>45267</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>45236</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>45832.35545138889</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45769.6009375</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>45698.65606481482</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
         <v>45693</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>45831.72686342592</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45874</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>45876</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>45426</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44993</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>45876</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>45719.42197916667</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>45719.43646990741</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44733</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44799.36695601852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44994</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44665</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>45068.58563657408</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>45426.34148148148</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45363.54878472222</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44967.80034722222</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44967</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45880.68200231482</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>44929</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>45254</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>45321</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>45835.62752314815</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45317</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>45730.43966435185</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45880.32907407408</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>45361.57299768519</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>45614</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45164.82913194445</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45877.57847222222</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>45877.62969907407</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45880.34064814815</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>45351.48662037037</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>45583</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>44930</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>45042</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>44608</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>44909.51885416666</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41697,7 +41697,7 @@
         <v>45600</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41759,7 +41759,7 @@
         <v>45107.53688657407</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41816,7 +41816,7 @@
         <v>45456.59535879629</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41873,7 +41873,7 @@
         <v>45881.45898148148</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41930,7 +41930,7 @@
         <v>45310</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>44438</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45839</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>45089</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>45520</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42220,7 +42220,7 @@
         <v>45839</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45881.44938657407</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
         <v>45091.69766203704</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>45882.37202546297</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>45751.32001157408</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>45474.41729166666</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>45839</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>45821.31292824074</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>45840.68518518518</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42758,7 +42758,7 @@
         <v>45840</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         <v>45642</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>45695.83655092592</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>45707</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>45645</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>45113</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43120,7 +43120,7 @@
         <v>45113.80170138889</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>45757.6997337963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>45757</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>45631.44464120371</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>45882.52290509259</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>45736.45847222222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43467,7 +43467,7 @@
         <v>45693</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43524,7 +43524,7 @@
         <v>45693</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43581,7 +43581,7 @@
         <v>45719.4094212963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43643,7 +43643,7 @@
         <v>45719.43872685185</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>44644.37548611111</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>44788</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45761.47540509259</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45761.47748842592</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>44400.6750925926</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -44000,7 +44000,7 @@
         <v>44403.3119212963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>44980</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45693</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45841.5847337963</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>44508.44033564815</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>44817</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>44519.64902777778</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45442</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45656</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44528,7 +44528,7 @@
         <v>45216.39040509259</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>45098.63572916666</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>45694</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>44820.47935185185</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45065.43013888889</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44818,7 +44818,7 @@
         <v>45637</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>44532</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45691</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>45691</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45719.43755787037</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45170,7 +45170,7 @@
         <v>45054.95675925926</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>45047.31793981481</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>44888</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>44207</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>45127</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>44379.5745949074</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>45048.55349537037</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>44848</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>45259</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>45478</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45842.74049768518</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>45223</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>44420</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>44993</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>45714.55368055555</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45723.63290509259</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45763.52995370371</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>44531</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45599</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>44532</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>45642.63524305556</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45646.61892361111</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>44984.69216435185</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>44379.56163194445</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>45757.67611111111</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>45078</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>44378.56137731481</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45391.37361111111</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>45679</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45679</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>44123</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>44139</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>45520</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>44581.60254629629</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47143,7 +47143,7 @@
         <v>45202</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47200,7 +47200,7 @@
         <v>44568.67040509259</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>45638</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44900.54711805555</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45580</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>44123</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44944</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45555.5727662037</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47604,7 +47604,7 @@
         <v>45295</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>44168.55746527778</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>45763.52744212963</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>45152</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>44908.425625</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47899,7 +47899,7 @@
         <v>45845.53202546296</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47956,7 +47956,7 @@
         <v>45554</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>45757</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>44358.63490740741</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48127,7 +48127,7 @@
         <v>44816</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>45763.6503125</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>44949.4708912037</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>45316</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45317</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>44403.29719907408</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45890</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>44946.43564814814</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45033</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>44531</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45307</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45104.6828125</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45642</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48888,7 +48888,7 @@
         <v>45851.60097222222</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48950,7 +48950,7 @@
         <v>44105</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>44209</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>45851.62018518519</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49131,7 +49131,7 @@
         <v>45644.62677083333</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>44273</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49245,7 +49245,7 @@
         <v>45426</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49302,7 +49302,7 @@
         <v>45849.49259259259</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49359,7 +49359,7 @@
         <v>44960.65061342593</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         <v>44960</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>45852.67366898148</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>44593.64863425926</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45852.39642361111</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>44928</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49716,7 +49716,7 @@
         <v>45852.36871527778</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49773,7 +49773,7 @@
         <v>45884</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49830,7 +49830,7 @@
         <v>45852.68978009259</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49892,7 +49892,7 @@
         <v>45552</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49949,7 +49949,7 @@
         <v>45891.46827546296</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
         <v>45852</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -50068,7 +50068,7 @@
         <v>45852.72965277778</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50130,7 +50130,7 @@
         <v>45891.33204861111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>45121</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50249,7 +50249,7 @@
         <v>45854.44017361111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50311,7 +50311,7 @@
         <v>45896</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50368,7 +50368,7 @@
         <v>44819.50233796296</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50430,7 +50430,7 @@
         <v>45896.57368055556</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50487,7 +50487,7 @@
         <v>44616</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50544,7 +50544,7 @@
         <v>44886</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50601,7 +50601,7 @@
         <v>45896.61050925926</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50658,7 +50658,7 @@
         <v>45896.57171296296</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50715,7 +50715,7 @@
         <v>45896</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>44560</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50829,7 +50829,7 @@
         <v>44600</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50891,7 +50891,7 @@
         <v>45898.46040509259</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50948,7 +50948,7 @@
         <v>44623.41775462963</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -51010,7 +51010,7 @@
         <v>44623.5571875</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -51072,7 +51072,7 @@
         <v>45167.3721412037</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>45897</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51186,7 +51186,7 @@
         <v>45856.34959490741</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>45856</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51310,7 +51310,7 @@
         <v>44965</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51367,7 +51367,7 @@
         <v>44965</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51424,7 +51424,7 @@
         <v>45308.63298611111</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51481,7 +51481,7 @@
         <v>45212.34997685185</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>44886.5928125</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51595,7 +51595,7 @@
         <v>45293</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51652,7 +51652,7 @@
         <v>45181.58055555556</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51714,7 +51714,7 @@
         <v>45670</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>45856.34034722222</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45856.34231481481</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>44742</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45902.42243055555</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -52024,7 +52024,7 @@
         <v>45901.41756944444</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -52086,7 +52086,7 @@
         <v>45901.41853009259</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52148,7 +52148,7 @@
         <v>45880</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52205,7 +52205,7 @@
         <v>45231</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>45838</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>45341</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52381,7 +52381,7 @@
         <v>45901.67194444445</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>45838</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52495,7 +52495,7 @@
         <v>45838</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         <v>45594</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52614,7 +52614,7 @@
         <v>45300.55028935185</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>45903.69096064815</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45904.77746527778</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52790,7 +52790,7 @@
         <v>45097</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52847,7 +52847,7 @@
         <v>45903.69358796296</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52909,7 +52909,7 @@
         <v>44969</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52966,7 +52966,7 @@
         <v>44944</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -53023,7 +53023,7 @@
         <v>45601</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>45154.35092592592</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>44652</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>45678</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53251,7 +53251,7 @@
         <v>44679</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53308,7 +53308,7 @@
         <v>45905.5756712963</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53365,7 +53365,7 @@
         <v>45905.62641203704</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53427,7 +53427,7 @@
         <v>45349</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53484,7 +53484,7 @@
         <v>45851.62179398148</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>45863.44648148148</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53603,7 +53603,7 @@
         <v>45863.45355324074</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53660,7 +53660,7 @@
         <v>45905.64862268518</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>45891.4865625</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
         <v>45656</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53836,7 +53836,7 @@
         <v>45905.62541666667</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53898,7 +53898,7 @@
         <v>45694</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53955,7 +53955,7 @@
         <v>45909.57565972222</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -54017,7 +54017,7 @@
         <v>45910.59415509259</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -54079,7 +54079,7 @@
         <v>44806</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>45867.58056712963</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>45049.66025462963</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54250,7 +54250,7 @@
         <v>45910.59475694445</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54312,7 +54312,7 @@
         <v>44574</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>44645.39157407408</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>44497.4666087963</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45152</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>44964.65261574074</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45912.7097337963</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54664,7 +54664,7 @@
         <v>44599.44832175926</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45831.46731481481</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>45904</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>45638</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45903</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45000.44666666666</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -55006,7 +55006,7 @@
         <v>45762.61341435185</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -55063,7 +55063,7 @@
         <v>45713.44519675926</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -55120,7 +55120,7 @@
         <v>45327.61831018519</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>45352</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>44944</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45266</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>44872</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45513.51815972223</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45617.59006944444</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45049</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         <v>44560</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55638,7 +55638,7 @@
         <v>45336.53908564815</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>45614.67020833334</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>45770.61341435185</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45677.39440972222</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45169</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>45244.52202546296</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55995,7 +55995,7 @@
         <v>45435.34778935185</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>45763</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>45548.42854166667</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56171,7 +56171,7 @@
         <v>44532</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56228,7 +56228,7 @@
         <v>45190</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>44977</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>45336.54270833333</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>45110</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>45194</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56518,7 +56518,7 @@
         <v>45474</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56575,7 +56575,7 @@
         <v>45611</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56632,7 +56632,7 @@
         <v>45300.55680555556</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56689,7 +56689,7 @@
         <v>45589</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56746,7 +56746,7 @@
         <v>45589</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56803,7 +56803,7 @@
         <v>44609.60171296296</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56865,7 +56865,7 @@
         <v>44503</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56922,7 +56922,7 @@
         <v>44624.35083333333</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56984,7 +56984,7 @@
         <v>45456.58491898148</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -57041,7 +57041,7 @@
         <v>44897</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -57098,7 +57098,7 @@
         <v>45729</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -57155,7 +57155,7 @@
         <v>45729</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>45327</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57269,7 +57269,7 @@
         <v>45014</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57326,7 +57326,7 @@
         <v>45222</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57383,7 +57383,7 @@
         <v>44593</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57440,7 +57440,7 @@
         <v>45685.5778125</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57497,7 +57497,7 @@
         <v>45695.59805555556</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57559,7 +57559,7 @@
         <v>45460</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57621,7 +57621,7 @@
         <v>45345.56</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -57678,7 +57678,7 @@
         <v>44914.67600694444</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -57735,7 +57735,7 @@
         <v>45061</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -57792,7 +57792,7 @@
         <v>44210</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -57849,7 +57849,7 @@
         <v>45583.47836805556</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -57911,7 +57911,7 @@
         <v>44912</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -57968,7 +57968,7 @@
         <v>44967.78984953704</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -58025,7 +58025,7 @@
         <v>45075.51982638889</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -58082,7 +58082,7 @@
         <v>45720.60410879629</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -58139,7 +58139,7 @@
         <v>45699</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -58196,7 +58196,7 @@
         <v>45733.63099537037</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -58253,7 +58253,7 @@
         <v>45426.61569444444</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>45478.60802083334</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45719.40723379629</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -58434,7 +58434,7 @@
         <v>45154.34931712963</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -567,7 +567,7 @@
         <v>45603</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>45812.47355324074</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>45882.73309027778</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>45548</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>45827.64737268518</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>44377</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45313</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45082</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>45715.38824074074</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>45728</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>45882.47538194444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45812.55136574074</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>44971</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>45803.55260416667</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>45803.55737268519</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45086</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44222</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>45202</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>44623</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44575</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45812</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>45758</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45196</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>44356</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>44180</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45442</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45092</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44497</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45799.60315972222</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>44792</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>45803.61035879629</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45841.64539351852</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>44532</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44500</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>44351</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>45316</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>44574</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45107</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>45736.53695601852</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45097</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>44719</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44664</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>44974</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>45442</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>44740</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44659</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>45371</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>44791</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45090</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>45803.55535879629</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>44684</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45831.55982638889</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>44495</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>45222</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45694.55559027778</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>45035.44672453704</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45474</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>45803.61554398148</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>45715.38105324074</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45762.62260416667</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>45293</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>44489</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>45841.80690972223</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>45168.50667824074</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45189</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>45903</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>44967</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44614</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44379</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>44651</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>45694.49650462963</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45783</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>44963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>45464</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45687</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>44909</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>44487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45273</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>45107</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>45167</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>45805.41232638889</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>45098</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>44673.47858796296</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>45811.38710648148</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>45679</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>45818.60254629629</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>45817.34614583333</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>45358</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>45817</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>45736.49902777778</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>45820.84516203704</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45763.52524305556</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>44897</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>45874.69282407407</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45874</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>44645</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>45336</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>44958</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>45841.81555555556</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45665</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44917.59298611111</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>45314.55579861111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>44467</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>45757.49934027778</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44917</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>44855</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>45107</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>45762.57244212963</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>44849</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>45853.76976851852</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45896.47487268518</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45901.66702546296</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>45385</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>44144</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>44602</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>44602</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>44583.61803240741</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>44517</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44119</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44407</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>44567.81241898148</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>44544</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44526</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44609.61430555556</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44489</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>44323.58961805556</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>44299</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>44714</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>44491.50769675926</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44252</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44569.5340625</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44486</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44662.56783564815</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>44572.39640046296</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>44659.70381944445</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44603</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44700</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44839</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>44230</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44494</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44784</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44369.65428240741</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>44612</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>44720</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44886</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44598</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>44883.56321759259</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44314</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44610</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44865.43494212963</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44167</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44357</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44742</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>44704</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44533.4678587963</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>44764</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44453</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44297</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>44153</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44351</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>44349.49666666667</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44584.63190972222</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>44609</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>44490.64313657407</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>44091</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>44281.4499537037</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>44610</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>44335.52201388889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>44512</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>44740.68142361111</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>44816</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         <v>44297</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>44705.78475694444</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>44705.83326388889</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>44692.87630787037</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44722.30703703704</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>44328.57100694445</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44369</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44698.67151620371</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44750.678125</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>44277.65263888889</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>44685.6212037037</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>44543</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>44461</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>44383</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>44702.70721064815</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>44378.69857638889</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44442.35195601852</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44442</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44733.43420138889</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>44504.59193287037</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>44711</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>44643.51446759259</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>44750.45800925926</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>44095</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>44599.43265046296</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>44551.59704861111</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>44743</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>44846</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>44623.4572337963</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>44865</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>44461.73350694445</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44134</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>44446.47693287037</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>44571.44563657408</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>44103</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>44593</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>44838.40635416667</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>44491.54116898148</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>44676</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>44459</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>44729</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44160</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>44476.61263888889</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>44144</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>44266.57917824074</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>44847.35622685185</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>44517</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>44705.84535879629</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>44634</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>44294.37555555555</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44659.57912037037</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>44886.58890046296</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>44791.38336805555</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>44623</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>44762</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44798</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45187.61136574074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45371.50738425926</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>44144</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45723</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45208.46130787037</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>44859.36896990741</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>44328</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>44832</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>44799.36359953704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>45050.49392361111</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>44883</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>44866</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>44583.61555555555</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18730,7 +18730,7 @@
         <v>44575</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>44479</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>45741.45114583334</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>44575.4366087963</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>45119</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>44847</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>44966</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>45699.71063657408</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>45729</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45743.50744212963</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45259.52809027778</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>44446</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45175.57060185185</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45096</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>44501.71344907407</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45756.44024305556</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45756.50738425926</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>45695.59197916667</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>45644.47723379629</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45006</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>44489</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45644</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45307</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>44548</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>45614</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45327</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>44550.37994212963</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>44543.34697916666</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         <v>44831</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45300</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>45758</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>44980</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20584,7 +20584,7 @@
         <v>44809.92752314815</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>45670</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>44810</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>44371.49178240741</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>45776.48275462963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45776</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45776.45263888889</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>45107.55574074074</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>45254.49552083333</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>45776.6415162037</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>45611</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45777.37119212963</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45344.64759259259</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45777.34894675926</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45777.32731481481</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45777.52655092593</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>45107</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>45107</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>45107</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>45777</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45344.69567129629</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>44816</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45520</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>45574</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45779.6665162037</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45133</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45096</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>44395</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45098.62966435185</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45779.65787037037</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>45779.49085648148</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>44495</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44544</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44519</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>45783.61053240741</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>45335</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>45293</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>45163.59913194444</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>45096</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>45294.5666550926</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>45784.57266203704</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>44095</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>44551.76711805556</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>44553</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>45327</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>44569.49344907407</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45407.49721064815</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45784.80497685185</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45329</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45177.79766203704</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45558.42498842593</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>45562</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>45368.64787037037</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>45231.54601851852</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>44569.69358796296</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23824,7 +23824,7 @@
         <v>44603</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>45161</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>45259</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>45259</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45524</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>44629.57741898148</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>45468</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45684</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45037</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>45134.57021990741</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>45254</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>44533.46665509259</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>45021.29524305555</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45583</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45583</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44535</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44637.35744212963</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>45036</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>45624</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>44883</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>44849</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45726</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>45371.67368055556</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>45790.51040509259</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45091</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>45162</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>45159.44694444445</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>45790.44972222222</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>44522.55518518519</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>45583.48449074074</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45145</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>45584.60038194444</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45625.58501157408</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45790.51186342593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44894.57065972222</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>45201.62318287037</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25936,7 +25936,7 @@
         <v>45358</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>44522</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>44616</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>45181.33571759259</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>44516</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>45341</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>45177.56940972222</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>45736.60863425926</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45341.63811342593</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>45525</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>44935</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>45614.65928240741</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45335.66331018518</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>45195.64807870371</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45763</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>45636</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44277.65650462963</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44504</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44435.38657407407</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44602</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45644</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>45159.45748842593</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45643</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44678.3315625</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>44610</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>45615</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45490</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45638</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>44649</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45439</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>45429</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>45644</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>45188</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>44977</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>44832.49594907407</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45797.45900462963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>45338.49412037037</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44131</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45721.35173611111</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45798.42252314815</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>45798.41734953703</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44624.64538194444</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>45797.42777777778</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>45799.53348379629</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
         <v>45618.71140046296</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>45693</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>44637.56178240741</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>45148</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>45148</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45148</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>44588</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28908,7 +28908,7 @@
         <v>45323.55914351852</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45453</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>45194</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>45799.53803240741</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45799.5421875</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>45799.57714120371</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>45799.64877314815</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29332,7 +29332,7 @@
         <v>45799.67806712963</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45733.62903935185</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45799.68190972223</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>44140</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45524</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>45601</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>44109</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>44847</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>45799.53947916667</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45799.54104166666</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>44594</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>45638</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44967</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45737.40503472222</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45371</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45799.65021990741</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45799.6527199074</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>45799.43496527777</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30408,7 +30408,7 @@
         <v>44909</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>45086.7037037037</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>45677</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>45190</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>44629.42423611111</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>44599.42277777778</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>45744</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45341</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45608</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>44593</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>44593.61355324074</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>45803.36384259259</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>45344</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45351.54596064815</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>45803.63395833333</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>44946</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45425.94947916667</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>45762.49243055555</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45805.4094675926</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>45054.9271875</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>45664</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>45194.63479166666</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45805.41010416667</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>45805.41813657407</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>44426</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45646.50211805556</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45173</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44106</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>44608</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>44594</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>45194.60876157408</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>45805.43402777778</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>44819.62</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>45614</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45202.4997337963</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45055</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>45805.4255787037</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45182</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45182</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>45093.46706018518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>45511</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>44130</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45552</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45810.44339120371</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45809</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -33063,7 +33063,7 @@
         <v>45407.69575231482</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -33120,7 +33120,7 @@
         <v>45188.42052083334</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>45231.62840277778</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>45215.44233796297</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>44960</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>44960.66233796296</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>45677</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45726</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>45695.8391550926</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33581,7 +33581,7 @@
         <v>45695.84078703704</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>44209</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45809</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45809</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45453.69339120371</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>45810.44299768518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>45809</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45812.48032407407</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>44553</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>45810.45960648148</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45705.2953125</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         <v>44126</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45775.46377314815</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45231</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44575</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45097</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>45216</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>45216</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>44200</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>45721.34715277778</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>45814</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>45813</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34880,7 +34880,7 @@
         <v>45813.46034722222</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34937,7 +34937,7 @@
         <v>45173</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>45624</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>45694</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>44893</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45369</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>44155</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>44588</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45729</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>45729</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>44904</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45208.4350462963</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>44659</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>45707</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35693,7 +35693,7 @@
         <v>45705</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>45818.57910879629</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>45180.40255787037</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>44614.59027777778</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45817</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>44679.68706018518</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>45149.56928240741</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>45358</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45379</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36231,7 +36231,7 @@
         <v>44912.29869212963</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36288,7 +36288,7 @@
         <v>45181.36815972222</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>44614.69730324074</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45691</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36469,7 +36469,7 @@
         <v>45820</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45820</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45443</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         <v>45817</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36707,7 +36707,7 @@
         <v>44967.55960648148</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>45523</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>44679.66694444444</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36883,7 +36883,7 @@
         <v>45820</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>44223</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>45721.60894675926</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>45254</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>45182</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45182</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45821.45905092593</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45175</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>45824.43798611111</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45821.44101851852</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45699</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45152</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>45694.49037037037</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>45202</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>44699</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>45825.44482638889</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>45825.49060185185</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37887,7 +37887,7 @@
         <v>45827.62096064815</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>44222</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -38001,7 +38001,7 @@
         <v>45225.46480324074</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -38058,7 +38058,7 @@
         <v>45131</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38115,7 +38115,7 @@
         <v>45827.64092592592</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>45259</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38234,7 +38234,7 @@
         <v>45827.46288194445</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>44512</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>45236.47697916667</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>45874.705</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38467,7 +38467,7 @@
         <v>45831.42365740741</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38524,7 +38524,7 @@
         <v>45831.42616898148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>45831.73</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>44159</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38705,7 +38705,7 @@
         <v>45390</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38762,7 +38762,7 @@
         <v>44617.48311342593</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>44245</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>45299</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45832.35590277778</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>44977</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>45831.40671296296</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>45446.78256944445</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>45267</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>45236</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>45832.35545138889</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45769.6009375</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>45698.65606481482</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
         <v>45693</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>45831.72686342592</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45874</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>45876</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>45426</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44993</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>45876</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>45719.42197916667</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>45719.43646990741</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44733</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44799.36695601852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44994</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44665</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>45068.58563657408</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>45426.34148148148</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45363.54878472222</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44967.80034722222</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44967</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45880.68200231482</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>44929</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>45254</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>45321</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>45835.62752314815</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45317</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>45730.43966435185</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45880.32907407408</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>45361.57299768519</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>45614</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45164.82913194445</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45877.57847222222</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>45877.62969907407</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45880.34064814815</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>45351.48662037037</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>45583</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>44930</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>45042</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>44608</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>44909.51885416666</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41697,7 +41697,7 @@
         <v>45600</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41759,7 +41759,7 @@
         <v>45107.53688657407</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41816,7 +41816,7 @@
         <v>45456.59535879629</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41873,7 +41873,7 @@
         <v>45881.45898148148</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41930,7 +41930,7 @@
         <v>45310</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>44438</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45839</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>45089</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>45520</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42220,7 +42220,7 @@
         <v>45839</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45881.44938657407</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
         <v>45091.69766203704</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>45882.37202546297</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>45751.32001157408</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>45474.41729166666</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>45839</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>45821.31292824074</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>45840.68518518518</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42758,7 +42758,7 @@
         <v>45840</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         <v>45642</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>45695.83655092592</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>45707</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>45645</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>45113</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43120,7 +43120,7 @@
         <v>45113.80170138889</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>45757.6997337963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>45757</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>45631.44464120371</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>45882.52290509259</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>45736.45847222222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43467,7 +43467,7 @@
         <v>45693</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43524,7 +43524,7 @@
         <v>45693</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43581,7 +43581,7 @@
         <v>45719.4094212963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43643,7 +43643,7 @@
         <v>45719.43872685185</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>44644.37548611111</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>44788</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45761.47540509259</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45761.47748842592</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>44400.6750925926</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -44000,7 +44000,7 @@
         <v>44403.3119212963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>44980</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45693</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45841.5847337963</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>44508.44033564815</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>44817</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>44519.64902777778</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45442</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45656</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44528,7 +44528,7 @@
         <v>45216.39040509259</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>45098.63572916666</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>45694</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>44820.47935185185</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45065.43013888889</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44818,7 +44818,7 @@
         <v>45637</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>44532</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45691</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>45691</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45719.43755787037</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45170,7 +45170,7 @@
         <v>45054.95675925926</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>45047.31793981481</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>44888</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>44207</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>45127</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>44379.5745949074</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>45048.55349537037</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>44848</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>45259</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>45478</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45842.74049768518</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>45223</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>44420</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>44993</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>45714.55368055555</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45723.63290509259</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45763.52995370371</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>44531</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45599</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>44532</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>45642.63524305556</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45646.61892361111</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>44984.69216435185</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>44379.56163194445</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>45757.67611111111</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>45078</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>44378.56137731481</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45391.37361111111</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>45679</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45679</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>44123</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>44139</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>45520</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>44581.60254629629</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47143,7 +47143,7 @@
         <v>45202</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47200,7 +47200,7 @@
         <v>44568.67040509259</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>45638</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44900.54711805555</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45580</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>44123</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44944</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45555.5727662037</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47604,7 +47604,7 @@
         <v>45295</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>44168.55746527778</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>45763.52744212963</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>45152</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>44908.425625</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47899,7 +47899,7 @@
         <v>45845.53202546296</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47956,7 +47956,7 @@
         <v>45554</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>45757</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>44358.63490740741</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48127,7 +48127,7 @@
         <v>44816</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>45763.6503125</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>44949.4708912037</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>45316</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45317</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>44403.29719907408</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45890</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>44946.43564814814</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45033</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>44531</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45307</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45104.6828125</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45642</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48888,7 +48888,7 @@
         <v>45851.60097222222</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48950,7 +48950,7 @@
         <v>44105</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>44209</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>45851.62018518519</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49131,7 +49131,7 @@
         <v>45644.62677083333</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>44273</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49245,7 +49245,7 @@
         <v>45426</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49302,7 +49302,7 @@
         <v>45849.49259259259</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49359,7 +49359,7 @@
         <v>44960.65061342593</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         <v>44960</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>45852.67366898148</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>44593.64863425926</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45852.39642361111</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>44928</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49716,7 +49716,7 @@
         <v>45852.36871527778</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49773,7 +49773,7 @@
         <v>45884</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49830,7 +49830,7 @@
         <v>45852.68978009259</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49892,7 +49892,7 @@
         <v>45552</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49949,7 +49949,7 @@
         <v>45891.46827546296</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
         <v>45852</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -50068,7 +50068,7 @@
         <v>45852.72965277778</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50130,7 +50130,7 @@
         <v>45891.33204861111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>45121</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50249,7 +50249,7 @@
         <v>45854.44017361111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50311,7 +50311,7 @@
         <v>45896</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50368,7 +50368,7 @@
         <v>44819.50233796296</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50430,7 +50430,7 @@
         <v>45896.57368055556</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50487,7 +50487,7 @@
         <v>44616</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50544,7 +50544,7 @@
         <v>44886</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50601,7 +50601,7 @@
         <v>45896.61050925926</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50658,7 +50658,7 @@
         <v>45896.57171296296</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50715,7 +50715,7 @@
         <v>45896</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>44560</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50829,7 +50829,7 @@
         <v>44600</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50891,7 +50891,7 @@
         <v>45898.46040509259</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50948,7 +50948,7 @@
         <v>44623.41775462963</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -51010,7 +51010,7 @@
         <v>44623.5571875</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -51072,7 +51072,7 @@
         <v>45167.3721412037</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>45897</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51186,7 +51186,7 @@
         <v>45856.34959490741</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>45856</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51310,7 +51310,7 @@
         <v>44965</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51367,7 +51367,7 @@
         <v>44965</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51424,7 +51424,7 @@
         <v>45308.63298611111</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51481,7 +51481,7 @@
         <v>45212.34997685185</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>44886.5928125</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51595,7 +51595,7 @@
         <v>45293</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51652,7 +51652,7 @@
         <v>45181.58055555556</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51714,7 +51714,7 @@
         <v>45670</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>45856.34034722222</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45856.34231481481</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>44742</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45902.42243055555</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -52024,7 +52024,7 @@
         <v>45901.41756944444</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -52086,7 +52086,7 @@
         <v>45901.41853009259</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52148,7 +52148,7 @@
         <v>45880</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52205,7 +52205,7 @@
         <v>45231</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>45838</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>45341</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52381,7 +52381,7 @@
         <v>45901.67194444445</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>45838</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52495,7 +52495,7 @@
         <v>45838</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         <v>45594</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52614,7 +52614,7 @@
         <v>45300.55028935185</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>45903.69096064815</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45904.77746527778</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52790,7 +52790,7 @@
         <v>45097</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52847,7 +52847,7 @@
         <v>45903.69358796296</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52909,7 +52909,7 @@
         <v>44969</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52966,7 +52966,7 @@
         <v>44944</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -53023,7 +53023,7 @@
         <v>45601</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>45154.35092592592</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>44652</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>45678</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53251,7 +53251,7 @@
         <v>44679</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53308,7 +53308,7 @@
         <v>45905.5756712963</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53365,7 +53365,7 @@
         <v>45905.62641203704</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53427,7 +53427,7 @@
         <v>45349</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53484,7 +53484,7 @@
         <v>45851.62179398148</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>45863.44648148148</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53603,7 +53603,7 @@
         <v>45863.45355324074</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53660,7 +53660,7 @@
         <v>45905.64862268518</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>45891.4865625</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
         <v>45656</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53836,7 +53836,7 @@
         <v>45905.62541666667</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53898,7 +53898,7 @@
         <v>45694</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53955,7 +53955,7 @@
         <v>45909.57565972222</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -54017,7 +54017,7 @@
         <v>45910.59415509259</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -54079,7 +54079,7 @@
         <v>44806</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>45867.58056712963</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>45049.66025462963</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54250,7 +54250,7 @@
         <v>45910.59475694445</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54312,7 +54312,7 @@
         <v>44574</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>44645.39157407408</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>44497.4666087963</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45152</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>44964.65261574074</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45912.7097337963</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54664,7 +54664,7 @@
         <v>44599.44832175926</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45831.46731481481</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>45904</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>45638</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45903</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45000.44666666666</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -55006,7 +55006,7 @@
         <v>45762.61341435185</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -55063,7 +55063,7 @@
         <v>45713.44519675926</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -55120,7 +55120,7 @@
         <v>45327.61831018519</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>45352</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>44944</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45266</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>44872</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45513.51815972223</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45617.59006944444</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45049</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         <v>44560</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55638,7 +55638,7 @@
         <v>45336.53908564815</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>45614.67020833334</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>45770.61341435185</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45677.39440972222</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45169</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>45244.52202546296</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55995,7 +55995,7 @@
         <v>45435.34778935185</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>45763</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>45548.42854166667</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56171,7 +56171,7 @@
         <v>44532</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56228,7 +56228,7 @@
         <v>45190</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>44977</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>45336.54270833333</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>45110</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>45194</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56518,7 +56518,7 @@
         <v>45474</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56575,7 +56575,7 @@
         <v>45611</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56632,7 +56632,7 @@
         <v>45300.55680555556</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56689,7 +56689,7 @@
         <v>45589</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56746,7 +56746,7 @@
         <v>45589</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56803,7 +56803,7 @@
         <v>44609.60171296296</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56865,7 +56865,7 @@
         <v>44503</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56922,7 +56922,7 @@
         <v>44624.35083333333</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56984,7 +56984,7 @@
         <v>45456.58491898148</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -57041,7 +57041,7 @@
         <v>44897</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -57098,7 +57098,7 @@
         <v>45729</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -57155,7 +57155,7 @@
         <v>45729</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>45327</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57269,7 +57269,7 @@
         <v>45014</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57326,7 +57326,7 @@
         <v>45222</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57383,7 +57383,7 @@
         <v>44593</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57440,7 +57440,7 @@
         <v>45685.5778125</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57497,7 +57497,7 @@
         <v>45695.59805555556</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57559,7 +57559,7 @@
         <v>45460</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57621,7 +57621,7 @@
         <v>45345.56</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -57678,7 +57678,7 @@
         <v>44914.67600694444</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -57735,7 +57735,7 @@
         <v>45061</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -57792,7 +57792,7 @@
         <v>44210</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -57849,7 +57849,7 @@
         <v>45583.47836805556</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -57911,7 +57911,7 @@
         <v>44912</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -57968,7 +57968,7 @@
         <v>44967.78984953704</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -58025,7 +58025,7 @@
         <v>45075.51982638889</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -58082,7 +58082,7 @@
         <v>45720.60410879629</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -58139,7 +58139,7 @@
         <v>45699</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -58196,7 +58196,7 @@
         <v>45733.63099537037</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -58253,7 +58253,7 @@
         <v>45426.61569444444</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>45478.60802083334</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45719.40723379629</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -58434,7 +58434,7 @@
         <v>45154.34931712963</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -567,7 +567,7 @@
         <v>45548</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         <v>45882.73309027778</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>45603</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45827.64737268518</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>44377</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>45313</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45715.38824074074</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45082</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45901.67194444445</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>45882</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>45728</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>45812.55136574074</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>44971</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44623</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>44222</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>45803.55737268519</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>45803.55260416667</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>45086</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>45202</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>44575</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>44356</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45196</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>45758</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>44180</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>45442</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>45092</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>44497</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>45799.60315972222</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>44792</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>45803.61035879629</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>44532</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>45841.64539351852</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>45316</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>45736.53695601852</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>45097</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>44500</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>45442</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>44574</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>45107</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>45915</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>44351</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44719</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>44664</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>44974</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>45474</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>44740</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45371</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>44659</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45905.62541666667</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>45905.62641203704</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>44791</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45090</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>44804</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45803.55535879629</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>44495</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>45831.55982638889</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44684</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>45910.59475694445</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>45910.59415509259</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44967</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>45222</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>45762.62260416667</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45803.61554398148</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>45715.38105324074</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>45694.55559027778</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45168.50667824074</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>45293</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>44489</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>45841.80690972223</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>45189</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>45035.44672453704</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45903</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>45922.80255787037</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>44614</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>44379</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>44651</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45783</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45358</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>44645</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>45336</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>45687</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>45107</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45665</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>45694.49650462963</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>45811.38710648148</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45098</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>45679</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>45817</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>45817.34614583333</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44487</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45818.60254629629</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>45736.49902777778</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>45314.55579861111</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>44917</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>44855</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>44958</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>44673.47858796296</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>45464</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>45442</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>44467</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>45762.57244212963</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>45167</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>45107</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>45841.81555555556</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>44909</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>45853.76976851852</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>44897</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>45896.47487268518</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>44963</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45901.66702546296</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>44849</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>45273</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>45757.49934027778</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45385</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>45805.41232638889</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>45874</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>45874.69282407407</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45917.43857638889</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>44917.59298611111</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>45820.84516203704</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>44144</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>44119</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44602</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>44583.61803240741</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>44602</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44517</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>44567.81241898148</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>44407</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>44544</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44526</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>44489</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>44609.61430555556</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>44323.58961805556</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>44299</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44714</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44491.50769675926</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>44252</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>44569.5340625</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>44486</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>44662.56783564815</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44572.39640046296</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>44659.70381944445</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>44603</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44700</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44230</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>44494</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>44839</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44784</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>44369.65428240741</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>44612</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>44720</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>44886</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>44598</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>44883.56321759259</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>44314</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>44610</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>44865.43494212963</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>44167</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>44357</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>44742</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>44704</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44533.4678587963</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>44764</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>44297</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>44153</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>44351</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>44349.49666666667</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>44584.63190972222</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>44490.64313657407</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>44609</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>44610</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>44281.4499537037</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>44335.52201388889</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>44512</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>44740.68142361111</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>44816</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>44297</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>44722.30703703704</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>44705.78475694444</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>44705.83326388889</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>44692.87630787037</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>44698.67151620371</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>44277.65263888889</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>44328.57100694445</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>44369</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>44599.43265046296</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>44543</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>44461</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15865,7 +15865,7 @@
         <v>44383</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44378.69857638889</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>44702.70721064815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>44865</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>44461.73350694445</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>44504.59193287037</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>44643.51446759259</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>44750.45800925926</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>44593</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>44442.35195601852</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44442</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>44846</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>44551.59704861111</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44134</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>44446.47693287037</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>44750.678125</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>44571.44563657408</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>44103</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>44838.40635416667</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>44459</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>44491.54116898148</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>44676</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>44479</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>44489</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>44476.61263888889</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44160</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44847.35622685185</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>44705.84535879629</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>44543.34697916666</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44517</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>44685.6212037037</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>44495</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>44634</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>44522.55518518519</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>44886.58890046296</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>44649</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>44799.36359953704</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>44583.61555555555</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>44575</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>44847</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>44733.43420138889</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>44575.4366087963</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>45223</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>44711</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>44209</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>45107.53688657407</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>44928</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>45061</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>45453</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45638</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>45776.6415162037</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>45695.8391550926</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>44109</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>45091.69766203704</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>44581.60254629629</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>45520</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>44599.42277777778</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>45777.37119212963</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45777</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45107.55574074074</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45776.45263888889</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45777.52655092593</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45777.34894675926</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>45656</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44977</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45574</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45167.3721412037</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45468</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>45776.48275462963</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>45776</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>44679.66694444444</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45777.32731481481</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45779.49085648148</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>44967.78984953704</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45119</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>44637.35744212963</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>45615</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>44637.56178240741</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45763.52995370371</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>45779.6665162037</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>44139</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>45316</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>45614.65928240741</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45695.59805555556</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>44531</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>45779.65787037037</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44519</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>45783.61053240741</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>45344.69567129629</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45694</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45294.5666550926</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>44743</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>45756.44024305556</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>44608</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>45784.80497685185</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>44816</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>45784.57266203704</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45694.49037037037</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>44508.44033564815</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>44644.37548611111</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>45426.61569444444</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45558.42498842593</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45187.61136574074</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>44569.69358796296</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>45254</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45368.64787037037</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>44993</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44531</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44400.6750925926</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>44532</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45351.54596064815</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45584.60038194444</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44623.4572337963</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44944</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>45161</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44900.54711805555</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>45618.71140046296</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>45548.42854166667</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44742</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>45583.47836805556</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>44519.64902777778</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>45736.60863425926</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>44123</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>44967</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>44872</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         <v>45091</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45371.67368055556</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45684</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>44379.56163194445</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>45407.49721064815</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45562</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>45177.79766203704</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>45212.34997685185</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45625.58501157408</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>44532</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>44944</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45093.46706018518</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45329</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>44569.49344907407</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>45583.48449074074</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>44969</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>44568.67040509259</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>45054.9271875</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>45033</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>44859.36896990741</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44159</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>45693</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44832</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>45601</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>45231</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45790.44972222222</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>45169</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>45216</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44729</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>45327</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>45726</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>45790.51186342593</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>45133</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>45790.51040509259</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>44144</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>44980</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>45552</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45523</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44645.39157407408</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>45371.50738425926</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>44266.57917824074</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>44616</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>45743.50744212963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45042</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45425.94947916667</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>45244.52202546296</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45047.31793981481</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>44624.64538194444</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>45691</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45614</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>44294.37555555555</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>45490</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>45195.64807870371</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>44960.65061342593</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>44960</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26487,7 +26487,7 @@
         <v>45583</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>45295</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>45327</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>45439</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>44659.57912037037</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45050.49392361111</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>45335.66331018518</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>45369</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26968,7 +26968,7 @@
         <v>45037</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27030,7 +27030,7 @@
         <v>44791.38336805555</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>45300</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>44533.46665509259</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45636</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45797.42777777778</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44200</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>45162</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45154.35092592592</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>45693</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>45733.63099537037</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>45691</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>45363.54878472222</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>44849</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>45677</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27843,7 +27843,7 @@
         <v>45757.6997337963</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45757</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>44277.65650462963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28014,7 +28014,7 @@
         <v>45617.59006944444</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>45797.45900462963</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44977</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>44809.92752314815</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45525</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45429</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>45638</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>45799.53803240741</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>45300.55028935185</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28542,7 +28542,7 @@
         <v>45799.53348379629</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28604,7 +28604,7 @@
         <v>44617.48311342593</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>44623</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>44762</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>45798.41734953703</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>44993</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>45799.57714120371</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>45107</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>45107</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45733.62903935185</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45799.65021990741</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45799.6527199074</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>44106</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>45737.40503472222</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45799.53947916667</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>45799.54104166666</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>45068.58563657408</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>44929</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>44798</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>44105</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>45693</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45799.43496527777</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45799.5421875</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45799.64877314815</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>45798.42252314815</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>44144</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>44847</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>45803.36384259259</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>45086.7037037037</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>45601</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>44659</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45803.63395833333</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>45608</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>44544</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45341</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>45744</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>45159.45748842593</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>44949.4708912037</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45624</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45805.4094675926</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>44593</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>44593.61355324074</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31026,7 +31026,7 @@
         <v>44131</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>45149.56928240741</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>45805.41813657407</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>45805.4255787037</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>44395</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45805.43402777778</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>44548</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31450,7 +31450,7 @@
         <v>45127</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>45805.41010416667</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>45216</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>44594</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45078</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45721.60894675926</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>44909</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31864,7 +31864,7 @@
         <v>45555.5727662037</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>45809</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45215.44233796297</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>45810.44339120371</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>45809</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>45614</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>45182</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>45182</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>45145</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>45358</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>44273</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>45809</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45809</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>45453.69339120371</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32697,7 +32697,7 @@
         <v>44616</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45511</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32811,7 +32811,7 @@
         <v>44140</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>45810.44299768518</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>45719.40723379629</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>45644</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>45644</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>45646.50211805556</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>45055</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>44912</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>44551.76711805556</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>45611</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45812.48032407407</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>45813.46034722222</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>45813</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>45698.65606481482</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>45407.69575231482</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>45307</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45236.47697916667</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>44512</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>45341</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>45097</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>45719.43755787037</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45721.34715277778</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>45814</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>45006</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>45202</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>45474.41729166666</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -34323,7 +34323,7 @@
         <v>45678</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>45817</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
         <v>44893</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>45182</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>45818.57910879629</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>44946</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>44522</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44904</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>44245</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>45817</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44593.64863425926</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>45152</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>45299</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>44126</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>44403.29719907408</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44130</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44426</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>45820</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45642</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>45307</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>45293</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>44819.50233796296</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>45351.48662037037</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>45726</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>45664</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>44600</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>45456.59535879629</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>45694</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>44806</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>45371</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36088,7 +36088,7 @@
         <v>45338.49412037037</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>44358.63490740741</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44908.425625</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>45820</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>45820</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>45163.59913194444</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36430,7 +36430,7 @@
         <v>45181.58055555556</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>45134.57021990741</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44866</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>45236</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>45152</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44883</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44799.36695601852</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45821.44101851852</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>45202.4997337963</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>44602</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>45164.82913194445</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>45341.63811342593</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>45446.78256944445</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>44210</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>45524</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>45208.4350462963</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>45065.43013888889</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>45426.34148148148</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44371.49178240741</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>45723</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>45699</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44967.80034722222</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>44967</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>45631.44464120371</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>44503</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45720.60410879629</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>45344</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>45000.44666666666</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>44966</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45188</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>45177.56940972222</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>44560</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>45036</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>44817</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>44831</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>44629.42423611111</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>45677.39440972222</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45021.29524305555</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>44699</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>44574</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>45188.42052083334</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45096</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>45721.35173611111</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>44886</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38993,7 +38993,7 @@
         <v>44516</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         <v>45580</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -39107,7 +39107,7 @@
         <v>45293</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>45656</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45757.67611111111</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39283,7 +39283,7 @@
         <v>45300.55680555556</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>44155</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39397,7 +39397,7 @@
         <v>44560</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39454,7 +39454,7 @@
         <v>44446</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39511,7 +39511,7 @@
         <v>45208.46130787037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>44594</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39625,7 +39625,7 @@
         <v>45552</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39682,7 +39682,7 @@
         <v>45173</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39739,7 +39739,7 @@
         <v>45426</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>44912.29869212963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>45194</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45231</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39972,7 +39972,7 @@
         <v>44886.5928125</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>45520</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -40086,7 +40086,7 @@
         <v>45201.62318287037</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -40143,7 +40143,7 @@
         <v>45824.43798611111</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>44967.55960648148</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40262,7 +40262,7 @@
         <v>44614.59027777778</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40319,7 +40319,7 @@
         <v>44810</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>44930</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>45098.62966435185</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40490,7 +40490,7 @@
         <v>45756.50738425926</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>45014</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>45121</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>45175</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>45474</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45614</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>45194</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40904,7 +40904,7 @@
         <v>45729</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>44819.62</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>45637</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>45335</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45391.37361111111</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45825.49060185185</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>44832.49594907407</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>45825.44482638889</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45821.45905092593</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
         <v>45317</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>45341</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45254</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>45763</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>45714.55368055555</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41727,7 +41727,7 @@
         <v>45719.42197916667</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
         <v>45719.43646990741</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>44935</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45222</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>45216.39040509259</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45695.83655092592</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>44168.55746527778</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>45638</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -42198,7 +42198,7 @@
         <v>44914.67600694444</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42255,7 +42255,7 @@
         <v>44678.3315625</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>44501.71344907407</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42379,7 +42379,7 @@
         <v>44984.69216435185</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -42441,7 +42441,7 @@
         <v>44379.5745949074</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45827.64092592592</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>44588</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42612,7 +42612,7 @@
         <v>45259</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>45827.46288194445</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42731,7 +42731,7 @@
         <v>45231.62840277778</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42788,7 +42788,7 @@
         <v>45705</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45259.52809027778</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>44207</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45827.62096064815</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45831.40671296296</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45524</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45831.72686342592</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>45831.73</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>45831.42365740741</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43326,7 +43326,7 @@
         <v>45831.42616898148</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         <v>45642</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>45390</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>44623.5571875</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>44960</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>44960.66233796296</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>45190</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43735,7 +43735,7 @@
         <v>45054.95675925926</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>44575</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43849,7 +43849,7 @@
         <v>44994</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43906,7 +43906,7 @@
         <v>44679.68706018518</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45736.45847222222</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44532</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>45643</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44820.47935185185</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>44733</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>45352</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>45181.33571759259</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44377,7 +44377,7 @@
         <v>45358</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -44434,7 +44434,7 @@
         <v>45719.4094212963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45719.43872685185</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>44894.57065972222</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44620,7 +44620,7 @@
         <v>45049</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45202</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>45832.35545138889</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45259</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>44378.56137731481</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>45832.35590277778</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44982,7 +44982,7 @@
         <v>44944</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -45039,7 +45039,7 @@
         <v>44504</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -45096,7 +45096,7 @@
         <v>44222</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -45153,7 +45153,7 @@
         <v>45225.46480324074</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -45210,7 +45210,7 @@
         <v>45835.62752314815</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -45272,7 +45272,7 @@
         <v>45254</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45329,7 +45329,7 @@
         <v>44603</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45386,7 +45386,7 @@
         <v>45513.51815972223</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>44328</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>45821.31292824074</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>45839</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45839</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>44848</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45839</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45815,7 +45815,7 @@
         <v>44438</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45877,7 +45877,7 @@
         <v>45693</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45934,7 +45934,7 @@
         <v>45841.5847337963</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45991,7 +45991,7 @@
         <v>45267</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -46053,7 +46053,7 @@
         <v>45840</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -46110,7 +46110,7 @@
         <v>45379</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -46167,7 +46167,7 @@
         <v>45323.55914351852</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>45757</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>45751.32001157408</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46343,7 +46343,7 @@
         <v>45758</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46400,7 +46400,7 @@
         <v>45840.68518518518</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>45763</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46514,7 +46514,7 @@
         <v>45638</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46571,7 +46571,7 @@
         <v>45842.74049768518</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46628,7 +46628,7 @@
         <v>45152</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46690,7 +46690,7 @@
         <v>45679</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>44588</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>45763.52744212963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46861,7 +46861,7 @@
         <v>45113.80170138889</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>44883</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46980,7 +46980,7 @@
         <v>45693</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -47037,7 +47037,7 @@
         <v>44553</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>45770.61341435185</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -47156,7 +47156,7 @@
         <v>45705.2953125</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>45707</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -47280,7 +47280,7 @@
         <v>44964.65261574074</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>44123</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>45670</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47456,7 +47456,7 @@
         <v>45113</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47513,7 +47513,7 @@
         <v>45845.53202546296</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45096</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47627,7 +47627,7 @@
         <v>44788</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47684,7 +47684,7 @@
         <v>45098.63572916666</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47741,7 +47741,7 @@
         <v>45670</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47803,7 +47803,7 @@
         <v>45148</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47860,7 +47860,7 @@
         <v>45361.57299768519</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47922,7 +47922,7 @@
         <v>45456.58491898148</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47979,7 +47979,7 @@
         <v>44980</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -48036,7 +48036,7 @@
         <v>45884</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -48093,7 +48093,7 @@
         <v>45104.6828125</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -48150,7 +48150,7 @@
         <v>45890</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>45478.60802083334</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45891.33204861111</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>45096</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>44977</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45259</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48502,7 +48502,7 @@
         <v>45460</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45642.63524305556</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45763.6503125</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45231.54601851852</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45849.49259259259</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>44609.60171296296</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45891.46827546296</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>45644.62677083333</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>45761.47540509259</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45852.39642361111</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
         <v>45761.47748842592</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45426</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45852.72965277778</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45852</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45851.62018518519</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49382,7 +49382,7 @@
         <v>45852.68978009259</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45852.67366898148</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49506,7 +49506,7 @@
         <v>45852.36871527778</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>45173</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49620,7 +49620,7 @@
         <v>45851.60097222222</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49682,7 +49682,7 @@
         <v>44816</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>45699.71063657408</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45308.63298611111</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>45107</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49910,7 +49910,7 @@
         <v>44535</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>44629.57741898148</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>44888</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -50091,7 +50091,7 @@
         <v>44608</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -50153,7 +50153,7 @@
         <v>45110</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -50210,7 +50210,7 @@
         <v>44209</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -50267,7 +50267,7 @@
         <v>45707</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50329,7 +50329,7 @@
         <v>45896.61050925926</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50386,7 +50386,7 @@
         <v>45896</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50443,7 +50443,7 @@
         <v>45896</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50500,7 +50500,7 @@
         <v>45644</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>44497.4666087963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50614,7 +50614,7 @@
         <v>44946.43564814814</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50671,7 +50671,7 @@
         <v>44965</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50728,7 +50728,7 @@
         <v>44965</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50785,7 +50785,7 @@
         <v>45896.57368055556</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50842,7 +50842,7 @@
         <v>44679</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50899,7 +50899,7 @@
         <v>45897</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50956,7 +50956,7 @@
         <v>45594</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -51018,7 +51018,7 @@
         <v>45336.53908564815</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -51075,7 +51075,7 @@
         <v>45854.44017361111</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -51137,7 +51137,7 @@
         <v>45896.57171296296</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -51194,7 +51194,7 @@
         <v>45336.54270833333</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -51251,7 +51251,7 @@
         <v>45856.34034722222</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51313,7 +51313,7 @@
         <v>45856.34231481481</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>45901.41853009259</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51437,7 +51437,7 @@
         <v>44223</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51494,7 +51494,7 @@
         <v>45898.46040509259</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>45901.41756944444</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51613,7 +51613,7 @@
         <v>45856.34959490741</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51675,7 +51675,7 @@
         <v>45856</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51737,7 +51737,7 @@
         <v>44623.41775462963</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>45645</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45903.69358796296</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45838</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>45902.42243055555</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -52042,7 +52042,7 @@
         <v>44614.69730324074</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45644.47723379629</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45259</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45075.51982638889</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45903.69096064815</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>45589</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52394,7 +52394,7 @@
         <v>45589</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52451,7 +52451,7 @@
         <v>45614.67020833334</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52508,7 +52508,7 @@
         <v>45838</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>45695.84078703704</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52627,7 +52627,7 @@
         <v>45148</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45148</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52741,7 +52741,7 @@
         <v>45182</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52798,7 +52798,7 @@
         <v>45838</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52855,7 +52855,7 @@
         <v>45266</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52912,7 +52912,7 @@
         <v>45646.61892361111</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52969,7 +52969,7 @@
         <v>45695.59197916667</v>
       </c>
       <c r="C823" s="1" 